--- a/Sindhi Muslim/Student Attendance/ECE (ROSE)/ECE (ROSE) Monthly Attendance - Aug2024-Jan2025.xlsx
+++ b/Sindhi Muslim/Student Attendance/ECE (ROSE)/ECE (ROSE) Monthly Attendance - Aug2024-Jan2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Student Attendance\ECE (ROSE)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F08251-C4EC-4961-8806-50BEBB78CB67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CCF0CF1-D42A-4737-AC59-F76B8B735AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -790,24 +790,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="17" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -831,6 +813,24 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -1610,75 +1610,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="39"/>
-      <c r="U1" s="39"/>
-      <c r="V1" s="39"/>
-      <c r="W1" s="39"/>
-      <c r="X1" s="39"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
     </row>
     <row r="2" spans="1:28" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="40"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="40"/>
-      <c r="U2" s="40"/>
-      <c r="V2" s="40"/>
-      <c r="W2" s="40"/>
-      <c r="X2" s="40"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
+      <c r="W2" s="48"/>
+      <c r="X2" s="48"/>
     </row>
     <row r="3" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="E3" s="38" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -1749,25 +1749,25 @@
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="W3" s="35" t="s">
+      <c r="W3" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="X3" s="35" t="s">
+      <c r="X3" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="Y3" s="41" t="s">
+      <c r="Y3" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="42"/>
+      <c r="Z3" s="36"/>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
     </row>
     <row r="4" spans="1:28" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="45"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
       <c r="F4" s="23">
         <v>45519</v>
       </c>
@@ -1819,8 +1819,8 @@
       <c r="V4" s="23">
         <v>45535</v>
       </c>
-      <c r="W4" s="35"/>
-      <c r="X4" s="35"/>
+      <c r="W4" s="46"/>
+      <c r="X4" s="46"/>
       <c r="Y4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1853,13 +1853,13 @@
       <c r="H5" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I5" s="46" t="s">
+      <c r="I5" s="40" t="s">
         <v>123</v>
       </c>
       <c r="J5" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K5" s="36" t="s">
+      <c r="K5" s="43" t="s">
         <v>122</v>
       </c>
       <c r="L5" s="12" t="s">
@@ -1874,10 +1874,10 @@
       <c r="O5" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P5" s="46" t="s">
+      <c r="P5" s="40" t="s">
         <v>123</v>
       </c>
-      <c r="Q5" s="36" t="s">
+      <c r="Q5" s="43" t="s">
         <v>118</v>
       </c>
       <c r="R5" s="12" t="s">
@@ -1889,7 +1889,7 @@
       <c r="T5" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="U5" s="36" t="s">
+      <c r="U5" s="43" t="s">
         <v>119</v>
       </c>
       <c r="V5" s="12" t="s">
@@ -1937,11 +1937,11 @@
       <c r="H6" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I6" s="47"/>
+      <c r="I6" s="41"/>
       <c r="J6" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K6" s="37"/>
+      <c r="K6" s="44"/>
       <c r="L6" s="12" t="s">
         <v>117</v>
       </c>
@@ -1954,8 +1954,8 @@
       <c r="O6" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P6" s="47"/>
-      <c r="Q6" s="37"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="44"/>
       <c r="R6" s="12" t="s">
         <v>117</v>
       </c>
@@ -1965,7 +1965,7 @@
       <c r="T6" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="U6" s="37"/>
+      <c r="U6" s="44"/>
       <c r="V6" s="12" t="s">
         <v>116</v>
       </c>
@@ -2009,11 +2009,11 @@
       <c r="H7" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I7" s="47"/>
+      <c r="I7" s="41"/>
       <c r="J7" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K7" s="37"/>
+      <c r="K7" s="44"/>
       <c r="L7" s="12" t="s">
         <v>117</v>
       </c>
@@ -2026,8 +2026,8 @@
       <c r="O7" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="P7" s="47"/>
-      <c r="Q7" s="37"/>
+      <c r="P7" s="41"/>
+      <c r="Q7" s="44"/>
       <c r="R7" s="12" t="s">
         <v>117</v>
       </c>
@@ -2037,7 +2037,7 @@
       <c r="T7" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="U7" s="37"/>
+      <c r="U7" s="44"/>
       <c r="V7" s="12" t="s">
         <v>116</v>
       </c>
@@ -2079,11 +2079,11 @@
       <c r="H8" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I8" s="47"/>
+      <c r="I8" s="41"/>
       <c r="J8" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K8" s="37"/>
+      <c r="K8" s="44"/>
       <c r="L8" s="12" t="s">
         <v>117</v>
       </c>
@@ -2096,8 +2096,8 @@
       <c r="O8" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="P8" s="47"/>
-      <c r="Q8" s="37"/>
+      <c r="P8" s="41"/>
+      <c r="Q8" s="44"/>
       <c r="R8" s="12" t="s">
         <v>117</v>
       </c>
@@ -2107,7 +2107,7 @@
       <c r="T8" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="U8" s="37"/>
+      <c r="U8" s="44"/>
       <c r="V8" s="12" t="s">
         <v>116</v>
       </c>
@@ -2119,12 +2119,12 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="Y8" s="41" t="s">
+      <c r="Y8" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="Z8" s="43"/>
-      <c r="AA8" s="43"/>
-      <c r="AB8" s="42"/>
+      <c r="Z8" s="37"/>
+      <c r="AA8" s="37"/>
+      <c r="AB8" s="36"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
@@ -2151,11 +2151,11 @@
       <c r="H9" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I9" s="47"/>
+      <c r="I9" s="41"/>
       <c r="J9" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K9" s="37"/>
+      <c r="K9" s="44"/>
       <c r="L9" s="12" t="s">
         <v>117</v>
       </c>
@@ -2168,8 +2168,8 @@
       <c r="O9" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="P9" s="47"/>
-      <c r="Q9" s="37"/>
+      <c r="P9" s="41"/>
+      <c r="Q9" s="44"/>
       <c r="R9" s="12" t="s">
         <v>117</v>
       </c>
@@ -2179,7 +2179,7 @@
       <c r="T9" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="U9" s="37"/>
+      <c r="U9" s="44"/>
       <c r="V9" s="12" t="s">
         <v>116</v>
       </c>
@@ -2229,11 +2229,11 @@
       <c r="H10" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I10" s="47"/>
+      <c r="I10" s="41"/>
       <c r="J10" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K10" s="37"/>
+      <c r="K10" s="44"/>
       <c r="L10" s="12" t="s">
         <v>117</v>
       </c>
@@ -2246,8 +2246,8 @@
       <c r="O10" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P10" s="47"/>
-      <c r="Q10" s="37"/>
+      <c r="P10" s="41"/>
+      <c r="Q10" s="44"/>
       <c r="R10" s="12" t="s">
         <v>117</v>
       </c>
@@ -2257,7 +2257,7 @@
       <c r="T10" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="U10" s="37"/>
+      <c r="U10" s="44"/>
       <c r="V10" s="12" t="s">
         <v>116</v>
       </c>
@@ -2310,11 +2310,11 @@
       <c r="H11" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I11" s="47"/>
+      <c r="I11" s="41"/>
       <c r="J11" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K11" s="37"/>
+      <c r="K11" s="44"/>
       <c r="L11" s="12" t="s">
         <v>117</v>
       </c>
@@ -2327,8 +2327,8 @@
       <c r="O11" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="P11" s="47"/>
-      <c r="Q11" s="37"/>
+      <c r="P11" s="41"/>
+      <c r="Q11" s="44"/>
       <c r="R11" s="12" t="s">
         <v>117</v>
       </c>
@@ -2338,7 +2338,7 @@
       <c r="T11" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="U11" s="37"/>
+      <c r="U11" s="44"/>
       <c r="V11" s="12" t="s">
         <v>116</v>
       </c>
@@ -2389,11 +2389,11 @@
       <c r="H12" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I12" s="47"/>
+      <c r="I12" s="41"/>
       <c r="J12" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K12" s="37"/>
+      <c r="K12" s="44"/>
       <c r="L12" s="12" t="s">
         <v>117</v>
       </c>
@@ -2406,8 +2406,8 @@
       <c r="O12" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="37"/>
+      <c r="P12" s="41"/>
+      <c r="Q12" s="44"/>
       <c r="R12" s="12" t="s">
         <v>117</v>
       </c>
@@ -2417,7 +2417,7 @@
       <c r="T12" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="U12" s="37"/>
+      <c r="U12" s="44"/>
       <c r="V12" s="12" t="s">
         <v>116</v>
       </c>
@@ -2470,11 +2470,11 @@
       <c r="H13" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I13" s="47"/>
+      <c r="I13" s="41"/>
       <c r="J13" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K13" s="37"/>
+      <c r="K13" s="44"/>
       <c r="L13" s="12" t="s">
         <v>117</v>
       </c>
@@ -2487,8 +2487,8 @@
       <c r="O13" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P13" s="47"/>
-      <c r="Q13" s="37"/>
+      <c r="P13" s="41"/>
+      <c r="Q13" s="44"/>
       <c r="R13" s="12" t="s">
         <v>117</v>
       </c>
@@ -2498,7 +2498,7 @@
       <c r="T13" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="U13" s="37"/>
+      <c r="U13" s="44"/>
       <c r="V13" s="12" t="s">
         <v>116</v>
       </c>
@@ -2540,11 +2540,11 @@
       <c r="H14" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I14" s="47"/>
+      <c r="I14" s="41"/>
       <c r="J14" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K14" s="37"/>
+      <c r="K14" s="44"/>
       <c r="L14" s="12" t="s">
         <v>117</v>
       </c>
@@ -2557,8 +2557,8 @@
       <c r="O14" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P14" s="47"/>
-      <c r="Q14" s="37"/>
+      <c r="P14" s="41"/>
+      <c r="Q14" s="44"/>
       <c r="R14" s="12" t="s">
         <v>117</v>
       </c>
@@ -2568,7 +2568,7 @@
       <c r="T14" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="U14" s="37"/>
+      <c r="U14" s="44"/>
       <c r="V14" s="12" t="s">
         <v>116</v>
       </c>
@@ -2610,11 +2610,11 @@
       <c r="H15" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I15" s="47"/>
+      <c r="I15" s="41"/>
       <c r="J15" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K15" s="37"/>
+      <c r="K15" s="44"/>
       <c r="L15" s="12" t="s">
         <v>117</v>
       </c>
@@ -2627,8 +2627,8 @@
       <c r="O15" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="P15" s="47"/>
-      <c r="Q15" s="37"/>
+      <c r="P15" s="41"/>
+      <c r="Q15" s="44"/>
       <c r="R15" s="12" t="s">
         <v>117</v>
       </c>
@@ -2638,7 +2638,7 @@
       <c r="T15" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="U15" s="37"/>
+      <c r="U15" s="44"/>
       <c r="V15" s="12" t="s">
         <v>116</v>
       </c>
@@ -2680,11 +2680,11 @@
       <c r="H16" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I16" s="47"/>
+      <c r="I16" s="41"/>
       <c r="J16" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K16" s="37"/>
+      <c r="K16" s="44"/>
       <c r="L16" s="12" t="s">
         <v>117</v>
       </c>
@@ -2697,8 +2697,8 @@
       <c r="O16" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P16" s="47"/>
-      <c r="Q16" s="37"/>
+      <c r="P16" s="41"/>
+      <c r="Q16" s="44"/>
       <c r="R16" s="12" t="s">
         <v>117</v>
       </c>
@@ -2708,7 +2708,7 @@
       <c r="T16" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="U16" s="37"/>
+      <c r="U16" s="44"/>
       <c r="V16" s="12" t="s">
         <v>116</v>
       </c>
@@ -2720,12 +2720,12 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="Y16" s="41" t="s">
+      <c r="Y16" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="Z16" s="43"/>
-      <c r="AA16" s="43"/>
-      <c r="AB16" s="42"/>
+      <c r="Z16" s="37"/>
+      <c r="AA16" s="37"/>
+      <c r="AB16" s="36"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
@@ -2752,11 +2752,11 @@
       <c r="H17" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I17" s="47"/>
+      <c r="I17" s="41"/>
       <c r="J17" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K17" s="37"/>
+      <c r="K17" s="44"/>
       <c r="L17" s="12" t="s">
         <v>117</v>
       </c>
@@ -2769,8 +2769,8 @@
       <c r="O17" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P17" s="47"/>
-      <c r="Q17" s="37"/>
+      <c r="P17" s="41"/>
+      <c r="Q17" s="44"/>
       <c r="R17" s="12" t="s">
         <v>116</v>
       </c>
@@ -2780,7 +2780,7 @@
       <c r="T17" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="U17" s="37"/>
+      <c r="U17" s="44"/>
       <c r="V17" s="12" t="s">
         <v>116</v>
       </c>
@@ -2830,11 +2830,11 @@
       <c r="H18" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I18" s="47"/>
+      <c r="I18" s="41"/>
       <c r="J18" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K18" s="37"/>
+      <c r="K18" s="44"/>
       <c r="L18" s="12" t="s">
         <v>117</v>
       </c>
@@ -2847,8 +2847,8 @@
       <c r="O18" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P18" s="47"/>
-      <c r="Q18" s="37"/>
+      <c r="P18" s="41"/>
+      <c r="Q18" s="44"/>
       <c r="R18" s="12" t="s">
         <v>117</v>
       </c>
@@ -2858,7 +2858,7 @@
       <c r="T18" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="U18" s="37"/>
+      <c r="U18" s="44"/>
       <c r="V18" s="12" t="s">
         <v>116</v>
       </c>
@@ -2911,11 +2911,11 @@
       <c r="H19" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I19" s="47"/>
+      <c r="I19" s="41"/>
       <c r="J19" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K19" s="37"/>
+      <c r="K19" s="44"/>
       <c r="L19" s="12" t="s">
         <v>117</v>
       </c>
@@ -2928,8 +2928,8 @@
       <c r="O19" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P19" s="47"/>
-      <c r="Q19" s="37"/>
+      <c r="P19" s="41"/>
+      <c r="Q19" s="44"/>
       <c r="R19" s="12" t="s">
         <v>117</v>
       </c>
@@ -2939,7 +2939,7 @@
       <c r="T19" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="U19" s="37"/>
+      <c r="U19" s="44"/>
       <c r="V19" s="12" t="s">
         <v>116</v>
       </c>
@@ -2992,11 +2992,11 @@
       <c r="H20" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I20" s="47"/>
+      <c r="I20" s="41"/>
       <c r="J20" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K20" s="37"/>
+      <c r="K20" s="44"/>
       <c r="L20" s="12" t="s">
         <v>117</v>
       </c>
@@ -3009,8 +3009,8 @@
       <c r="O20" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P20" s="47"/>
-      <c r="Q20" s="37"/>
+      <c r="P20" s="41"/>
+      <c r="Q20" s="44"/>
       <c r="R20" s="12" t="s">
         <v>117</v>
       </c>
@@ -3020,7 +3020,7 @@
       <c r="T20" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="U20" s="37"/>
+      <c r="U20" s="44"/>
       <c r="V20" s="12" t="s">
         <v>116</v>
       </c>
@@ -3073,11 +3073,11 @@
       <c r="H21" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I21" s="47"/>
+      <c r="I21" s="41"/>
       <c r="J21" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K21" s="37"/>
+      <c r="K21" s="44"/>
       <c r="L21" s="12" t="s">
         <v>117</v>
       </c>
@@ -3090,8 +3090,8 @@
       <c r="O21" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P21" s="47"/>
-      <c r="Q21" s="37"/>
+      <c r="P21" s="41"/>
+      <c r="Q21" s="44"/>
       <c r="R21" s="12" t="s">
         <v>116</v>
       </c>
@@ -3101,7 +3101,7 @@
       <c r="T21" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="U21" s="37"/>
+      <c r="U21" s="44"/>
       <c r="V21" s="12" t="s">
         <v>116</v>
       </c>
@@ -3139,11 +3139,11 @@
       <c r="H22" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I22" s="47"/>
+      <c r="I22" s="41"/>
       <c r="J22" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K22" s="37"/>
+      <c r="K22" s="44"/>
       <c r="L22" s="12" t="s">
         <v>117</v>
       </c>
@@ -3156,8 +3156,8 @@
       <c r="O22" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="P22" s="47"/>
-      <c r="Q22" s="37"/>
+      <c r="P22" s="41"/>
+      <c r="Q22" s="44"/>
       <c r="R22" s="12" t="s">
         <v>117</v>
       </c>
@@ -3167,7 +3167,7 @@
       <c r="T22" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="U22" s="37"/>
+      <c r="U22" s="44"/>
       <c r="V22" s="12" t="s">
         <v>116</v>
       </c>
@@ -3205,11 +3205,11 @@
       <c r="H23" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I23" s="47"/>
+      <c r="I23" s="41"/>
       <c r="J23" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K23" s="37"/>
+      <c r="K23" s="44"/>
       <c r="L23" s="12" t="s">
         <v>117</v>
       </c>
@@ -3222,8 +3222,8 @@
       <c r="O23" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P23" s="47"/>
-      <c r="Q23" s="37"/>
+      <c r="P23" s="41"/>
+      <c r="Q23" s="44"/>
       <c r="R23" s="12" t="s">
         <v>117</v>
       </c>
@@ -3233,7 +3233,7 @@
       <c r="T23" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="U23" s="37"/>
+      <c r="U23" s="44"/>
       <c r="V23" s="12" t="s">
         <v>116</v>
       </c>
@@ -3271,9 +3271,9 @@
       <c r="H24" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I24" s="47"/>
+      <c r="I24" s="41"/>
       <c r="J24" s="12"/>
-      <c r="K24" s="37"/>
+      <c r="K24" s="44"/>
       <c r="L24" s="12" t="s">
         <v>117</v>
       </c>
@@ -3286,8 +3286,8 @@
       <c r="O24" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P24" s="47"/>
-      <c r="Q24" s="37"/>
+      <c r="P24" s="41"/>
+      <c r="Q24" s="44"/>
       <c r="R24" s="12" t="s">
         <v>117</v>
       </c>
@@ -3297,7 +3297,7 @@
       <c r="T24" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="U24" s="37"/>
+      <c r="U24" s="44"/>
       <c r="V24" s="12" t="s">
         <v>116</v>
       </c>
@@ -3335,11 +3335,11 @@
       <c r="H25" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I25" s="47"/>
+      <c r="I25" s="41"/>
       <c r="J25" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K25" s="37"/>
+      <c r="K25" s="44"/>
       <c r="L25" s="12" t="s">
         <v>117</v>
       </c>
@@ -3352,8 +3352,8 @@
       <c r="O25" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="P25" s="47"/>
-      <c r="Q25" s="37"/>
+      <c r="P25" s="41"/>
+      <c r="Q25" s="44"/>
       <c r="R25" s="12" t="s">
         <v>117</v>
       </c>
@@ -3363,7 +3363,7 @@
       <c r="T25" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="U25" s="37"/>
+      <c r="U25" s="44"/>
       <c r="V25" s="12" t="s">
         <v>116</v>
       </c>
@@ -3395,15 +3395,15 @@
       <c r="F26" s="12"/>
       <c r="G26" s="12"/>
       <c r="H26" s="12"/>
-      <c r="I26" s="47"/>
+      <c r="I26" s="41"/>
       <c r="J26" s="12"/>
-      <c r="K26" s="37"/>
+      <c r="K26" s="44"/>
       <c r="L26" s="12"/>
       <c r="M26" s="12"/>
       <c r="N26" s="12"/>
       <c r="O26" s="12"/>
-      <c r="P26" s="47"/>
-      <c r="Q26" s="37"/>
+      <c r="P26" s="41"/>
+      <c r="Q26" s="44"/>
       <c r="R26" s="12" t="s">
         <v>117</v>
       </c>
@@ -3413,7 +3413,7 @@
       <c r="T26" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="U26" s="37"/>
+      <c r="U26" s="44"/>
       <c r="V26" s="12" t="s">
         <v>116</v>
       </c>
@@ -3445,19 +3445,19 @@
       <c r="F27" s="12"/>
       <c r="G27" s="12"/>
       <c r="H27" s="12"/>
-      <c r="I27" s="47"/>
+      <c r="I27" s="41"/>
       <c r="J27" s="12"/>
-      <c r="K27" s="37"/>
+      <c r="K27" s="44"/>
       <c r="L27" s="12"/>
       <c r="M27" s="12"/>
       <c r="N27" s="12"/>
       <c r="O27" s="12"/>
-      <c r="P27" s="47"/>
-      <c r="Q27" s="37"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="44"/>
       <c r="R27" s="12"/>
       <c r="S27" s="12"/>
       <c r="T27" s="12"/>
-      <c r="U27" s="37"/>
+      <c r="U27" s="44"/>
       <c r="V27" s="12"/>
       <c r="W27" s="5">
         <f t="shared" si="1"/>
@@ -3493,11 +3493,11 @@
       <c r="H28" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I28" s="47"/>
+      <c r="I28" s="41"/>
       <c r="J28" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K28" s="37"/>
+      <c r="K28" s="44"/>
       <c r="L28" s="12" t="s">
         <v>117</v>
       </c>
@@ -3510,8 +3510,8 @@
       <c r="O28" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P28" s="47"/>
-      <c r="Q28" s="37"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="44"/>
       <c r="R28" s="12" t="s">
         <v>117</v>
       </c>
@@ -3521,7 +3521,7 @@
       <c r="T28" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="U28" s="37"/>
+      <c r="U28" s="44"/>
       <c r="V28" s="12" t="s">
         <v>116</v>
       </c>
@@ -3559,9 +3559,9 @@
       <c r="H29" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I29" s="47"/>
+      <c r="I29" s="41"/>
       <c r="J29" s="12"/>
-      <c r="K29" s="37"/>
+      <c r="K29" s="44"/>
       <c r="L29" s="12" t="s">
         <v>116</v>
       </c>
@@ -3574,8 +3574,8 @@
       <c r="O29" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P29" s="47"/>
-      <c r="Q29" s="37"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="44"/>
       <c r="R29" s="12" t="s">
         <v>116</v>
       </c>
@@ -3585,7 +3585,7 @@
       <c r="T29" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="U29" s="37"/>
+      <c r="U29" s="44"/>
       <c r="V29" s="12" t="s">
         <v>116</v>
       </c>
@@ -3623,11 +3623,11 @@
       <c r="H30" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I30" s="47"/>
+      <c r="I30" s="41"/>
       <c r="J30" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K30" s="37"/>
+      <c r="K30" s="44"/>
       <c r="L30" s="12" t="s">
         <v>117</v>
       </c>
@@ -3640,8 +3640,8 @@
       <c r="O30" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="P30" s="47"/>
-      <c r="Q30" s="37"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="44"/>
       <c r="R30" s="12" t="s">
         <v>116</v>
       </c>
@@ -3651,7 +3651,7 @@
       <c r="T30" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="U30" s="37"/>
+      <c r="U30" s="44"/>
       <c r="V30" s="12" t="s">
         <v>116</v>
       </c>
@@ -3689,11 +3689,11 @@
       <c r="H31" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I31" s="47"/>
+      <c r="I31" s="41"/>
       <c r="J31" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K31" s="37"/>
+      <c r="K31" s="44"/>
       <c r="L31" s="12" t="s">
         <v>117</v>
       </c>
@@ -3706,8 +3706,8 @@
       <c r="O31" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P31" s="47"/>
-      <c r="Q31" s="37"/>
+      <c r="P31" s="41"/>
+      <c r="Q31" s="44"/>
       <c r="R31" s="12" t="s">
         <v>117</v>
       </c>
@@ -3717,7 +3717,7 @@
       <c r="T31" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="U31" s="37"/>
+      <c r="U31" s="44"/>
       <c r="V31" s="12" t="s">
         <v>116</v>
       </c>
@@ -3755,11 +3755,11 @@
       <c r="H32" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I32" s="47"/>
+      <c r="I32" s="41"/>
       <c r="J32" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K32" s="37"/>
+      <c r="K32" s="44"/>
       <c r="L32" s="12" t="s">
         <v>117</v>
       </c>
@@ -3772,8 +3772,8 @@
       <c r="O32" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="P32" s="47"/>
-      <c r="Q32" s="37"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="44"/>
       <c r="R32" s="12" t="s">
         <v>116</v>
       </c>
@@ -3783,7 +3783,7 @@
       <c r="T32" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="U32" s="37"/>
+      <c r="U32" s="44"/>
       <c r="V32" s="12" t="s">
         <v>116</v>
       </c>
@@ -3821,11 +3821,11 @@
       <c r="H33" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I33" s="47"/>
+      <c r="I33" s="41"/>
       <c r="J33" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K33" s="37"/>
+      <c r="K33" s="44"/>
       <c r="L33" s="12" t="s">
         <v>117</v>
       </c>
@@ -3838,8 +3838,8 @@
       <c r="O33" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P33" s="47"/>
-      <c r="Q33" s="37"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="44"/>
       <c r="R33" s="12" t="s">
         <v>117</v>
       </c>
@@ -3849,7 +3849,7 @@
       <c r="T33" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="U33" s="37"/>
+      <c r="U33" s="44"/>
       <c r="V33" s="12" t="s">
         <v>116</v>
       </c>
@@ -3887,11 +3887,11 @@
       <c r="H34" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I34" s="47"/>
+      <c r="I34" s="41"/>
       <c r="J34" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K34" s="37"/>
+      <c r="K34" s="44"/>
       <c r="L34" s="12" t="s">
         <v>117</v>
       </c>
@@ -3904,8 +3904,8 @@
       <c r="O34" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P34" s="47"/>
-      <c r="Q34" s="37"/>
+      <c r="P34" s="41"/>
+      <c r="Q34" s="44"/>
       <c r="R34" s="12" t="s">
         <v>117</v>
       </c>
@@ -3915,7 +3915,7 @@
       <c r="T34" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="U34" s="37"/>
+      <c r="U34" s="44"/>
       <c r="V34" s="12" t="s">
         <v>116</v>
       </c>
@@ -3953,11 +3953,11 @@
       <c r="H35" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I35" s="47"/>
+      <c r="I35" s="41"/>
       <c r="J35" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K35" s="37"/>
+      <c r="K35" s="44"/>
       <c r="L35" s="12" t="s">
         <v>117</v>
       </c>
@@ -3970,8 +3970,8 @@
       <c r="O35" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P35" s="47"/>
-      <c r="Q35" s="37"/>
+      <c r="P35" s="41"/>
+      <c r="Q35" s="44"/>
       <c r="R35" s="12" t="s">
         <v>116</v>
       </c>
@@ -3981,7 +3981,7 @@
       <c r="T35" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="U35" s="37"/>
+      <c r="U35" s="44"/>
       <c r="V35" s="12" t="s">
         <v>116</v>
       </c>
@@ -4019,9 +4019,9 @@
       <c r="H36" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I36" s="47"/>
+      <c r="I36" s="41"/>
       <c r="J36" s="12"/>
-      <c r="K36" s="37"/>
+      <c r="K36" s="44"/>
       <c r="L36" s="12" t="s">
         <v>116</v>
       </c>
@@ -4034,8 +4034,8 @@
       <c r="O36" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="P36" s="47"/>
-      <c r="Q36" s="37"/>
+      <c r="P36" s="41"/>
+      <c r="Q36" s="44"/>
       <c r="R36" s="12" t="s">
         <v>117</v>
       </c>
@@ -4045,7 +4045,7 @@
       <c r="T36" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="U36" s="37"/>
+      <c r="U36" s="44"/>
       <c r="V36" s="12" t="s">
         <v>116</v>
       </c>
@@ -4083,11 +4083,11 @@
       <c r="H37" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I37" s="47"/>
+      <c r="I37" s="41"/>
       <c r="J37" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K37" s="37"/>
+      <c r="K37" s="44"/>
       <c r="L37" s="12" t="s">
         <v>117</v>
       </c>
@@ -4100,8 +4100,8 @@
       <c r="O37" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="P37" s="47"/>
-      <c r="Q37" s="37"/>
+      <c r="P37" s="41"/>
+      <c r="Q37" s="44"/>
       <c r="R37" s="12" t="s">
         <v>117</v>
       </c>
@@ -4111,7 +4111,7 @@
       <c r="T37" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="U37" s="37"/>
+      <c r="U37" s="44"/>
       <c r="V37" s="12" t="s">
         <v>116</v>
       </c>
@@ -4143,19 +4143,19 @@
       <c r="F38" s="12"/>
       <c r="G38" s="12"/>
       <c r="H38" s="12"/>
-      <c r="I38" s="47"/>
+      <c r="I38" s="41"/>
       <c r="J38" s="12"/>
-      <c r="K38" s="37"/>
+      <c r="K38" s="44"/>
       <c r="L38" s="12"/>
       <c r="M38" s="12"/>
       <c r="N38" s="12"/>
       <c r="O38" s="12"/>
-      <c r="P38" s="47"/>
-      <c r="Q38" s="37"/>
+      <c r="P38" s="41"/>
+      <c r="Q38" s="44"/>
       <c r="R38" s="12"/>
       <c r="S38" s="12"/>
       <c r="T38" s="12"/>
-      <c r="U38" s="37"/>
+      <c r="U38" s="44"/>
       <c r="V38" s="12"/>
       <c r="W38" s="5">
         <f t="shared" si="1"/>
@@ -4185,19 +4185,19 @@
       <c r="F39" s="12"/>
       <c r="G39" s="12"/>
       <c r="H39" s="12"/>
-      <c r="I39" s="47"/>
+      <c r="I39" s="41"/>
       <c r="J39" s="12"/>
-      <c r="K39" s="37"/>
+      <c r="K39" s="44"/>
       <c r="L39" s="12"/>
       <c r="M39" s="12"/>
       <c r="N39" s="12"/>
       <c r="O39" s="12"/>
-      <c r="P39" s="47"/>
-      <c r="Q39" s="37"/>
+      <c r="P39" s="41"/>
+      <c r="Q39" s="44"/>
       <c r="R39" s="12"/>
       <c r="S39" s="12"/>
       <c r="T39" s="12"/>
-      <c r="U39" s="37"/>
+      <c r="U39" s="44"/>
       <c r="V39" s="12"/>
       <c r="W39" s="5">
         <f t="shared" si="1"/>
@@ -4227,9 +4227,9 @@
       <c r="F40" s="12"/>
       <c r="G40" s="12"/>
       <c r="H40" s="12"/>
-      <c r="I40" s="47"/>
+      <c r="I40" s="41"/>
       <c r="J40" s="12"/>
-      <c r="K40" s="37"/>
+      <c r="K40" s="44"/>
       <c r="L40" s="12"/>
       <c r="M40" s="12"/>
       <c r="N40" s="12" t="s">
@@ -4238,8 +4238,8 @@
       <c r="O40" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P40" s="47"/>
-      <c r="Q40" s="37"/>
+      <c r="P40" s="41"/>
+      <c r="Q40" s="44"/>
       <c r="R40" s="12" t="s">
         <v>116</v>
       </c>
@@ -4249,7 +4249,7 @@
       <c r="T40" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="U40" s="37"/>
+      <c r="U40" s="44"/>
       <c r="V40" s="12" t="s">
         <v>116</v>
       </c>
@@ -4279,9 +4279,9 @@
       <c r="F41" s="12"/>
       <c r="G41" s="12"/>
       <c r="H41" s="12"/>
-      <c r="I41" s="47"/>
+      <c r="I41" s="41"/>
       <c r="J41" s="12"/>
-      <c r="K41" s="37"/>
+      <c r="K41" s="44"/>
       <c r="L41" s="12"/>
       <c r="M41" s="12"/>
       <c r="N41" s="12" t="s">
@@ -4290,8 +4290,8 @@
       <c r="O41" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P41" s="47"/>
-      <c r="Q41" s="37"/>
+      <c r="P41" s="41"/>
+      <c r="Q41" s="44"/>
       <c r="R41" s="12" t="s">
         <v>116</v>
       </c>
@@ -4301,7 +4301,7 @@
       <c r="T41" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="U41" s="37"/>
+      <c r="U41" s="44"/>
       <c r="V41" s="12" t="s">
         <v>116</v>
       </c>
@@ -4339,11 +4339,11 @@
       <c r="H42" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I42" s="47"/>
+      <c r="I42" s="41"/>
       <c r="J42" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K42" s="37"/>
+      <c r="K42" s="44"/>
       <c r="L42" s="12" t="s">
         <v>117</v>
       </c>
@@ -4356,8 +4356,8 @@
       <c r="O42" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P42" s="47"/>
-      <c r="Q42" s="37"/>
+      <c r="P42" s="41"/>
+      <c r="Q42" s="44"/>
       <c r="R42" s="12" t="s">
         <v>117</v>
       </c>
@@ -4367,7 +4367,7 @@
       <c r="T42" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="U42" s="37"/>
+      <c r="U42" s="44"/>
       <c r="V42" s="12" t="s">
         <v>116</v>
       </c>
@@ -4405,11 +4405,11 @@
       <c r="H43" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I43" s="47"/>
+      <c r="I43" s="41"/>
       <c r="J43" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K43" s="37"/>
+      <c r="K43" s="44"/>
       <c r="L43" s="12" t="s">
         <v>117</v>
       </c>
@@ -4422,8 +4422,8 @@
       <c r="O43" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="P43" s="47"/>
-      <c r="Q43" s="37"/>
+      <c r="P43" s="41"/>
+      <c r="Q43" s="44"/>
       <c r="R43" s="12" t="s">
         <v>117</v>
       </c>
@@ -4433,7 +4433,7 @@
       <c r="T43" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="U43" s="37"/>
+      <c r="U43" s="44"/>
       <c r="V43" s="12" t="s">
         <v>116</v>
       </c>
@@ -4471,11 +4471,11 @@
       <c r="H44" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I44" s="47"/>
+      <c r="I44" s="41"/>
       <c r="J44" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K44" s="37"/>
+      <c r="K44" s="44"/>
       <c r="L44" s="12" t="s">
         <v>117</v>
       </c>
@@ -4488,8 +4488,8 @@
       <c r="O44" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="P44" s="47"/>
-      <c r="Q44" s="37"/>
+      <c r="P44" s="41"/>
+      <c r="Q44" s="44"/>
       <c r="R44" s="12" t="s">
         <v>117</v>
       </c>
@@ -4499,7 +4499,7 @@
       <c r="T44" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="U44" s="37"/>
+      <c r="U44" s="44"/>
       <c r="V44" s="12" t="s">
         <v>116</v>
       </c>
@@ -4531,19 +4531,19 @@
       <c r="F45" s="12"/>
       <c r="G45" s="12"/>
       <c r="H45" s="12"/>
-      <c r="I45" s="47"/>
+      <c r="I45" s="41"/>
       <c r="J45" s="12"/>
-      <c r="K45" s="37"/>
+      <c r="K45" s="44"/>
       <c r="L45" s="12"/>
       <c r="M45" s="12"/>
       <c r="N45" s="12"/>
       <c r="O45" s="12"/>
-      <c r="P45" s="47"/>
-      <c r="Q45" s="37"/>
+      <c r="P45" s="41"/>
+      <c r="Q45" s="44"/>
       <c r="R45" s="12"/>
       <c r="S45" s="12"/>
       <c r="T45" s="12"/>
-      <c r="U45" s="37"/>
+      <c r="U45" s="44"/>
       <c r="V45" s="12"/>
       <c r="W45" s="5">
         <f t="shared" si="1"/>
@@ -4579,11 +4579,11 @@
       <c r="H46" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I46" s="47"/>
+      <c r="I46" s="41"/>
       <c r="J46" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K46" s="37"/>
+      <c r="K46" s="44"/>
       <c r="L46" s="12" t="s">
         <v>117</v>
       </c>
@@ -4596,8 +4596,8 @@
       <c r="O46" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P46" s="47"/>
-      <c r="Q46" s="37"/>
+      <c r="P46" s="41"/>
+      <c r="Q46" s="44"/>
       <c r="R46" s="12" t="s">
         <v>117</v>
       </c>
@@ -4607,7 +4607,7 @@
       <c r="T46" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="U46" s="37"/>
+      <c r="U46" s="44"/>
       <c r="V46" s="12" t="s">
         <v>116</v>
       </c>
@@ -4637,11 +4637,11 @@
       <c r="F47" s="12"/>
       <c r="G47" s="12"/>
       <c r="H47" s="12"/>
-      <c r="I47" s="47"/>
+      <c r="I47" s="41"/>
       <c r="J47" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K47" s="37"/>
+      <c r="K47" s="44"/>
       <c r="L47" s="12" t="s">
         <v>117</v>
       </c>
@@ -4654,8 +4654,8 @@
       <c r="O47" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P47" s="47"/>
-      <c r="Q47" s="37"/>
+      <c r="P47" s="41"/>
+      <c r="Q47" s="44"/>
       <c r="R47" s="12" t="s">
         <v>117</v>
       </c>
@@ -4665,7 +4665,7 @@
       <c r="T47" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="U47" s="37"/>
+      <c r="U47" s="44"/>
       <c r="V47" s="12" t="s">
         <v>116</v>
       </c>
@@ -4703,11 +4703,11 @@
       <c r="H48" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I48" s="47"/>
+      <c r="I48" s="41"/>
       <c r="J48" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K48" s="37"/>
+      <c r="K48" s="44"/>
       <c r="L48" s="12" t="s">
         <v>117</v>
       </c>
@@ -4720,8 +4720,8 @@
       <c r="O48" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P48" s="47"/>
-      <c r="Q48" s="37"/>
+      <c r="P48" s="41"/>
+      <c r="Q48" s="44"/>
       <c r="R48" s="12" t="s">
         <v>117</v>
       </c>
@@ -4731,7 +4731,7 @@
       <c r="T48" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="U48" s="37"/>
+      <c r="U48" s="44"/>
       <c r="V48" s="12" t="s">
         <v>116</v>
       </c>
@@ -4761,19 +4761,19 @@
       <c r="F49" s="12"/>
       <c r="G49" s="12"/>
       <c r="H49" s="12"/>
-      <c r="I49" s="47"/>
+      <c r="I49" s="41"/>
       <c r="J49" s="12"/>
-      <c r="K49" s="37"/>
+      <c r="K49" s="44"/>
       <c r="L49" s="12"/>
       <c r="M49" s="12"/>
       <c r="N49" s="12"/>
       <c r="O49" s="12"/>
-      <c r="P49" s="47"/>
-      <c r="Q49" s="37"/>
+      <c r="P49" s="41"/>
+      <c r="Q49" s="44"/>
       <c r="R49" s="12"/>
       <c r="S49" s="12"/>
       <c r="T49" s="12"/>
-      <c r="U49" s="37"/>
+      <c r="U49" s="44"/>
       <c r="V49" s="12"/>
       <c r="W49" s="5">
         <f t="shared" si="1"/>
@@ -4801,19 +4801,19 @@
       <c r="F50" s="29"/>
       <c r="G50" s="29"/>
       <c r="H50" s="29"/>
-      <c r="I50" s="47"/>
+      <c r="I50" s="41"/>
       <c r="J50" s="29"/>
-      <c r="K50" s="37"/>
+      <c r="K50" s="44"/>
       <c r="L50" s="29"/>
       <c r="M50" s="29"/>
       <c r="N50" s="29"/>
       <c r="O50" s="29"/>
-      <c r="P50" s="47"/>
-      <c r="Q50" s="37"/>
+      <c r="P50" s="41"/>
+      <c r="Q50" s="44"/>
       <c r="R50" s="29"/>
       <c r="S50" s="29"/>
       <c r="T50" s="29"/>
-      <c r="U50" s="37"/>
+      <c r="U50" s="44"/>
       <c r="V50" s="29"/>
       <c r="W50" s="30">
         <f t="shared" si="1"/>
@@ -4841,19 +4841,19 @@
       <c r="F51" s="31"/>
       <c r="G51" s="31"/>
       <c r="H51" s="31"/>
-      <c r="I51" s="47"/>
+      <c r="I51" s="41"/>
       <c r="J51" s="31"/>
-      <c r="K51" s="37"/>
+      <c r="K51" s="44"/>
       <c r="L51" s="31"/>
       <c r="M51" s="31"/>
       <c r="N51" s="31"/>
       <c r="O51" s="31"/>
-      <c r="P51" s="47"/>
-      <c r="Q51" s="37"/>
+      <c r="P51" s="41"/>
+      <c r="Q51" s="44"/>
       <c r="R51" s="31"/>
       <c r="S51" s="31"/>
       <c r="T51" s="31"/>
-      <c r="U51" s="37"/>
+      <c r="U51" s="44"/>
       <c r="V51" s="31"/>
       <c r="W51" s="30">
         <f t="shared" si="1"/>
@@ -4881,19 +4881,19 @@
       <c r="F52" s="31"/>
       <c r="G52" s="31"/>
       <c r="H52" s="31"/>
-      <c r="I52" s="48"/>
+      <c r="I52" s="42"/>
       <c r="J52" s="31"/>
-      <c r="K52" s="38"/>
+      <c r="K52" s="45"/>
       <c r="L52" s="31"/>
       <c r="M52" s="31"/>
       <c r="N52" s="31"/>
       <c r="O52" s="31"/>
-      <c r="P52" s="48"/>
-      <c r="Q52" s="38"/>
+      <c r="P52" s="42"/>
+      <c r="Q52" s="45"/>
       <c r="R52" s="31"/>
       <c r="S52" s="31"/>
       <c r="T52" s="31"/>
-      <c r="U52" s="38"/>
+      <c r="U52" s="45"/>
       <c r="V52" s="31"/>
       <c r="W52" s="5">
         <f t="shared" si="1"/>
@@ -4906,6 +4906,8 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:X1"/>
+    <mergeCell ref="A2:X2"/>
     <mergeCell ref="Y3:Z3"/>
     <mergeCell ref="Y8:AB8"/>
     <mergeCell ref="A3:A4"/>
@@ -4921,8 +4923,6 @@
     <mergeCell ref="X3:X4"/>
     <mergeCell ref="U5:U52"/>
     <mergeCell ref="Q5:Q52"/>
-    <mergeCell ref="A1:X1"/>
-    <mergeCell ref="A2:X2"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:Q5 U5 R5:T50 V5:V50 F6:H50 J6:J50 L6:O50 F4:V4">
     <cfRule type="expression" dxfId="56" priority="15">
@@ -5027,102 +5027,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="39"/>
-      <c r="U1" s="39"/>
-      <c r="V1" s="39"/>
-      <c r="W1" s="39"/>
-      <c r="X1" s="39"/>
-      <c r="Y1" s="39"/>
-      <c r="Z1" s="39"/>
-      <c r="AA1" s="39"/>
-      <c r="AB1" s="39"/>
-      <c r="AC1" s="39"/>
-      <c r="AD1" s="39"/>
-      <c r="AE1" s="39"/>
-      <c r="AF1" s="39"/>
-      <c r="AG1" s="39"/>
-      <c r="AH1" s="39"/>
-      <c r="AI1" s="39"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="47"/>
+      <c r="AA1" s="47"/>
+      <c r="AB1" s="47"/>
+      <c r="AC1" s="47"/>
+      <c r="AD1" s="47"/>
+      <c r="AE1" s="47"/>
+      <c r="AF1" s="47"/>
+      <c r="AG1" s="47"/>
+      <c r="AH1" s="47"/>
+      <c r="AI1" s="47"/>
       <c r="AJ1" s="32"/>
       <c r="AK1" s="32"/>
     </row>
     <row r="2" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="48" t="s">
         <v>124</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="40"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="40"/>
-      <c r="U2" s="40"/>
-      <c r="V2" s="40"/>
-      <c r="W2" s="40"/>
-      <c r="X2" s="40"/>
-      <c r="Y2" s="40"/>
-      <c r="Z2" s="40"/>
-      <c r="AA2" s="40"/>
-      <c r="AB2" s="40"/>
-      <c r="AC2" s="40"/>
-      <c r="AD2" s="40"/>
-      <c r="AE2" s="40"/>
-      <c r="AF2" s="40"/>
-      <c r="AG2" s="40"/>
-      <c r="AH2" s="40"/>
-      <c r="AI2" s="40"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
+      <c r="W2" s="48"/>
+      <c r="X2" s="48"/>
+      <c r="Y2" s="48"/>
+      <c r="Z2" s="48"/>
+      <c r="AA2" s="48"/>
+      <c r="AB2" s="48"/>
+      <c r="AC2" s="48"/>
+      <c r="AD2" s="48"/>
+      <c r="AE2" s="48"/>
+      <c r="AF2" s="48"/>
+      <c r="AG2" s="48"/>
+      <c r="AH2" s="48"/>
+      <c r="AI2" s="48"/>
       <c r="AJ2" s="33"/>
       <c r="AK2" s="33"/>
       <c r="AL2" s="33"/>
     </row>
     <row r="3" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="E3" s="38" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -5245,25 +5245,25 @@
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="AJ3" s="35" t="s">
+      <c r="AJ3" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="AK3" s="35" t="s">
+      <c r="AK3" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="41" t="s">
+      <c r="AL3" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="AM3" s="42"/>
+      <c r="AM3" s="36"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
     </row>
     <row r="4" spans="1:41" ht="36" x14ac:dyDescent="0.25">
-      <c r="A4" s="45"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
       <c r="F4" s="23">
         <v>45536</v>
       </c>
@@ -5354,8 +5354,8 @@
       <c r="AI4" s="23">
         <v>45565</v>
       </c>
-      <c r="AJ4" s="35"/>
-      <c r="AK4" s="35"/>
+      <c r="AJ4" s="46"/>
+      <c r="AK4" s="46"/>
       <c r="AL4" s="4" t="s">
         <v>7</v>
       </c>
@@ -5808,12 +5808,12 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="AL8" s="41" t="s">
+      <c r="AL8" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="AM8" s="43"/>
-      <c r="AN8" s="43"/>
-      <c r="AO8" s="42"/>
+      <c r="AM8" s="37"/>
+      <c r="AN8" s="37"/>
+      <c r="AO8" s="36"/>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
@@ -6713,12 +6713,12 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AL16" s="41" t="s">
+      <c r="AL16" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="AM16" s="43"/>
-      <c r="AN16" s="43"/>
-      <c r="AO16" s="42"/>
+      <c r="AM16" s="37"/>
+      <c r="AN16" s="37"/>
+      <c r="AO16" s="36"/>
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
@@ -10408,13 +10408,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:AI1"/>
-    <mergeCell ref="A2:AI2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="AJ3:AJ4"/>
     <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="AL3:AM3"/>
@@ -10425,6 +10418,13 @@
     <mergeCell ref="AH5:AH53"/>
     <mergeCell ref="AL8:AO8"/>
     <mergeCell ref="AL16:AO16"/>
+    <mergeCell ref="A1:AI1"/>
+    <mergeCell ref="A2:AI2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
   </mergeCells>
   <conditionalFormatting sqref="F5 M5 T5 AA5:AH5 G5:L50 N5:S50 U5:Z50 AI5:AI53 AB6:AG50 AB51:AE51 AF51:AG52 AC52:AE52 AC53:AG53 F4:AI4">
     <cfRule type="expression" dxfId="46" priority="8">
@@ -10530,86 +10530,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="39"/>
-      <c r="U1" s="39"/>
-      <c r="V1" s="39"/>
-      <c r="W1" s="39"/>
-      <c r="X1" s="39"/>
-      <c r="Y1" s="39"/>
-      <c r="Z1" s="39"/>
-      <c r="AA1" s="39"/>
-      <c r="AB1" s="39"/>
-      <c r="AC1" s="39"/>
-      <c r="AD1" s="39"/>
-      <c r="AE1" s="39"/>
-      <c r="AF1" s="39"/>
-      <c r="AG1" s="39"/>
-      <c r="AH1" s="39"/>
-      <c r="AI1" s="39"/>
-      <c r="AJ1" s="39"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="47"/>
+      <c r="AA1" s="47"/>
+      <c r="AB1" s="47"/>
+      <c r="AC1" s="47"/>
+      <c r="AD1" s="47"/>
+      <c r="AE1" s="47"/>
+      <c r="AF1" s="47"/>
+      <c r="AG1" s="47"/>
+      <c r="AH1" s="47"/>
+      <c r="AI1" s="47"/>
+      <c r="AJ1" s="47"/>
       <c r="AK1" s="32"/>
       <c r="AL1" s="32"/>
     </row>
     <row r="2" spans="1:42" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="40"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="40"/>
-      <c r="U2" s="40"/>
-      <c r="V2" s="40"/>
-      <c r="W2" s="40"/>
-      <c r="X2" s="40"/>
-      <c r="Y2" s="40"/>
-      <c r="Z2" s="40"/>
-      <c r="AA2" s="40"/>
-      <c r="AB2" s="40"/>
-      <c r="AC2" s="40"/>
-      <c r="AD2" s="40"/>
-      <c r="AE2" s="40"/>
-      <c r="AF2" s="40"/>
-      <c r="AG2" s="40"/>
-      <c r="AH2" s="40"/>
-      <c r="AI2" s="40"/>
-      <c r="AJ2" s="40"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
+      <c r="W2" s="48"/>
+      <c r="X2" s="48"/>
+      <c r="Y2" s="48"/>
+      <c r="Z2" s="48"/>
+      <c r="AA2" s="48"/>
+      <c r="AB2" s="48"/>
+      <c r="AC2" s="48"/>
+      <c r="AD2" s="48"/>
+      <c r="AE2" s="48"/>
+      <c r="AF2" s="48"/>
+      <c r="AG2" s="48"/>
+      <c r="AH2" s="48"/>
+      <c r="AI2" s="48"/>
+      <c r="AJ2" s="48"/>
       <c r="AK2" s="33"/>
       <c r="AL2" s="33"/>
       <c r="AM2" s="33"/>
@@ -10754,16 +10754,16 @@
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="AK3" s="35" t="s">
+      <c r="AK3" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="AL3" s="35" t="s">
+      <c r="AL3" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="AM3" s="41" t="s">
+      <c r="AM3" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="AN3" s="42"/>
+      <c r="AN3" s="36"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
     </row>
@@ -10866,8 +10866,8 @@
       <c r="AJ4" s="23">
         <v>45596</v>
       </c>
-      <c r="AK4" s="35"/>
-      <c r="AL4" s="35"/>
+      <c r="AK4" s="46"/>
+      <c r="AL4" s="46"/>
       <c r="AM4" s="4" t="s">
         <v>7</v>
       </c>
@@ -11340,12 +11340,12 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AM8" s="41" t="s">
+      <c r="AM8" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="AN8" s="43"/>
-      <c r="AO8" s="43"/>
-      <c r="AP8" s="42"/>
+      <c r="AN8" s="37"/>
+      <c r="AO8" s="37"/>
+      <c r="AP8" s="36"/>
     </row>
     <row r="9" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="13">
@@ -12293,12 +12293,12 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="AM16" s="41" t="s">
+      <c r="AM16" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="AN16" s="43"/>
-      <c r="AO16" s="43"/>
-      <c r="AP16" s="42"/>
+      <c r="AN16" s="37"/>
+      <c r="AO16" s="37"/>
+      <c r="AP16" s="36"/>
     </row>
     <row r="17" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="13">
@@ -16715,13 +16715,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:AJ1"/>
-    <mergeCell ref="A2:AJ2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="AL3:AL4"/>
     <mergeCell ref="AM3:AN3"/>
@@ -16731,6 +16724,13 @@
     <mergeCell ref="AF5:AF56"/>
     <mergeCell ref="AM8:AP8"/>
     <mergeCell ref="AM16:AP16"/>
+    <mergeCell ref="A1:AJ1"/>
+    <mergeCell ref="A2:AJ2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:AJ5 F6:J56 L6:Q56 S6:X56 Z6:AE56 AG6:AJ56 AM4:AN4">
     <cfRule type="expression" dxfId="36" priority="9">
@@ -16833,84 +16833,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="39"/>
-      <c r="U1" s="39"/>
-      <c r="V1" s="39"/>
-      <c r="W1" s="39"/>
-      <c r="X1" s="39"/>
-      <c r="Y1" s="39"/>
-      <c r="Z1" s="39"/>
-      <c r="AA1" s="39"/>
-      <c r="AB1" s="39"/>
-      <c r="AC1" s="39"/>
-      <c r="AD1" s="39"/>
-      <c r="AE1" s="39"/>
-      <c r="AF1" s="39"/>
-      <c r="AG1" s="39"/>
-      <c r="AH1" s="39"/>
-      <c r="AI1" s="39"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="47"/>
+      <c r="AA1" s="47"/>
+      <c r="AB1" s="47"/>
+      <c r="AC1" s="47"/>
+      <c r="AD1" s="47"/>
+      <c r="AE1" s="47"/>
+      <c r="AF1" s="47"/>
+      <c r="AG1" s="47"/>
+      <c r="AH1" s="47"/>
+      <c r="AI1" s="47"/>
       <c r="AJ1" s="32"/>
       <c r="AK1" s="32"/>
     </row>
     <row r="2" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="48" t="s">
         <v>133</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="40"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="40"/>
-      <c r="U2" s="40"/>
-      <c r="V2" s="40"/>
-      <c r="W2" s="40"/>
-      <c r="X2" s="40"/>
-      <c r="Y2" s="40"/>
-      <c r="Z2" s="40"/>
-      <c r="AA2" s="40"/>
-      <c r="AB2" s="40"/>
-      <c r="AC2" s="40"/>
-      <c r="AD2" s="40"/>
-      <c r="AE2" s="40"/>
-      <c r="AF2" s="40"/>
-      <c r="AG2" s="40"/>
-      <c r="AH2" s="40"/>
-      <c r="AI2" s="40"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
+      <c r="W2" s="48"/>
+      <c r="X2" s="48"/>
+      <c r="Y2" s="48"/>
+      <c r="Z2" s="48"/>
+      <c r="AA2" s="48"/>
+      <c r="AB2" s="48"/>
+      <c r="AC2" s="48"/>
+      <c r="AD2" s="48"/>
+      <c r="AE2" s="48"/>
+      <c r="AF2" s="48"/>
+      <c r="AG2" s="48"/>
+      <c r="AH2" s="48"/>
+      <c r="AI2" s="48"/>
       <c r="AJ2" s="33"/>
       <c r="AK2" s="33"/>
       <c r="AL2" s="33"/>
@@ -17051,16 +17051,16 @@
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="AJ3" s="35" t="s">
+      <c r="AJ3" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="AK3" s="35" t="s">
+      <c r="AK3" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="41" t="s">
+      <c r="AL3" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="AM3" s="42"/>
+      <c r="AM3" s="36"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
     </row>
@@ -17160,8 +17160,8 @@
       <c r="AI4" s="23">
         <v>45626</v>
       </c>
-      <c r="AJ4" s="35"/>
-      <c r="AK4" s="35"/>
+      <c r="AJ4" s="46"/>
+      <c r="AK4" s="46"/>
       <c r="AL4" s="4" t="s">
         <v>7</v>
       </c>
@@ -17610,12 +17610,12 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="AL8" s="41" t="s">
+      <c r="AL8" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="AM8" s="43"/>
-      <c r="AN8" s="43"/>
-      <c r="AO8" s="42"/>
+      <c r="AM8" s="37"/>
+      <c r="AN8" s="37"/>
+      <c r="AO8" s="36"/>
     </row>
     <row r="9" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="13">
@@ -18507,12 +18507,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AL16" s="41" t="s">
+      <c r="AL16" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="AM16" s="43"/>
-      <c r="AN16" s="43"/>
-      <c r="AO16" s="42"/>
+      <c r="AM16" s="37"/>
+      <c r="AN16" s="37"/>
+      <c r="AO16" s="36"/>
     </row>
     <row r="17" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="13">
@@ -22871,6 +22871,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="AL8:AO8"/>
+    <mergeCell ref="AL16:AO16"/>
+    <mergeCell ref="AJ3:AJ4"/>
+    <mergeCell ref="AK3:AK4"/>
+    <mergeCell ref="AL3:AM3"/>
     <mergeCell ref="AC5:AC58"/>
     <mergeCell ref="A1:AI1"/>
     <mergeCell ref="A2:AI2"/>
@@ -22884,11 +22889,6 @@
     <mergeCell ref="O5:O58"/>
     <mergeCell ref="T5:T58"/>
     <mergeCell ref="V5:V58"/>
-    <mergeCell ref="AL8:AO8"/>
-    <mergeCell ref="AL16:AO16"/>
-    <mergeCell ref="AJ3:AJ4"/>
-    <mergeCell ref="AK3:AK4"/>
-    <mergeCell ref="AL3:AM3"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:AI5 F6:G58 I6:M58 P6:S58 U6:U58 W6:AB58 AD6:AI58 AL4:AM4">
     <cfRule type="expression" dxfId="26" priority="10">
@@ -22991,84 +22991,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="39"/>
-      <c r="U1" s="39"/>
-      <c r="V1" s="39"/>
-      <c r="W1" s="39"/>
-      <c r="X1" s="39"/>
-      <c r="Y1" s="39"/>
-      <c r="Z1" s="39"/>
-      <c r="AA1" s="39"/>
-      <c r="AB1" s="39"/>
-      <c r="AC1" s="39"/>
-      <c r="AD1" s="39"/>
-      <c r="AE1" s="39"/>
-      <c r="AF1" s="39"/>
-      <c r="AG1" s="39"/>
-      <c r="AH1" s="39"/>
-      <c r="AI1" s="39"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="47"/>
+      <c r="AA1" s="47"/>
+      <c r="AB1" s="47"/>
+      <c r="AC1" s="47"/>
+      <c r="AD1" s="47"/>
+      <c r="AE1" s="47"/>
+      <c r="AF1" s="47"/>
+      <c r="AG1" s="47"/>
+      <c r="AH1" s="47"/>
+      <c r="AI1" s="47"/>
       <c r="AJ1" s="32"/>
       <c r="AK1" s="32"/>
     </row>
     <row r="2" spans="1:38" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="48" t="s">
         <v>133</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="40"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="40"/>
-      <c r="U2" s="40"/>
-      <c r="V2" s="40"/>
-      <c r="W2" s="40"/>
-      <c r="X2" s="40"/>
-      <c r="Y2" s="40"/>
-      <c r="Z2" s="40"/>
-      <c r="AA2" s="40"/>
-      <c r="AB2" s="40"/>
-      <c r="AC2" s="40"/>
-      <c r="AD2" s="40"/>
-      <c r="AE2" s="40"/>
-      <c r="AF2" s="40"/>
-      <c r="AG2" s="40"/>
-      <c r="AH2" s="40"/>
-      <c r="AI2" s="40"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
+      <c r="W2" s="48"/>
+      <c r="X2" s="48"/>
+      <c r="Y2" s="48"/>
+      <c r="Z2" s="48"/>
+      <c r="AA2" s="48"/>
+      <c r="AB2" s="48"/>
+      <c r="AC2" s="48"/>
+      <c r="AD2" s="48"/>
+      <c r="AE2" s="48"/>
+      <c r="AF2" s="48"/>
+      <c r="AG2" s="48"/>
+      <c r="AH2" s="48"/>
+      <c r="AI2" s="48"/>
       <c r="AJ2" s="33"/>
       <c r="AK2" s="33"/>
     </row>
@@ -23212,7 +23212,7 @@
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="AK3" s="35" t="s">
+      <c r="AK3" s="46" t="s">
         <v>5</v>
       </c>
       <c r="AL3" s="53" t="s">
@@ -23318,7 +23318,7 @@
       <c r="AJ4" s="23">
         <v>45657</v>
       </c>
-      <c r="AK4" s="35"/>
+      <c r="AK4" s="46"/>
       <c r="AL4" s="54"/>
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23335,7 +23335,7 @@
       <c r="E5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="46" t="s">
+      <c r="F5" s="40" t="s">
         <v>141</v>
       </c>
       <c r="G5" s="34" t="s">
@@ -23356,7 +23356,7 @@
       <c r="L5" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M5" s="46" t="s">
+      <c r="M5" s="40" t="s">
         <v>141</v>
       </c>
       <c r="N5" s="34" t="s">
@@ -23377,7 +23377,7 @@
       <c r="S5" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="T5" s="46" t="s">
+      <c r="T5" s="40" t="s">
         <v>141</v>
       </c>
       <c r="U5" s="34" t="s">
@@ -23395,37 +23395,37 @@
       <c r="Y5" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="Z5" s="36" t="s">
+      <c r="Z5" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="AA5" s="46" t="s">
+      <c r="AA5" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="AB5" s="36" t="s">
+      <c r="AB5" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="AC5" s="36" t="s">
+      <c r="AC5" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="AD5" s="36" t="s">
+      <c r="AD5" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="AE5" s="36" t="s">
+      <c r="AE5" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="AF5" s="36" t="s">
+      <c r="AF5" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="AG5" s="36" t="s">
+      <c r="AG5" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="AH5" s="46" t="s">
+      <c r="AH5" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="AI5" s="36" t="s">
+      <c r="AI5" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="AJ5" s="36" t="s">
+      <c r="AJ5" s="43" t="s">
         <v>142</v>
       </c>
       <c r="AK5" s="5">
@@ -23453,7 +23453,7 @@
       <c r="E6" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="47"/>
+      <c r="F6" s="41"/>
       <c r="G6" s="34" t="s">
         <v>117</v>
       </c>
@@ -23472,7 +23472,7 @@
       <c r="L6" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M6" s="47"/>
+      <c r="M6" s="41"/>
       <c r="N6" s="34" t="s">
         <v>117</v>
       </c>
@@ -23491,7 +23491,7 @@
       <c r="S6" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="T6" s="47"/>
+      <c r="T6" s="41"/>
       <c r="U6" s="34" t="s">
         <v>117</v>
       </c>
@@ -23507,17 +23507,17 @@
       <c r="Y6" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Z6" s="37"/>
-      <c r="AA6" s="47"/>
-      <c r="AB6" s="37"/>
-      <c r="AC6" s="37"/>
-      <c r="AD6" s="37"/>
-      <c r="AE6" s="37"/>
-      <c r="AF6" s="37"/>
-      <c r="AG6" s="37"/>
-      <c r="AH6" s="47"/>
-      <c r="AI6" s="37"/>
-      <c r="AJ6" s="37"/>
+      <c r="Z6" s="44"/>
+      <c r="AA6" s="41"/>
+      <c r="AB6" s="44"/>
+      <c r="AC6" s="44"/>
+      <c r="AD6" s="44"/>
+      <c r="AE6" s="44"/>
+      <c r="AF6" s="44"/>
+      <c r="AG6" s="44"/>
+      <c r="AH6" s="41"/>
+      <c r="AI6" s="44"/>
+      <c r="AJ6" s="44"/>
       <c r="AK6" s="5">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -23543,7 +23543,7 @@
       <c r="E7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="47"/>
+      <c r="F7" s="41"/>
       <c r="G7" s="34" t="s">
         <v>117</v>
       </c>
@@ -23562,7 +23562,7 @@
       <c r="L7" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="M7" s="47"/>
+      <c r="M7" s="41"/>
       <c r="N7" s="34" t="s">
         <v>117</v>
       </c>
@@ -23581,7 +23581,7 @@
       <c r="S7" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T7" s="47"/>
+      <c r="T7" s="41"/>
       <c r="U7" s="34" t="s">
         <v>117</v>
       </c>
@@ -23597,17 +23597,17 @@
       <c r="Y7" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Z7" s="37"/>
-      <c r="AA7" s="47"/>
-      <c r="AB7" s="37"/>
-      <c r="AC7" s="37"/>
-      <c r="AD7" s="37"/>
-      <c r="AE7" s="37"/>
-      <c r="AF7" s="37"/>
-      <c r="AG7" s="37"/>
-      <c r="AH7" s="47"/>
-      <c r="AI7" s="37"/>
-      <c r="AJ7" s="37"/>
+      <c r="Z7" s="44"/>
+      <c r="AA7" s="41"/>
+      <c r="AB7" s="44"/>
+      <c r="AC7" s="44"/>
+      <c r="AD7" s="44"/>
+      <c r="AE7" s="44"/>
+      <c r="AF7" s="44"/>
+      <c r="AG7" s="44"/>
+      <c r="AH7" s="41"/>
+      <c r="AI7" s="44"/>
+      <c r="AJ7" s="44"/>
       <c r="AK7" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -23631,7 +23631,7 @@
       <c r="E8" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="47"/>
+      <c r="F8" s="41"/>
       <c r="G8" s="34" t="s">
         <v>117</v>
       </c>
@@ -23650,7 +23650,7 @@
       <c r="L8" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M8" s="47"/>
+      <c r="M8" s="41"/>
       <c r="N8" s="34" t="s">
         <v>116</v>
       </c>
@@ -23669,7 +23669,7 @@
       <c r="S8" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T8" s="47"/>
+      <c r="T8" s="41"/>
       <c r="U8" s="34" t="s">
         <v>117</v>
       </c>
@@ -23685,17 +23685,17 @@
       <c r="Y8" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z8" s="37"/>
-      <c r="AA8" s="47"/>
-      <c r="AB8" s="37"/>
-      <c r="AC8" s="37"/>
-      <c r="AD8" s="37"/>
-      <c r="AE8" s="37"/>
-      <c r="AF8" s="37"/>
-      <c r="AG8" s="37"/>
-      <c r="AH8" s="47"/>
-      <c r="AI8" s="37"/>
-      <c r="AJ8" s="37"/>
+      <c r="Z8" s="44"/>
+      <c r="AA8" s="41"/>
+      <c r="AB8" s="44"/>
+      <c r="AC8" s="44"/>
+      <c r="AD8" s="44"/>
+      <c r="AE8" s="44"/>
+      <c r="AF8" s="44"/>
+      <c r="AG8" s="44"/>
+      <c r="AH8" s="41"/>
+      <c r="AI8" s="44"/>
+      <c r="AJ8" s="44"/>
       <c r="AK8" s="5">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -23721,7 +23721,7 @@
       <c r="E9" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="47"/>
+      <c r="F9" s="41"/>
       <c r="G9" s="34" t="s">
         <v>117</v>
       </c>
@@ -23740,7 +23740,7 @@
       <c r="L9" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M9" s="47"/>
+      <c r="M9" s="41"/>
       <c r="N9" s="34" t="s">
         <v>117</v>
       </c>
@@ -23759,7 +23759,7 @@
       <c r="S9" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T9" s="47"/>
+      <c r="T9" s="41"/>
       <c r="U9" s="34" t="s">
         <v>117</v>
       </c>
@@ -23775,17 +23775,17 @@
       <c r="Y9" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Z9" s="37"/>
-      <c r="AA9" s="47"/>
-      <c r="AB9" s="37"/>
-      <c r="AC9" s="37"/>
-      <c r="AD9" s="37"/>
-      <c r="AE9" s="37"/>
-      <c r="AF9" s="37"/>
-      <c r="AG9" s="37"/>
-      <c r="AH9" s="47"/>
-      <c r="AI9" s="37"/>
-      <c r="AJ9" s="37"/>
+      <c r="Z9" s="44"/>
+      <c r="AA9" s="41"/>
+      <c r="AB9" s="44"/>
+      <c r="AC9" s="44"/>
+      <c r="AD9" s="44"/>
+      <c r="AE9" s="44"/>
+      <c r="AF9" s="44"/>
+      <c r="AG9" s="44"/>
+      <c r="AH9" s="41"/>
+      <c r="AI9" s="44"/>
+      <c r="AJ9" s="44"/>
       <c r="AK9" s="5">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -23811,7 +23811,7 @@
       <c r="E10" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="47"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="34" t="s">
         <v>117</v>
       </c>
@@ -23830,7 +23830,7 @@
       <c r="L10" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="M10" s="47"/>
+      <c r="M10" s="41"/>
       <c r="N10" s="34" t="s">
         <v>116</v>
       </c>
@@ -23849,7 +23849,7 @@
       <c r="S10" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T10" s="47"/>
+      <c r="T10" s="41"/>
       <c r="U10" s="34" t="s">
         <v>117</v>
       </c>
@@ -23865,17 +23865,17 @@
       <c r="Y10" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z10" s="37"/>
-      <c r="AA10" s="47"/>
-      <c r="AB10" s="37"/>
-      <c r="AC10" s="37"/>
-      <c r="AD10" s="37"/>
-      <c r="AE10" s="37"/>
-      <c r="AF10" s="37"/>
-      <c r="AG10" s="37"/>
-      <c r="AH10" s="47"/>
-      <c r="AI10" s="37"/>
-      <c r="AJ10" s="37"/>
+      <c r="Z10" s="44"/>
+      <c r="AA10" s="41"/>
+      <c r="AB10" s="44"/>
+      <c r="AC10" s="44"/>
+      <c r="AD10" s="44"/>
+      <c r="AE10" s="44"/>
+      <c r="AF10" s="44"/>
+      <c r="AG10" s="44"/>
+      <c r="AH10" s="41"/>
+      <c r="AI10" s="44"/>
+      <c r="AJ10" s="44"/>
       <c r="AK10" s="5">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -23901,7 +23901,7 @@
       <c r="E11" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="47"/>
+      <c r="F11" s="41"/>
       <c r="G11" s="34" t="s">
         <v>116</v>
       </c>
@@ -23920,7 +23920,7 @@
       <c r="L11" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="M11" s="47"/>
+      <c r="M11" s="41"/>
       <c r="N11" s="34" t="s">
         <v>117</v>
       </c>
@@ -23939,7 +23939,7 @@
       <c r="S11" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="T11" s="47"/>
+      <c r="T11" s="41"/>
       <c r="U11" s="34" t="s">
         <v>117</v>
       </c>
@@ -23955,17 +23955,17 @@
       <c r="Y11" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Z11" s="37"/>
-      <c r="AA11" s="47"/>
-      <c r="AB11" s="37"/>
-      <c r="AC11" s="37"/>
-      <c r="AD11" s="37"/>
-      <c r="AE11" s="37"/>
-      <c r="AF11" s="37"/>
-      <c r="AG11" s="37"/>
-      <c r="AH11" s="47"/>
-      <c r="AI11" s="37"/>
-      <c r="AJ11" s="37"/>
+      <c r="Z11" s="44"/>
+      <c r="AA11" s="41"/>
+      <c r="AB11" s="44"/>
+      <c r="AC11" s="44"/>
+      <c r="AD11" s="44"/>
+      <c r="AE11" s="44"/>
+      <c r="AF11" s="44"/>
+      <c r="AG11" s="44"/>
+      <c r="AH11" s="41"/>
+      <c r="AI11" s="44"/>
+      <c r="AJ11" s="44"/>
       <c r="AK11" s="5">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -23991,7 +23991,7 @@
       <c r="E12" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="47"/>
+      <c r="F12" s="41"/>
       <c r="G12" s="34" t="s">
         <v>117</v>
       </c>
@@ -24010,7 +24010,7 @@
       <c r="L12" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M12" s="47"/>
+      <c r="M12" s="41"/>
       <c r="N12" s="34" t="s">
         <v>117</v>
       </c>
@@ -24029,7 +24029,7 @@
       <c r="S12" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T12" s="47"/>
+      <c r="T12" s="41"/>
       <c r="U12" s="34" t="s">
         <v>117</v>
       </c>
@@ -24045,17 +24045,17 @@
       <c r="Y12" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z12" s="37"/>
-      <c r="AA12" s="47"/>
-      <c r="AB12" s="37"/>
-      <c r="AC12" s="37"/>
-      <c r="AD12" s="37"/>
-      <c r="AE12" s="37"/>
-      <c r="AF12" s="37"/>
-      <c r="AG12" s="37"/>
-      <c r="AH12" s="47"/>
-      <c r="AI12" s="37"/>
-      <c r="AJ12" s="37"/>
+      <c r="Z12" s="44"/>
+      <c r="AA12" s="41"/>
+      <c r="AB12" s="44"/>
+      <c r="AC12" s="44"/>
+      <c r="AD12" s="44"/>
+      <c r="AE12" s="44"/>
+      <c r="AF12" s="44"/>
+      <c r="AG12" s="44"/>
+      <c r="AH12" s="41"/>
+      <c r="AI12" s="44"/>
+      <c r="AJ12" s="44"/>
       <c r="AK12" s="5">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -24081,7 +24081,7 @@
       <c r="E13" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="47"/>
+      <c r="F13" s="41"/>
       <c r="G13" s="34" t="s">
         <v>117</v>
       </c>
@@ -24100,7 +24100,7 @@
       <c r="L13" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M13" s="47"/>
+      <c r="M13" s="41"/>
       <c r="N13" s="34" t="s">
         <v>117</v>
       </c>
@@ -24119,7 +24119,7 @@
       <c r="S13" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T13" s="47"/>
+      <c r="T13" s="41"/>
       <c r="U13" s="34" t="s">
         <v>117</v>
       </c>
@@ -24135,17 +24135,17 @@
       <c r="Y13" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Z13" s="37"/>
-      <c r="AA13" s="47"/>
-      <c r="AB13" s="37"/>
-      <c r="AC13" s="37"/>
-      <c r="AD13" s="37"/>
-      <c r="AE13" s="37"/>
-      <c r="AF13" s="37"/>
-      <c r="AG13" s="37"/>
-      <c r="AH13" s="47"/>
-      <c r="AI13" s="37"/>
-      <c r="AJ13" s="37"/>
+      <c r="Z13" s="44"/>
+      <c r="AA13" s="41"/>
+      <c r="AB13" s="44"/>
+      <c r="AC13" s="44"/>
+      <c r="AD13" s="44"/>
+      <c r="AE13" s="44"/>
+      <c r="AF13" s="44"/>
+      <c r="AG13" s="44"/>
+      <c r="AH13" s="41"/>
+      <c r="AI13" s="44"/>
+      <c r="AJ13" s="44"/>
       <c r="AK13" s="5">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -24171,7 +24171,7 @@
       <c r="E14" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="47"/>
+      <c r="F14" s="41"/>
       <c r="G14" s="34" t="s">
         <v>117</v>
       </c>
@@ -24190,7 +24190,7 @@
       <c r="L14" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M14" s="47"/>
+      <c r="M14" s="41"/>
       <c r="N14" s="34" t="s">
         <v>117</v>
       </c>
@@ -24209,7 +24209,7 @@
       <c r="S14" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T14" s="47"/>
+      <c r="T14" s="41"/>
       <c r="U14" s="34" t="s">
         <v>117</v>
       </c>
@@ -24225,17 +24225,17 @@
       <c r="Y14" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z14" s="37"/>
-      <c r="AA14" s="47"/>
-      <c r="AB14" s="37"/>
-      <c r="AC14" s="37"/>
-      <c r="AD14" s="37"/>
-      <c r="AE14" s="37"/>
-      <c r="AF14" s="37"/>
-      <c r="AG14" s="37"/>
-      <c r="AH14" s="47"/>
-      <c r="AI14" s="37"/>
-      <c r="AJ14" s="37"/>
+      <c r="Z14" s="44"/>
+      <c r="AA14" s="41"/>
+      <c r="AB14" s="44"/>
+      <c r="AC14" s="44"/>
+      <c r="AD14" s="44"/>
+      <c r="AE14" s="44"/>
+      <c r="AF14" s="44"/>
+      <c r="AG14" s="44"/>
+      <c r="AH14" s="41"/>
+      <c r="AI14" s="44"/>
+      <c r="AJ14" s="44"/>
       <c r="AK14" s="5">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -24261,7 +24261,7 @@
       <c r="E15" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="47"/>
+      <c r="F15" s="41"/>
       <c r="G15" s="34" t="s">
         <v>116</v>
       </c>
@@ -24280,7 +24280,7 @@
       <c r="L15" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M15" s="47"/>
+      <c r="M15" s="41"/>
       <c r="N15" s="34" t="s">
         <v>116</v>
       </c>
@@ -24299,7 +24299,7 @@
       <c r="S15" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="T15" s="47"/>
+      <c r="T15" s="41"/>
       <c r="U15" s="34" t="s">
         <v>116</v>
       </c>
@@ -24315,17 +24315,17 @@
       <c r="Y15" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z15" s="37"/>
-      <c r="AA15" s="47"/>
-      <c r="AB15" s="37"/>
-      <c r="AC15" s="37"/>
-      <c r="AD15" s="37"/>
-      <c r="AE15" s="37"/>
-      <c r="AF15" s="37"/>
-      <c r="AG15" s="37"/>
-      <c r="AH15" s="47"/>
-      <c r="AI15" s="37"/>
-      <c r="AJ15" s="37"/>
+      <c r="Z15" s="44"/>
+      <c r="AA15" s="41"/>
+      <c r="AB15" s="44"/>
+      <c r="AC15" s="44"/>
+      <c r="AD15" s="44"/>
+      <c r="AE15" s="44"/>
+      <c r="AF15" s="44"/>
+      <c r="AG15" s="44"/>
+      <c r="AH15" s="41"/>
+      <c r="AI15" s="44"/>
+      <c r="AJ15" s="44"/>
       <c r="AK15" s="5">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -24351,7 +24351,7 @@
       <c r="E16" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="47"/>
+      <c r="F16" s="41"/>
       <c r="G16" s="34" t="s">
         <v>117</v>
       </c>
@@ -24368,7 +24368,7 @@
       <c r="L16" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="M16" s="47"/>
+      <c r="M16" s="41"/>
       <c r="N16" s="34" t="s">
         <v>116</v>
       </c>
@@ -24387,7 +24387,7 @@
       <c r="S16" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T16" s="47"/>
+      <c r="T16" s="41"/>
       <c r="U16" s="34" t="s">
         <v>117</v>
       </c>
@@ -24403,17 +24403,17 @@
       <c r="Y16" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Z16" s="37"/>
-      <c r="AA16" s="47"/>
-      <c r="AB16" s="37"/>
-      <c r="AC16" s="37"/>
-      <c r="AD16" s="37"/>
-      <c r="AE16" s="37"/>
-      <c r="AF16" s="37"/>
-      <c r="AG16" s="37"/>
-      <c r="AH16" s="47"/>
-      <c r="AI16" s="37"/>
-      <c r="AJ16" s="37"/>
+      <c r="Z16" s="44"/>
+      <c r="AA16" s="41"/>
+      <c r="AB16" s="44"/>
+      <c r="AC16" s="44"/>
+      <c r="AD16" s="44"/>
+      <c r="AE16" s="44"/>
+      <c r="AF16" s="44"/>
+      <c r="AG16" s="44"/>
+      <c r="AH16" s="41"/>
+      <c r="AI16" s="44"/>
+      <c r="AJ16" s="44"/>
       <c r="AK16" s="5">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -24439,7 +24439,7 @@
       <c r="E17" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="47"/>
+      <c r="F17" s="41"/>
       <c r="G17" s="34" t="s">
         <v>117</v>
       </c>
@@ -24458,7 +24458,7 @@
       <c r="L17" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="M17" s="47"/>
+      <c r="M17" s="41"/>
       <c r="N17" s="34" t="s">
         <v>117</v>
       </c>
@@ -24477,7 +24477,7 @@
       <c r="S17" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T17" s="47"/>
+      <c r="T17" s="41"/>
       <c r="U17" s="34" t="s">
         <v>117</v>
       </c>
@@ -24493,17 +24493,17 @@
       <c r="Y17" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z17" s="37"/>
-      <c r="AA17" s="47"/>
-      <c r="AB17" s="37"/>
-      <c r="AC17" s="37"/>
-      <c r="AD17" s="37"/>
-      <c r="AE17" s="37"/>
-      <c r="AF17" s="37"/>
-      <c r="AG17" s="37"/>
-      <c r="AH17" s="47"/>
-      <c r="AI17" s="37"/>
-      <c r="AJ17" s="37"/>
+      <c r="Z17" s="44"/>
+      <c r="AA17" s="41"/>
+      <c r="AB17" s="44"/>
+      <c r="AC17" s="44"/>
+      <c r="AD17" s="44"/>
+      <c r="AE17" s="44"/>
+      <c r="AF17" s="44"/>
+      <c r="AG17" s="44"/>
+      <c r="AH17" s="41"/>
+      <c r="AI17" s="44"/>
+      <c r="AJ17" s="44"/>
       <c r="AK17" s="5">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -24529,7 +24529,7 @@
       <c r="E18" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="47"/>
+      <c r="F18" s="41"/>
       <c r="G18" s="34" t="s">
         <v>120</v>
       </c>
@@ -24548,7 +24548,7 @@
       <c r="L18" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="M18" s="47"/>
+      <c r="M18" s="41"/>
       <c r="N18" s="34" t="s">
         <v>117</v>
       </c>
@@ -24567,7 +24567,7 @@
       <c r="S18" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T18" s="47"/>
+      <c r="T18" s="41"/>
       <c r="U18" s="34" t="s">
         <v>117</v>
       </c>
@@ -24583,17 +24583,17 @@
       <c r="Y18" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z18" s="37"/>
-      <c r="AA18" s="47"/>
-      <c r="AB18" s="37"/>
-      <c r="AC18" s="37"/>
-      <c r="AD18" s="37"/>
-      <c r="AE18" s="37"/>
-      <c r="AF18" s="37"/>
-      <c r="AG18" s="37"/>
-      <c r="AH18" s="47"/>
-      <c r="AI18" s="37"/>
-      <c r="AJ18" s="37"/>
+      <c r="Z18" s="44"/>
+      <c r="AA18" s="41"/>
+      <c r="AB18" s="44"/>
+      <c r="AC18" s="44"/>
+      <c r="AD18" s="44"/>
+      <c r="AE18" s="44"/>
+      <c r="AF18" s="44"/>
+      <c r="AG18" s="44"/>
+      <c r="AH18" s="41"/>
+      <c r="AI18" s="44"/>
+      <c r="AJ18" s="44"/>
       <c r="AK18" s="5">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -24619,7 +24619,7 @@
       <c r="E19" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F19" s="47"/>
+      <c r="F19" s="41"/>
       <c r="G19" s="34" t="s">
         <v>117</v>
       </c>
@@ -24638,7 +24638,7 @@
       <c r="L19" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="M19" s="47"/>
+      <c r="M19" s="41"/>
       <c r="N19" s="34" t="s">
         <v>117</v>
       </c>
@@ -24657,7 +24657,7 @@
       <c r="S19" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T19" s="47"/>
+      <c r="T19" s="41"/>
       <c r="U19" s="34" t="s">
         <v>117</v>
       </c>
@@ -24673,17 +24673,17 @@
       <c r="Y19" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Z19" s="37"/>
-      <c r="AA19" s="47"/>
-      <c r="AB19" s="37"/>
-      <c r="AC19" s="37"/>
-      <c r="AD19" s="37"/>
-      <c r="AE19" s="37"/>
-      <c r="AF19" s="37"/>
-      <c r="AG19" s="37"/>
-      <c r="AH19" s="47"/>
-      <c r="AI19" s="37"/>
-      <c r="AJ19" s="37"/>
+      <c r="Z19" s="44"/>
+      <c r="AA19" s="41"/>
+      <c r="AB19" s="44"/>
+      <c r="AC19" s="44"/>
+      <c r="AD19" s="44"/>
+      <c r="AE19" s="44"/>
+      <c r="AF19" s="44"/>
+      <c r="AG19" s="44"/>
+      <c r="AH19" s="41"/>
+      <c r="AI19" s="44"/>
+      <c r="AJ19" s="44"/>
       <c r="AK19" s="5">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -24709,7 +24709,7 @@
       <c r="E20" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="47"/>
+      <c r="F20" s="41"/>
       <c r="G20" s="34" t="s">
         <v>117</v>
       </c>
@@ -24728,7 +24728,7 @@
       <c r="L20" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M20" s="47"/>
+      <c r="M20" s="41"/>
       <c r="N20" s="34" t="s">
         <v>117</v>
       </c>
@@ -24747,7 +24747,7 @@
       <c r="S20" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T20" s="47"/>
+      <c r="T20" s="41"/>
       <c r="U20" s="34" t="s">
         <v>117</v>
       </c>
@@ -24763,17 +24763,17 @@
       <c r="Y20" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z20" s="37"/>
-      <c r="AA20" s="47"/>
-      <c r="AB20" s="37"/>
-      <c r="AC20" s="37"/>
-      <c r="AD20" s="37"/>
-      <c r="AE20" s="37"/>
-      <c r="AF20" s="37"/>
-      <c r="AG20" s="37"/>
-      <c r="AH20" s="47"/>
-      <c r="AI20" s="37"/>
-      <c r="AJ20" s="37"/>
+      <c r="Z20" s="44"/>
+      <c r="AA20" s="41"/>
+      <c r="AB20" s="44"/>
+      <c r="AC20" s="44"/>
+      <c r="AD20" s="44"/>
+      <c r="AE20" s="44"/>
+      <c r="AF20" s="44"/>
+      <c r="AG20" s="44"/>
+      <c r="AH20" s="41"/>
+      <c r="AI20" s="44"/>
+      <c r="AJ20" s="44"/>
       <c r="AK20" s="5">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -24799,7 +24799,7 @@
       <c r="E21" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="47"/>
+      <c r="F21" s="41"/>
       <c r="G21" s="34" t="s">
         <v>116</v>
       </c>
@@ -24818,7 +24818,7 @@
       <c r="L21" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M21" s="47"/>
+      <c r="M21" s="41"/>
       <c r="N21" s="34" t="s">
         <v>116</v>
       </c>
@@ -24837,7 +24837,7 @@
       <c r="S21" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="T21" s="47"/>
+      <c r="T21" s="41"/>
       <c r="U21" s="34" t="s">
         <v>116</v>
       </c>
@@ -24853,17 +24853,17 @@
       <c r="Y21" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z21" s="37"/>
-      <c r="AA21" s="47"/>
-      <c r="AB21" s="37"/>
-      <c r="AC21" s="37"/>
-      <c r="AD21" s="37"/>
-      <c r="AE21" s="37"/>
-      <c r="AF21" s="37"/>
-      <c r="AG21" s="37"/>
-      <c r="AH21" s="47"/>
-      <c r="AI21" s="37"/>
-      <c r="AJ21" s="37"/>
+      <c r="Z21" s="44"/>
+      <c r="AA21" s="41"/>
+      <c r="AB21" s="44"/>
+      <c r="AC21" s="44"/>
+      <c r="AD21" s="44"/>
+      <c r="AE21" s="44"/>
+      <c r="AF21" s="44"/>
+      <c r="AG21" s="44"/>
+      <c r="AH21" s="41"/>
+      <c r="AI21" s="44"/>
+      <c r="AJ21" s="44"/>
       <c r="AK21" s="5">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -24889,7 +24889,7 @@
       <c r="E22" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="47"/>
+      <c r="F22" s="41"/>
       <c r="G22" s="34" t="s">
         <v>117</v>
       </c>
@@ -24908,7 +24908,7 @@
       <c r="L22" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M22" s="47"/>
+      <c r="M22" s="41"/>
       <c r="N22" s="34" t="s">
         <v>117</v>
       </c>
@@ -24927,7 +24927,7 @@
       <c r="S22" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T22" s="47"/>
+      <c r="T22" s="41"/>
       <c r="U22" s="34" t="s">
         <v>117</v>
       </c>
@@ -24943,17 +24943,17 @@
       <c r="Y22" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z22" s="37"/>
-      <c r="AA22" s="47"/>
-      <c r="AB22" s="37"/>
-      <c r="AC22" s="37"/>
-      <c r="AD22" s="37"/>
-      <c r="AE22" s="37"/>
-      <c r="AF22" s="37"/>
-      <c r="AG22" s="37"/>
-      <c r="AH22" s="47"/>
-      <c r="AI22" s="37"/>
-      <c r="AJ22" s="37"/>
+      <c r="Z22" s="44"/>
+      <c r="AA22" s="41"/>
+      <c r="AB22" s="44"/>
+      <c r="AC22" s="44"/>
+      <c r="AD22" s="44"/>
+      <c r="AE22" s="44"/>
+      <c r="AF22" s="44"/>
+      <c r="AG22" s="44"/>
+      <c r="AH22" s="41"/>
+      <c r="AI22" s="44"/>
+      <c r="AJ22" s="44"/>
       <c r="AK22" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -24979,7 +24979,7 @@
       <c r="E23" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="47"/>
+      <c r="F23" s="41"/>
       <c r="G23" s="34" t="s">
         <v>117</v>
       </c>
@@ -24998,7 +24998,7 @@
       <c r="L23" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M23" s="47"/>
+      <c r="M23" s="41"/>
       <c r="N23" s="34" t="s">
         <v>117</v>
       </c>
@@ -25017,7 +25017,7 @@
       <c r="S23" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T23" s="47"/>
+      <c r="T23" s="41"/>
       <c r="U23" s="34" t="s">
         <v>117</v>
       </c>
@@ -25033,17 +25033,17 @@
       <c r="Y23" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z23" s="37"/>
-      <c r="AA23" s="47"/>
-      <c r="AB23" s="37"/>
-      <c r="AC23" s="37"/>
-      <c r="AD23" s="37"/>
-      <c r="AE23" s="37"/>
-      <c r="AF23" s="37"/>
-      <c r="AG23" s="37"/>
-      <c r="AH23" s="47"/>
-      <c r="AI23" s="37"/>
-      <c r="AJ23" s="37"/>
+      <c r="Z23" s="44"/>
+      <c r="AA23" s="41"/>
+      <c r="AB23" s="44"/>
+      <c r="AC23" s="44"/>
+      <c r="AD23" s="44"/>
+      <c r="AE23" s="44"/>
+      <c r="AF23" s="44"/>
+      <c r="AG23" s="44"/>
+      <c r="AH23" s="41"/>
+      <c r="AI23" s="44"/>
+      <c r="AJ23" s="44"/>
       <c r="AK23" s="5">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -25067,7 +25067,7 @@
       <c r="E24" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="47"/>
+      <c r="F24" s="41"/>
       <c r="G24" s="34" t="s">
         <v>117</v>
       </c>
@@ -25086,7 +25086,7 @@
       <c r="L24" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M24" s="47"/>
+      <c r="M24" s="41"/>
       <c r="N24" s="34" t="s">
         <v>117</v>
       </c>
@@ -25105,7 +25105,7 @@
       <c r="S24" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T24" s="47"/>
+      <c r="T24" s="41"/>
       <c r="U24" s="34" t="s">
         <v>117</v>
       </c>
@@ -25121,17 +25121,17 @@
       <c r="Y24" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Z24" s="37"/>
-      <c r="AA24" s="47"/>
-      <c r="AB24" s="37"/>
-      <c r="AC24" s="37"/>
-      <c r="AD24" s="37"/>
-      <c r="AE24" s="37"/>
-      <c r="AF24" s="37"/>
-      <c r="AG24" s="37"/>
-      <c r="AH24" s="47"/>
-      <c r="AI24" s="37"/>
-      <c r="AJ24" s="37"/>
+      <c r="Z24" s="44"/>
+      <c r="AA24" s="41"/>
+      <c r="AB24" s="44"/>
+      <c r="AC24" s="44"/>
+      <c r="AD24" s="44"/>
+      <c r="AE24" s="44"/>
+      <c r="AF24" s="44"/>
+      <c r="AG24" s="44"/>
+      <c r="AH24" s="41"/>
+      <c r="AI24" s="44"/>
+      <c r="AJ24" s="44"/>
       <c r="AK24" s="5">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -25157,7 +25157,7 @@
       <c r="E25" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="47"/>
+      <c r="F25" s="41"/>
       <c r="G25" s="34" t="s">
         <v>117</v>
       </c>
@@ -25176,7 +25176,7 @@
       <c r="L25" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M25" s="47"/>
+      <c r="M25" s="41"/>
       <c r="N25" s="34" t="s">
         <v>117</v>
       </c>
@@ -25195,7 +25195,7 @@
       <c r="S25" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="T25" s="47"/>
+      <c r="T25" s="41"/>
       <c r="U25" s="34" t="s">
         <v>117</v>
       </c>
@@ -25211,17 +25211,17 @@
       <c r="Y25" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z25" s="37"/>
-      <c r="AA25" s="47"/>
-      <c r="AB25" s="37"/>
-      <c r="AC25" s="37"/>
-      <c r="AD25" s="37"/>
-      <c r="AE25" s="37"/>
-      <c r="AF25" s="37"/>
-      <c r="AG25" s="37"/>
-      <c r="AH25" s="47"/>
-      <c r="AI25" s="37"/>
-      <c r="AJ25" s="37"/>
+      <c r="Z25" s="44"/>
+      <c r="AA25" s="41"/>
+      <c r="AB25" s="44"/>
+      <c r="AC25" s="44"/>
+      <c r="AD25" s="44"/>
+      <c r="AE25" s="44"/>
+      <c r="AF25" s="44"/>
+      <c r="AG25" s="44"/>
+      <c r="AH25" s="41"/>
+      <c r="AI25" s="44"/>
+      <c r="AJ25" s="44"/>
       <c r="AK25" s="5">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -25245,7 +25245,7 @@
       <c r="E26" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="47"/>
+      <c r="F26" s="41"/>
       <c r="G26" s="34" t="s">
         <v>116</v>
       </c>
@@ -25264,7 +25264,7 @@
       <c r="L26" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M26" s="47"/>
+      <c r="M26" s="41"/>
       <c r="N26" s="34" t="s">
         <v>117</v>
       </c>
@@ -25283,7 +25283,7 @@
       <c r="S26" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T26" s="47"/>
+      <c r="T26" s="41"/>
       <c r="U26" s="34" t="s">
         <v>117</v>
       </c>
@@ -25299,17 +25299,17 @@
       <c r="Y26" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z26" s="37"/>
-      <c r="AA26" s="47"/>
-      <c r="AB26" s="37"/>
-      <c r="AC26" s="37"/>
-      <c r="AD26" s="37"/>
-      <c r="AE26" s="37"/>
-      <c r="AF26" s="37"/>
-      <c r="AG26" s="37"/>
-      <c r="AH26" s="47"/>
-      <c r="AI26" s="37"/>
-      <c r="AJ26" s="37"/>
+      <c r="Z26" s="44"/>
+      <c r="AA26" s="41"/>
+      <c r="AB26" s="44"/>
+      <c r="AC26" s="44"/>
+      <c r="AD26" s="44"/>
+      <c r="AE26" s="44"/>
+      <c r="AF26" s="44"/>
+      <c r="AG26" s="44"/>
+      <c r="AH26" s="41"/>
+      <c r="AI26" s="44"/>
+      <c r="AJ26" s="44"/>
       <c r="AK26" s="5">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -25331,7 +25331,7 @@
       <c r="E27" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="47"/>
+      <c r="F27" s="41"/>
       <c r="G27" s="34" t="s">
         <v>116</v>
       </c>
@@ -25350,7 +25350,7 @@
       <c r="L27" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M27" s="47"/>
+      <c r="M27" s="41"/>
       <c r="N27" s="34" t="s">
         <v>116</v>
       </c>
@@ -25369,7 +25369,7 @@
       <c r="S27" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="T27" s="47"/>
+      <c r="T27" s="41"/>
       <c r="U27" s="34" t="s">
         <v>116</v>
       </c>
@@ -25385,17 +25385,17 @@
       <c r="Y27" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Z27" s="37"/>
-      <c r="AA27" s="47"/>
-      <c r="AB27" s="37"/>
-      <c r="AC27" s="37"/>
-      <c r="AD27" s="37"/>
-      <c r="AE27" s="37"/>
-      <c r="AF27" s="37"/>
-      <c r="AG27" s="37"/>
-      <c r="AH27" s="47"/>
-      <c r="AI27" s="37"/>
-      <c r="AJ27" s="37"/>
+      <c r="Z27" s="44"/>
+      <c r="AA27" s="41"/>
+      <c r="AB27" s="44"/>
+      <c r="AC27" s="44"/>
+      <c r="AD27" s="44"/>
+      <c r="AE27" s="44"/>
+      <c r="AF27" s="44"/>
+      <c r="AG27" s="44"/>
+      <c r="AH27" s="41"/>
+      <c r="AI27" s="44"/>
+      <c r="AJ27" s="44"/>
       <c r="AK27" s="5">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -25419,7 +25419,7 @@
       <c r="E28" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="47"/>
+      <c r="F28" s="41"/>
       <c r="G28" s="34" t="s">
         <v>117</v>
       </c>
@@ -25438,7 +25438,7 @@
       <c r="L28" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="M28" s="47"/>
+      <c r="M28" s="41"/>
       <c r="N28" s="34" t="s">
         <v>117</v>
       </c>
@@ -25457,7 +25457,7 @@
       <c r="S28" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T28" s="47"/>
+      <c r="T28" s="41"/>
       <c r="U28" s="34" t="s">
         <v>117</v>
       </c>
@@ -25473,17 +25473,17 @@
       <c r="Y28" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z28" s="37"/>
-      <c r="AA28" s="47"/>
-      <c r="AB28" s="37"/>
-      <c r="AC28" s="37"/>
-      <c r="AD28" s="37"/>
-      <c r="AE28" s="37"/>
-      <c r="AF28" s="37"/>
-      <c r="AG28" s="37"/>
-      <c r="AH28" s="47"/>
-      <c r="AI28" s="37"/>
-      <c r="AJ28" s="37"/>
+      <c r="Z28" s="44"/>
+      <c r="AA28" s="41"/>
+      <c r="AB28" s="44"/>
+      <c r="AC28" s="44"/>
+      <c r="AD28" s="44"/>
+      <c r="AE28" s="44"/>
+      <c r="AF28" s="44"/>
+      <c r="AG28" s="44"/>
+      <c r="AH28" s="41"/>
+      <c r="AI28" s="44"/>
+      <c r="AJ28" s="44"/>
       <c r="AK28" s="5">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -25505,7 +25505,7 @@
       <c r="E29" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="47"/>
+      <c r="F29" s="41"/>
       <c r="G29" s="34" t="s">
         <v>117</v>
       </c>
@@ -25524,7 +25524,7 @@
       <c r="L29" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M29" s="47"/>
+      <c r="M29" s="41"/>
       <c r="N29" s="34" t="s">
         <v>116</v>
       </c>
@@ -25543,7 +25543,7 @@
       <c r="S29" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T29" s="47"/>
+      <c r="T29" s="41"/>
       <c r="U29" s="34" t="s">
         <v>116</v>
       </c>
@@ -25559,17 +25559,17 @@
       <c r="Y29" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Z29" s="37"/>
-      <c r="AA29" s="47"/>
-      <c r="AB29" s="37"/>
-      <c r="AC29" s="37"/>
-      <c r="AD29" s="37"/>
-      <c r="AE29" s="37"/>
-      <c r="AF29" s="37"/>
-      <c r="AG29" s="37"/>
-      <c r="AH29" s="47"/>
-      <c r="AI29" s="37"/>
-      <c r="AJ29" s="37"/>
+      <c r="Z29" s="44"/>
+      <c r="AA29" s="41"/>
+      <c r="AB29" s="44"/>
+      <c r="AC29" s="44"/>
+      <c r="AD29" s="44"/>
+      <c r="AE29" s="44"/>
+      <c r="AF29" s="44"/>
+      <c r="AG29" s="44"/>
+      <c r="AH29" s="41"/>
+      <c r="AI29" s="44"/>
+      <c r="AJ29" s="44"/>
       <c r="AK29" s="5">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -25593,7 +25593,7 @@
       <c r="E30" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F30" s="47"/>
+      <c r="F30" s="41"/>
       <c r="G30" s="34" t="s">
         <v>117</v>
       </c>
@@ -25612,7 +25612,7 @@
       <c r="L30" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="M30" s="47"/>
+      <c r="M30" s="41"/>
       <c r="N30" s="34" t="s">
         <v>117</v>
       </c>
@@ -25631,7 +25631,7 @@
       <c r="S30" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="T30" s="47"/>
+      <c r="T30" s="41"/>
       <c r="U30" s="34" t="s">
         <v>117</v>
       </c>
@@ -25647,17 +25647,17 @@
       <c r="Y30" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Z30" s="37"/>
-      <c r="AA30" s="47"/>
-      <c r="AB30" s="37"/>
-      <c r="AC30" s="37"/>
-      <c r="AD30" s="37"/>
-      <c r="AE30" s="37"/>
-      <c r="AF30" s="37"/>
-      <c r="AG30" s="37"/>
-      <c r="AH30" s="47"/>
-      <c r="AI30" s="37"/>
-      <c r="AJ30" s="37"/>
+      <c r="Z30" s="44"/>
+      <c r="AA30" s="41"/>
+      <c r="AB30" s="44"/>
+      <c r="AC30" s="44"/>
+      <c r="AD30" s="44"/>
+      <c r="AE30" s="44"/>
+      <c r="AF30" s="44"/>
+      <c r="AG30" s="44"/>
+      <c r="AH30" s="41"/>
+      <c r="AI30" s="44"/>
+      <c r="AJ30" s="44"/>
       <c r="AK30" s="5">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -25681,7 +25681,7 @@
       <c r="E31" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F31" s="47"/>
+      <c r="F31" s="41"/>
       <c r="G31" s="34" t="s">
         <v>117</v>
       </c>
@@ -25700,7 +25700,7 @@
       <c r="L31" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M31" s="47"/>
+      <c r="M31" s="41"/>
       <c r="N31" s="34" t="s">
         <v>116</v>
       </c>
@@ -25719,7 +25719,7 @@
       <c r="S31" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="T31" s="47"/>
+      <c r="T31" s="41"/>
       <c r="U31" s="34" t="s">
         <v>120</v>
       </c>
@@ -25735,17 +25735,17 @@
       <c r="Y31" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="Z31" s="37"/>
-      <c r="AA31" s="47"/>
-      <c r="AB31" s="37"/>
-      <c r="AC31" s="37"/>
-      <c r="AD31" s="37"/>
-      <c r="AE31" s="37"/>
-      <c r="AF31" s="37"/>
-      <c r="AG31" s="37"/>
-      <c r="AH31" s="47"/>
-      <c r="AI31" s="37"/>
-      <c r="AJ31" s="37"/>
+      <c r="Z31" s="44"/>
+      <c r="AA31" s="41"/>
+      <c r="AB31" s="44"/>
+      <c r="AC31" s="44"/>
+      <c r="AD31" s="44"/>
+      <c r="AE31" s="44"/>
+      <c r="AF31" s="44"/>
+      <c r="AG31" s="44"/>
+      <c r="AH31" s="41"/>
+      <c r="AI31" s="44"/>
+      <c r="AJ31" s="44"/>
       <c r="AK31" s="5">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -25771,7 +25771,7 @@
       <c r="E32" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="47"/>
+      <c r="F32" s="41"/>
       <c r="G32" s="34" t="s">
         <v>117</v>
       </c>
@@ -25790,7 +25790,7 @@
       <c r="L32" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="M32" s="47"/>
+      <c r="M32" s="41"/>
       <c r="N32" s="34" t="s">
         <v>117</v>
       </c>
@@ -25809,7 +25809,7 @@
       <c r="S32" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T32" s="47"/>
+      <c r="T32" s="41"/>
       <c r="U32" s="34" t="s">
         <v>117</v>
       </c>
@@ -25825,17 +25825,17 @@
       <c r="Y32" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z32" s="37"/>
-      <c r="AA32" s="47"/>
-      <c r="AB32" s="37"/>
-      <c r="AC32" s="37"/>
-      <c r="AD32" s="37"/>
-      <c r="AE32" s="37"/>
-      <c r="AF32" s="37"/>
-      <c r="AG32" s="37"/>
-      <c r="AH32" s="47"/>
-      <c r="AI32" s="37"/>
-      <c r="AJ32" s="37"/>
+      <c r="Z32" s="44"/>
+      <c r="AA32" s="41"/>
+      <c r="AB32" s="44"/>
+      <c r="AC32" s="44"/>
+      <c r="AD32" s="44"/>
+      <c r="AE32" s="44"/>
+      <c r="AF32" s="44"/>
+      <c r="AG32" s="44"/>
+      <c r="AH32" s="41"/>
+      <c r="AI32" s="44"/>
+      <c r="AJ32" s="44"/>
       <c r="AK32" s="5">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -25861,7 +25861,7 @@
       <c r="E33" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F33" s="47"/>
+      <c r="F33" s="41"/>
       <c r="G33" s="34" t="s">
         <v>117</v>
       </c>
@@ -25880,7 +25880,7 @@
       <c r="L33" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M33" s="47"/>
+      <c r="M33" s="41"/>
       <c r="N33" s="34" t="s">
         <v>117</v>
       </c>
@@ -25899,7 +25899,7 @@
       <c r="S33" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="T33" s="47"/>
+      <c r="T33" s="41"/>
       <c r="U33" s="34" t="s">
         <v>116</v>
       </c>
@@ -25915,17 +25915,17 @@
       <c r="Y33" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z33" s="37"/>
-      <c r="AA33" s="47"/>
-      <c r="AB33" s="37"/>
-      <c r="AC33" s="37"/>
-      <c r="AD33" s="37"/>
-      <c r="AE33" s="37"/>
-      <c r="AF33" s="37"/>
-      <c r="AG33" s="37"/>
-      <c r="AH33" s="47"/>
-      <c r="AI33" s="37"/>
-      <c r="AJ33" s="37"/>
+      <c r="Z33" s="44"/>
+      <c r="AA33" s="41"/>
+      <c r="AB33" s="44"/>
+      <c r="AC33" s="44"/>
+      <c r="AD33" s="44"/>
+      <c r="AE33" s="44"/>
+      <c r="AF33" s="44"/>
+      <c r="AG33" s="44"/>
+      <c r="AH33" s="41"/>
+      <c r="AI33" s="44"/>
+      <c r="AJ33" s="44"/>
       <c r="AK33" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -25951,7 +25951,7 @@
       <c r="E34" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F34" s="47"/>
+      <c r="F34" s="41"/>
       <c r="G34" s="34" t="s">
         <v>117</v>
       </c>
@@ -25970,7 +25970,7 @@
       <c r="L34" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M34" s="47"/>
+      <c r="M34" s="41"/>
       <c r="N34" s="34" t="s">
         <v>117</v>
       </c>
@@ -25989,7 +25989,7 @@
       <c r="S34" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T34" s="47"/>
+      <c r="T34" s="41"/>
       <c r="U34" s="34" t="s">
         <v>117</v>
       </c>
@@ -26005,17 +26005,17 @@
       <c r="Y34" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Z34" s="37"/>
-      <c r="AA34" s="47"/>
-      <c r="AB34" s="37"/>
-      <c r="AC34" s="37"/>
-      <c r="AD34" s="37"/>
-      <c r="AE34" s="37"/>
-      <c r="AF34" s="37"/>
-      <c r="AG34" s="37"/>
-      <c r="AH34" s="47"/>
-      <c r="AI34" s="37"/>
-      <c r="AJ34" s="37"/>
+      <c r="Z34" s="44"/>
+      <c r="AA34" s="41"/>
+      <c r="AB34" s="44"/>
+      <c r="AC34" s="44"/>
+      <c r="AD34" s="44"/>
+      <c r="AE34" s="44"/>
+      <c r="AF34" s="44"/>
+      <c r="AG34" s="44"/>
+      <c r="AH34" s="41"/>
+      <c r="AI34" s="44"/>
+      <c r="AJ34" s="44"/>
       <c r="AK34" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -26041,7 +26041,7 @@
       <c r="E35" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F35" s="47"/>
+      <c r="F35" s="41"/>
       <c r="G35" s="34" t="s">
         <v>117</v>
       </c>
@@ -26060,7 +26060,7 @@
       <c r="L35" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="M35" s="47"/>
+      <c r="M35" s="41"/>
       <c r="N35" s="34" t="s">
         <v>117</v>
       </c>
@@ -26079,7 +26079,7 @@
       <c r="S35" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T35" s="47"/>
+      <c r="T35" s="41"/>
       <c r="U35" s="34" t="s">
         <v>117</v>
       </c>
@@ -26095,17 +26095,17 @@
       <c r="Y35" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z35" s="37"/>
-      <c r="AA35" s="47"/>
-      <c r="AB35" s="37"/>
-      <c r="AC35" s="37"/>
-      <c r="AD35" s="37"/>
-      <c r="AE35" s="37"/>
-      <c r="AF35" s="37"/>
-      <c r="AG35" s="37"/>
-      <c r="AH35" s="47"/>
-      <c r="AI35" s="37"/>
-      <c r="AJ35" s="37"/>
+      <c r="Z35" s="44"/>
+      <c r="AA35" s="41"/>
+      <c r="AB35" s="44"/>
+      <c r="AC35" s="44"/>
+      <c r="AD35" s="44"/>
+      <c r="AE35" s="44"/>
+      <c r="AF35" s="44"/>
+      <c r="AG35" s="44"/>
+      <c r="AH35" s="41"/>
+      <c r="AI35" s="44"/>
+      <c r="AJ35" s="44"/>
       <c r="AK35" s="5">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -26131,7 +26131,7 @@
       <c r="E36" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F36" s="47"/>
+      <c r="F36" s="41"/>
       <c r="G36" s="34" t="s">
         <v>117</v>
       </c>
@@ -26150,7 +26150,7 @@
       <c r="L36" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="M36" s="47"/>
+      <c r="M36" s="41"/>
       <c r="N36" s="34" t="s">
         <v>116</v>
       </c>
@@ -26169,7 +26169,7 @@
       <c r="S36" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T36" s="47"/>
+      <c r="T36" s="41"/>
       <c r="U36" s="34" t="s">
         <v>117</v>
       </c>
@@ -26185,17 +26185,17 @@
       <c r="Y36" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Z36" s="37"/>
-      <c r="AA36" s="47"/>
-      <c r="AB36" s="37"/>
-      <c r="AC36" s="37"/>
-      <c r="AD36" s="37"/>
-      <c r="AE36" s="37"/>
-      <c r="AF36" s="37"/>
-      <c r="AG36" s="37"/>
-      <c r="AH36" s="47"/>
-      <c r="AI36" s="37"/>
-      <c r="AJ36" s="37"/>
+      <c r="Z36" s="44"/>
+      <c r="AA36" s="41"/>
+      <c r="AB36" s="44"/>
+      <c r="AC36" s="44"/>
+      <c r="AD36" s="44"/>
+      <c r="AE36" s="44"/>
+      <c r="AF36" s="44"/>
+      <c r="AG36" s="44"/>
+      <c r="AH36" s="41"/>
+      <c r="AI36" s="44"/>
+      <c r="AJ36" s="44"/>
       <c r="AK36" s="5">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -26221,7 +26221,7 @@
       <c r="E37" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F37" s="47"/>
+      <c r="F37" s="41"/>
       <c r="G37" s="34" t="s">
         <v>117</v>
       </c>
@@ -26240,7 +26240,7 @@
       <c r="L37" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="M37" s="47"/>
+      <c r="M37" s="41"/>
       <c r="N37" s="34" t="s">
         <v>117</v>
       </c>
@@ -26259,7 +26259,7 @@
       <c r="S37" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="T37" s="47"/>
+      <c r="T37" s="41"/>
       <c r="U37" s="34" t="s">
         <v>117</v>
       </c>
@@ -26275,17 +26275,17 @@
       <c r="Y37" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z37" s="37"/>
-      <c r="AA37" s="47"/>
-      <c r="AB37" s="37"/>
-      <c r="AC37" s="37"/>
-      <c r="AD37" s="37"/>
-      <c r="AE37" s="37"/>
-      <c r="AF37" s="37"/>
-      <c r="AG37" s="37"/>
-      <c r="AH37" s="47"/>
-      <c r="AI37" s="37"/>
-      <c r="AJ37" s="37"/>
+      <c r="Z37" s="44"/>
+      <c r="AA37" s="41"/>
+      <c r="AB37" s="44"/>
+      <c r="AC37" s="44"/>
+      <c r="AD37" s="44"/>
+      <c r="AE37" s="44"/>
+      <c r="AF37" s="44"/>
+      <c r="AG37" s="44"/>
+      <c r="AH37" s="41"/>
+      <c r="AI37" s="44"/>
+      <c r="AJ37" s="44"/>
       <c r="AK37" s="5">
         <f t="shared" ref="AK37:AK58" si="3">COUNTIF(F37:AJ37,"P")</f>
         <v>14</v>
@@ -26311,7 +26311,7 @@
       <c r="E38" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F38" s="47"/>
+      <c r="F38" s="41"/>
       <c r="G38" s="34" t="s">
         <v>117</v>
       </c>
@@ -26330,7 +26330,7 @@
       <c r="L38" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M38" s="47"/>
+      <c r="M38" s="41"/>
       <c r="N38" s="34" t="s">
         <v>117</v>
       </c>
@@ -26349,7 +26349,7 @@
       <c r="S38" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T38" s="47"/>
+      <c r="T38" s="41"/>
       <c r="U38" s="34" t="s">
         <v>117</v>
       </c>
@@ -26365,17 +26365,17 @@
       <c r="Y38" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z38" s="37"/>
-      <c r="AA38" s="47"/>
-      <c r="AB38" s="37"/>
-      <c r="AC38" s="37"/>
-      <c r="AD38" s="37"/>
-      <c r="AE38" s="37"/>
-      <c r="AF38" s="37"/>
-      <c r="AG38" s="37"/>
-      <c r="AH38" s="47"/>
-      <c r="AI38" s="37"/>
-      <c r="AJ38" s="37"/>
+      <c r="Z38" s="44"/>
+      <c r="AA38" s="41"/>
+      <c r="AB38" s="44"/>
+      <c r="AC38" s="44"/>
+      <c r="AD38" s="44"/>
+      <c r="AE38" s="44"/>
+      <c r="AF38" s="44"/>
+      <c r="AG38" s="44"/>
+      <c r="AH38" s="41"/>
+      <c r="AI38" s="44"/>
+      <c r="AJ38" s="44"/>
       <c r="AK38" s="5">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -26401,7 +26401,7 @@
       <c r="E39" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F39" s="47"/>
+      <c r="F39" s="41"/>
       <c r="G39" s="34" t="s">
         <v>116</v>
       </c>
@@ -26420,7 +26420,7 @@
       <c r="L39" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M39" s="47"/>
+      <c r="M39" s="41"/>
       <c r="N39" s="34" t="s">
         <v>117</v>
       </c>
@@ -26439,7 +26439,7 @@
       <c r="S39" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T39" s="47"/>
+      <c r="T39" s="41"/>
       <c r="U39" s="34" t="s">
         <v>117</v>
       </c>
@@ -26455,17 +26455,17 @@
       <c r="Y39" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z39" s="37"/>
-      <c r="AA39" s="47"/>
-      <c r="AB39" s="37"/>
-      <c r="AC39" s="37"/>
-      <c r="AD39" s="37"/>
-      <c r="AE39" s="37"/>
-      <c r="AF39" s="37"/>
-      <c r="AG39" s="37"/>
-      <c r="AH39" s="47"/>
-      <c r="AI39" s="37"/>
-      <c r="AJ39" s="37"/>
+      <c r="Z39" s="44"/>
+      <c r="AA39" s="41"/>
+      <c r="AB39" s="44"/>
+      <c r="AC39" s="44"/>
+      <c r="AD39" s="44"/>
+      <c r="AE39" s="44"/>
+      <c r="AF39" s="44"/>
+      <c r="AG39" s="44"/>
+      <c r="AH39" s="41"/>
+      <c r="AI39" s="44"/>
+      <c r="AJ39" s="44"/>
       <c r="AK39" s="5">
         <f t="shared" si="3"/>
         <v>14</v>
@@ -26491,7 +26491,7 @@
       <c r="E40" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F40" s="47"/>
+      <c r="F40" s="41"/>
       <c r="G40" s="34" t="s">
         <v>117</v>
       </c>
@@ -26510,7 +26510,7 @@
       <c r="L40" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="M40" s="47"/>
+      <c r="M40" s="41"/>
       <c r="N40" s="34" t="s">
         <v>117</v>
       </c>
@@ -26529,7 +26529,7 @@
       <c r="S40" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T40" s="47"/>
+      <c r="T40" s="41"/>
       <c r="U40" s="34" t="s">
         <v>117</v>
       </c>
@@ -26545,17 +26545,17 @@
       <c r="Y40" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z40" s="37"/>
-      <c r="AA40" s="47"/>
-      <c r="AB40" s="37"/>
-      <c r="AC40" s="37"/>
-      <c r="AD40" s="37"/>
-      <c r="AE40" s="37"/>
-      <c r="AF40" s="37"/>
-      <c r="AG40" s="37"/>
-      <c r="AH40" s="47"/>
-      <c r="AI40" s="37"/>
-      <c r="AJ40" s="37"/>
+      <c r="Z40" s="44"/>
+      <c r="AA40" s="41"/>
+      <c r="AB40" s="44"/>
+      <c r="AC40" s="44"/>
+      <c r="AD40" s="44"/>
+      <c r="AE40" s="44"/>
+      <c r="AF40" s="44"/>
+      <c r="AG40" s="44"/>
+      <c r="AH40" s="41"/>
+      <c r="AI40" s="44"/>
+      <c r="AJ40" s="44"/>
       <c r="AK40" s="5">
         <f t="shared" si="3"/>
         <v>17</v>
@@ -26581,7 +26581,7 @@
       <c r="E41" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F41" s="47"/>
+      <c r="F41" s="41"/>
       <c r="G41" s="34" t="s">
         <v>117</v>
       </c>
@@ -26600,7 +26600,7 @@
       <c r="L41" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M41" s="47"/>
+      <c r="M41" s="41"/>
       <c r="N41" s="34" t="s">
         <v>116</v>
       </c>
@@ -26619,7 +26619,7 @@
       <c r="S41" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="T41" s="47"/>
+      <c r="T41" s="41"/>
       <c r="U41" s="34" t="s">
         <v>116</v>
       </c>
@@ -26635,17 +26635,17 @@
       <c r="Y41" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z41" s="37"/>
-      <c r="AA41" s="47"/>
-      <c r="AB41" s="37"/>
-      <c r="AC41" s="37"/>
-      <c r="AD41" s="37"/>
-      <c r="AE41" s="37"/>
-      <c r="AF41" s="37"/>
-      <c r="AG41" s="37"/>
-      <c r="AH41" s="47"/>
-      <c r="AI41" s="37"/>
-      <c r="AJ41" s="37"/>
+      <c r="Z41" s="44"/>
+      <c r="AA41" s="41"/>
+      <c r="AB41" s="44"/>
+      <c r="AC41" s="44"/>
+      <c r="AD41" s="44"/>
+      <c r="AE41" s="44"/>
+      <c r="AF41" s="44"/>
+      <c r="AG41" s="44"/>
+      <c r="AH41" s="41"/>
+      <c r="AI41" s="44"/>
+      <c r="AJ41" s="44"/>
       <c r="AK41" s="5">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -26671,7 +26671,7 @@
       <c r="E42" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F42" s="47"/>
+      <c r="F42" s="41"/>
       <c r="G42" s="34" t="s">
         <v>117</v>
       </c>
@@ -26690,7 +26690,7 @@
       <c r="L42" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M42" s="47"/>
+      <c r="M42" s="41"/>
       <c r="N42" s="34" t="s">
         <v>117</v>
       </c>
@@ -26709,7 +26709,7 @@
       <c r="S42" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T42" s="47"/>
+      <c r="T42" s="41"/>
       <c r="U42" s="34" t="s">
         <v>117</v>
       </c>
@@ -26725,17 +26725,17 @@
       <c r="Y42" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z42" s="37"/>
-      <c r="AA42" s="47"/>
-      <c r="AB42" s="37"/>
-      <c r="AC42" s="37"/>
-      <c r="AD42" s="37"/>
-      <c r="AE42" s="37"/>
-      <c r="AF42" s="37"/>
-      <c r="AG42" s="37"/>
-      <c r="AH42" s="47"/>
-      <c r="AI42" s="37"/>
-      <c r="AJ42" s="37"/>
+      <c r="Z42" s="44"/>
+      <c r="AA42" s="41"/>
+      <c r="AB42" s="44"/>
+      <c r="AC42" s="44"/>
+      <c r="AD42" s="44"/>
+      <c r="AE42" s="44"/>
+      <c r="AF42" s="44"/>
+      <c r="AG42" s="44"/>
+      <c r="AH42" s="41"/>
+      <c r="AI42" s="44"/>
+      <c r="AJ42" s="44"/>
       <c r="AK42" s="5">
         <f t="shared" si="3"/>
         <v>13</v>
@@ -26761,7 +26761,7 @@
       <c r="E43" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="47"/>
+      <c r="F43" s="41"/>
       <c r="G43" s="34" t="s">
         <v>116</v>
       </c>
@@ -26780,7 +26780,7 @@
       <c r="L43" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M43" s="47"/>
+      <c r="M43" s="41"/>
       <c r="N43" s="34" t="s">
         <v>117</v>
       </c>
@@ -26799,7 +26799,7 @@
       <c r="S43" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="T43" s="47"/>
+      <c r="T43" s="41"/>
       <c r="U43" s="34" t="s">
         <v>120</v>
       </c>
@@ -26815,17 +26815,17 @@
       <c r="Y43" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Z43" s="37"/>
-      <c r="AA43" s="47"/>
-      <c r="AB43" s="37"/>
-      <c r="AC43" s="37"/>
-      <c r="AD43" s="37"/>
-      <c r="AE43" s="37"/>
-      <c r="AF43" s="37"/>
-      <c r="AG43" s="37"/>
-      <c r="AH43" s="47"/>
-      <c r="AI43" s="37"/>
-      <c r="AJ43" s="37"/>
+      <c r="Z43" s="44"/>
+      <c r="AA43" s="41"/>
+      <c r="AB43" s="44"/>
+      <c r="AC43" s="44"/>
+      <c r="AD43" s="44"/>
+      <c r="AE43" s="44"/>
+      <c r="AF43" s="44"/>
+      <c r="AG43" s="44"/>
+      <c r="AH43" s="41"/>
+      <c r="AI43" s="44"/>
+      <c r="AJ43" s="44"/>
       <c r="AK43" s="5">
         <f t="shared" si="3"/>
         <v>2</v>
@@ -26851,7 +26851,7 @@
       <c r="E44" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F44" s="47"/>
+      <c r="F44" s="41"/>
       <c r="G44" s="34" t="s">
         <v>117</v>
       </c>
@@ -26870,7 +26870,7 @@
       <c r="L44" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M44" s="47"/>
+      <c r="M44" s="41"/>
       <c r="N44" s="34" t="s">
         <v>117</v>
       </c>
@@ -26889,7 +26889,7 @@
       <c r="S44" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="T44" s="47"/>
+      <c r="T44" s="41"/>
       <c r="U44" s="34" t="s">
         <v>117</v>
       </c>
@@ -26905,17 +26905,17 @@
       <c r="Y44" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z44" s="37"/>
-      <c r="AA44" s="47"/>
-      <c r="AB44" s="37"/>
-      <c r="AC44" s="37"/>
-      <c r="AD44" s="37"/>
-      <c r="AE44" s="37"/>
-      <c r="AF44" s="37"/>
-      <c r="AG44" s="37"/>
-      <c r="AH44" s="47"/>
-      <c r="AI44" s="37"/>
-      <c r="AJ44" s="37"/>
+      <c r="Z44" s="44"/>
+      <c r="AA44" s="41"/>
+      <c r="AB44" s="44"/>
+      <c r="AC44" s="44"/>
+      <c r="AD44" s="44"/>
+      <c r="AE44" s="44"/>
+      <c r="AF44" s="44"/>
+      <c r="AG44" s="44"/>
+      <c r="AH44" s="41"/>
+      <c r="AI44" s="44"/>
+      <c r="AJ44" s="44"/>
       <c r="AK44" s="5">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -26941,7 +26941,7 @@
       <c r="E45" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="47"/>
+      <c r="F45" s="41"/>
       <c r="G45" s="34" t="s">
         <v>117</v>
       </c>
@@ -26960,7 +26960,7 @@
       <c r="L45" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M45" s="47"/>
+      <c r="M45" s="41"/>
       <c r="N45" s="34" t="s">
         <v>117</v>
       </c>
@@ -26979,7 +26979,7 @@
       <c r="S45" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="T45" s="47"/>
+      <c r="T45" s="41"/>
       <c r="U45" s="34" t="s">
         <v>120</v>
       </c>
@@ -26995,17 +26995,17 @@
       <c r="Y45" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z45" s="37"/>
-      <c r="AA45" s="47"/>
-      <c r="AB45" s="37"/>
-      <c r="AC45" s="37"/>
-      <c r="AD45" s="37"/>
-      <c r="AE45" s="37"/>
-      <c r="AF45" s="37"/>
-      <c r="AG45" s="37"/>
-      <c r="AH45" s="47"/>
-      <c r="AI45" s="37"/>
-      <c r="AJ45" s="37"/>
+      <c r="Z45" s="44"/>
+      <c r="AA45" s="41"/>
+      <c r="AB45" s="44"/>
+      <c r="AC45" s="44"/>
+      <c r="AD45" s="44"/>
+      <c r="AE45" s="44"/>
+      <c r="AF45" s="44"/>
+      <c r="AG45" s="44"/>
+      <c r="AH45" s="41"/>
+      <c r="AI45" s="44"/>
+      <c r="AJ45" s="44"/>
       <c r="AK45" s="5">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -27031,7 +27031,7 @@
       <c r="E46" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F46" s="47"/>
+      <c r="F46" s="41"/>
       <c r="G46" s="34" t="s">
         <v>117</v>
       </c>
@@ -27050,7 +27050,7 @@
       <c r="L46" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M46" s="47"/>
+      <c r="M46" s="41"/>
       <c r="N46" s="34" t="s">
         <v>117</v>
       </c>
@@ -27069,7 +27069,7 @@
       <c r="S46" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T46" s="47"/>
+      <c r="T46" s="41"/>
       <c r="U46" s="34" t="s">
         <v>117</v>
       </c>
@@ -27085,17 +27085,17 @@
       <c r="Y46" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z46" s="37"/>
-      <c r="AA46" s="47"/>
-      <c r="AB46" s="37"/>
-      <c r="AC46" s="37"/>
-      <c r="AD46" s="37"/>
-      <c r="AE46" s="37"/>
-      <c r="AF46" s="37"/>
-      <c r="AG46" s="37"/>
-      <c r="AH46" s="47"/>
-      <c r="AI46" s="37"/>
-      <c r="AJ46" s="37"/>
+      <c r="Z46" s="44"/>
+      <c r="AA46" s="41"/>
+      <c r="AB46" s="44"/>
+      <c r="AC46" s="44"/>
+      <c r="AD46" s="44"/>
+      <c r="AE46" s="44"/>
+      <c r="AF46" s="44"/>
+      <c r="AG46" s="44"/>
+      <c r="AH46" s="41"/>
+      <c r="AI46" s="44"/>
+      <c r="AJ46" s="44"/>
       <c r="AK46" s="5">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -27121,7 +27121,7 @@
       <c r="E47" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="47"/>
+      <c r="F47" s="41"/>
       <c r="G47" s="34" t="s">
         <v>117</v>
       </c>
@@ -27140,7 +27140,7 @@
       <c r="L47" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M47" s="47"/>
+      <c r="M47" s="41"/>
       <c r="N47" s="34" t="s">
         <v>117</v>
       </c>
@@ -27159,7 +27159,7 @@
       <c r="S47" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T47" s="47"/>
+      <c r="T47" s="41"/>
       <c r="U47" s="34" t="s">
         <v>117</v>
       </c>
@@ -27175,17 +27175,17 @@
       <c r="Y47" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z47" s="37"/>
-      <c r="AA47" s="47"/>
-      <c r="AB47" s="37"/>
-      <c r="AC47" s="37"/>
-      <c r="AD47" s="37"/>
-      <c r="AE47" s="37"/>
-      <c r="AF47" s="37"/>
-      <c r="AG47" s="37"/>
-      <c r="AH47" s="47"/>
-      <c r="AI47" s="37"/>
-      <c r="AJ47" s="37"/>
+      <c r="Z47" s="44"/>
+      <c r="AA47" s="41"/>
+      <c r="AB47" s="44"/>
+      <c r="AC47" s="44"/>
+      <c r="AD47" s="44"/>
+      <c r="AE47" s="44"/>
+      <c r="AF47" s="44"/>
+      <c r="AG47" s="44"/>
+      <c r="AH47" s="41"/>
+      <c r="AI47" s="44"/>
+      <c r="AJ47" s="44"/>
       <c r="AK47" s="5">
         <f t="shared" si="3"/>
         <v>13</v>
@@ -27209,7 +27209,7 @@
       <c r="E48" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F48" s="47"/>
+      <c r="F48" s="41"/>
       <c r="G48" s="34" t="s">
         <v>117</v>
       </c>
@@ -27228,7 +27228,7 @@
       <c r="L48" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M48" s="47"/>
+      <c r="M48" s="41"/>
       <c r="N48" s="34" t="s">
         <v>117</v>
       </c>
@@ -27247,7 +27247,7 @@
       <c r="S48" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T48" s="47"/>
+      <c r="T48" s="41"/>
       <c r="U48" s="34" t="s">
         <v>117</v>
       </c>
@@ -27263,17 +27263,17 @@
       <c r="Y48" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z48" s="37"/>
-      <c r="AA48" s="47"/>
-      <c r="AB48" s="37"/>
-      <c r="AC48" s="37"/>
-      <c r="AD48" s="37"/>
-      <c r="AE48" s="37"/>
-      <c r="AF48" s="37"/>
-      <c r="AG48" s="37"/>
-      <c r="AH48" s="47"/>
-      <c r="AI48" s="37"/>
-      <c r="AJ48" s="37"/>
+      <c r="Z48" s="44"/>
+      <c r="AA48" s="41"/>
+      <c r="AB48" s="44"/>
+      <c r="AC48" s="44"/>
+      <c r="AD48" s="44"/>
+      <c r="AE48" s="44"/>
+      <c r="AF48" s="44"/>
+      <c r="AG48" s="44"/>
+      <c r="AH48" s="41"/>
+      <c r="AI48" s="44"/>
+      <c r="AJ48" s="44"/>
       <c r="AK48" s="5">
         <f t="shared" si="3"/>
         <v>14</v>
@@ -27299,7 +27299,7 @@
       <c r="E49" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F49" s="47"/>
+      <c r="F49" s="41"/>
       <c r="G49" s="34" t="s">
         <v>117</v>
       </c>
@@ -27318,7 +27318,7 @@
       <c r="L49" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M49" s="47"/>
+      <c r="M49" s="41"/>
       <c r="N49" s="34" t="s">
         <v>117</v>
       </c>
@@ -27337,7 +27337,7 @@
       <c r="S49" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T49" s="47"/>
+      <c r="T49" s="41"/>
       <c r="U49" s="34" t="s">
         <v>116</v>
       </c>
@@ -27353,17 +27353,17 @@
       <c r="Y49" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Z49" s="37"/>
-      <c r="AA49" s="47"/>
-      <c r="AB49" s="37"/>
-      <c r="AC49" s="37"/>
-      <c r="AD49" s="37"/>
-      <c r="AE49" s="37"/>
-      <c r="AF49" s="37"/>
-      <c r="AG49" s="37"/>
-      <c r="AH49" s="47"/>
-      <c r="AI49" s="37"/>
-      <c r="AJ49" s="37"/>
+      <c r="Z49" s="44"/>
+      <c r="AA49" s="41"/>
+      <c r="AB49" s="44"/>
+      <c r="AC49" s="44"/>
+      <c r="AD49" s="44"/>
+      <c r="AE49" s="44"/>
+      <c r="AF49" s="44"/>
+      <c r="AG49" s="44"/>
+      <c r="AH49" s="41"/>
+      <c r="AI49" s="44"/>
+      <c r="AJ49" s="44"/>
       <c r="AK49" s="5">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -27389,7 +27389,7 @@
       <c r="E50" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F50" s="47"/>
+      <c r="F50" s="41"/>
       <c r="G50" s="34" t="s">
         <v>117</v>
       </c>
@@ -27408,7 +27408,7 @@
       <c r="L50" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M50" s="47"/>
+      <c r="M50" s="41"/>
       <c r="N50" s="34" t="s">
         <v>117</v>
       </c>
@@ -27427,7 +27427,7 @@
       <c r="S50" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T50" s="47"/>
+      <c r="T50" s="41"/>
       <c r="U50" s="34" t="s">
         <v>116</v>
       </c>
@@ -27443,17 +27443,17 @@
       <c r="Y50" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z50" s="37"/>
-      <c r="AA50" s="47"/>
-      <c r="AB50" s="37"/>
-      <c r="AC50" s="37"/>
-      <c r="AD50" s="37"/>
-      <c r="AE50" s="37"/>
-      <c r="AF50" s="37"/>
-      <c r="AG50" s="37"/>
-      <c r="AH50" s="47"/>
-      <c r="AI50" s="37"/>
-      <c r="AJ50" s="37"/>
+      <c r="Z50" s="44"/>
+      <c r="AA50" s="41"/>
+      <c r="AB50" s="44"/>
+      <c r="AC50" s="44"/>
+      <c r="AD50" s="44"/>
+      <c r="AE50" s="44"/>
+      <c r="AF50" s="44"/>
+      <c r="AG50" s="44"/>
+      <c r="AH50" s="41"/>
+      <c r="AI50" s="44"/>
+      <c r="AJ50" s="44"/>
       <c r="AK50" s="5">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -27479,7 +27479,7 @@
       <c r="E51" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F51" s="47"/>
+      <c r="F51" s="41"/>
       <c r="G51" s="34" t="s">
         <v>117</v>
       </c>
@@ -27498,7 +27498,7 @@
       <c r="L51" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="M51" s="47"/>
+      <c r="M51" s="41"/>
       <c r="N51" s="34" t="s">
         <v>117</v>
       </c>
@@ -27517,7 +27517,7 @@
       <c r="S51" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T51" s="47"/>
+      <c r="T51" s="41"/>
       <c r="U51" s="34" t="s">
         <v>117</v>
       </c>
@@ -27533,17 +27533,17 @@
       <c r="Y51" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Z51" s="37"/>
-      <c r="AA51" s="47"/>
-      <c r="AB51" s="37"/>
-      <c r="AC51" s="37"/>
-      <c r="AD51" s="37"/>
-      <c r="AE51" s="37"/>
-      <c r="AF51" s="37"/>
-      <c r="AG51" s="37"/>
-      <c r="AH51" s="47"/>
-      <c r="AI51" s="37"/>
-      <c r="AJ51" s="37"/>
+      <c r="Z51" s="44"/>
+      <c r="AA51" s="41"/>
+      <c r="AB51" s="44"/>
+      <c r="AC51" s="44"/>
+      <c r="AD51" s="44"/>
+      <c r="AE51" s="44"/>
+      <c r="AF51" s="44"/>
+      <c r="AG51" s="44"/>
+      <c r="AH51" s="41"/>
+      <c r="AI51" s="44"/>
+      <c r="AJ51" s="44"/>
       <c r="AK51" s="5">
         <f t="shared" si="3"/>
         <v>13</v>
@@ -27567,7 +27567,7 @@
       <c r="E52" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="47"/>
+      <c r="F52" s="41"/>
       <c r="G52" s="34" t="s">
         <v>116</v>
       </c>
@@ -27586,7 +27586,7 @@
       <c r="L52" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M52" s="47"/>
+      <c r="M52" s="41"/>
       <c r="N52" s="34" t="s">
         <v>117</v>
       </c>
@@ -27605,7 +27605,7 @@
       <c r="S52" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T52" s="47"/>
+      <c r="T52" s="41"/>
       <c r="U52" s="34" t="s">
         <v>116</v>
       </c>
@@ -27621,17 +27621,17 @@
       <c r="Y52" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z52" s="37"/>
-      <c r="AA52" s="47"/>
-      <c r="AB52" s="37"/>
-      <c r="AC52" s="37"/>
-      <c r="AD52" s="37"/>
-      <c r="AE52" s="37"/>
-      <c r="AF52" s="37"/>
-      <c r="AG52" s="37"/>
-      <c r="AH52" s="47"/>
-      <c r="AI52" s="37"/>
-      <c r="AJ52" s="37"/>
+      <c r="Z52" s="44"/>
+      <c r="AA52" s="41"/>
+      <c r="AB52" s="44"/>
+      <c r="AC52" s="44"/>
+      <c r="AD52" s="44"/>
+      <c r="AE52" s="44"/>
+      <c r="AF52" s="44"/>
+      <c r="AG52" s="44"/>
+      <c r="AH52" s="41"/>
+      <c r="AI52" s="44"/>
+      <c r="AJ52" s="44"/>
       <c r="AK52" s="5">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -27655,7 +27655,7 @@
       <c r="E53" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F53" s="47"/>
+      <c r="F53" s="41"/>
       <c r="G53" s="34" t="s">
         <v>117</v>
       </c>
@@ -27674,7 +27674,7 @@
       <c r="L53" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="M53" s="47"/>
+      <c r="M53" s="41"/>
       <c r="N53" s="34" t="s">
         <v>117</v>
       </c>
@@ -27693,7 +27693,7 @@
       <c r="S53" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T53" s="47"/>
+      <c r="T53" s="41"/>
       <c r="U53" s="34" t="s">
         <v>117</v>
       </c>
@@ -27709,17 +27709,17 @@
       <c r="Y53" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z53" s="37"/>
-      <c r="AA53" s="47"/>
-      <c r="AB53" s="37"/>
-      <c r="AC53" s="37"/>
-      <c r="AD53" s="37"/>
-      <c r="AE53" s="37"/>
-      <c r="AF53" s="37"/>
-      <c r="AG53" s="37"/>
-      <c r="AH53" s="47"/>
-      <c r="AI53" s="37"/>
-      <c r="AJ53" s="37"/>
+      <c r="Z53" s="44"/>
+      <c r="AA53" s="41"/>
+      <c r="AB53" s="44"/>
+      <c r="AC53" s="44"/>
+      <c r="AD53" s="44"/>
+      <c r="AE53" s="44"/>
+      <c r="AF53" s="44"/>
+      <c r="AG53" s="44"/>
+      <c r="AH53" s="41"/>
+      <c r="AI53" s="44"/>
+      <c r="AJ53" s="44"/>
       <c r="AK53" s="5">
         <f t="shared" si="3"/>
         <v>16</v>
@@ -27743,7 +27743,7 @@
       <c r="E54" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F54" s="47"/>
+      <c r="F54" s="41"/>
       <c r="G54" s="34" t="s">
         <v>117</v>
       </c>
@@ -27762,7 +27762,7 @@
       <c r="L54" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="M54" s="47"/>
+      <c r="M54" s="41"/>
       <c r="N54" s="34" t="s">
         <v>117</v>
       </c>
@@ -27781,7 +27781,7 @@
       <c r="S54" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T54" s="47"/>
+      <c r="T54" s="41"/>
       <c r="U54" s="34" t="s">
         <v>117</v>
       </c>
@@ -27797,17 +27797,17 @@
       <c r="Y54" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z54" s="37"/>
-      <c r="AA54" s="47"/>
-      <c r="AB54" s="37"/>
-      <c r="AC54" s="37"/>
-      <c r="AD54" s="37"/>
-      <c r="AE54" s="37"/>
-      <c r="AF54" s="37"/>
-      <c r="AG54" s="37"/>
-      <c r="AH54" s="47"/>
-      <c r="AI54" s="37"/>
-      <c r="AJ54" s="37"/>
+      <c r="Z54" s="44"/>
+      <c r="AA54" s="41"/>
+      <c r="AB54" s="44"/>
+      <c r="AC54" s="44"/>
+      <c r="AD54" s="44"/>
+      <c r="AE54" s="44"/>
+      <c r="AF54" s="44"/>
+      <c r="AG54" s="44"/>
+      <c r="AH54" s="41"/>
+      <c r="AI54" s="44"/>
+      <c r="AJ54" s="44"/>
       <c r="AK54" s="5">
         <f t="shared" si="3"/>
         <v>17</v>
@@ -27831,7 +27831,7 @@
       <c r="E55" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F55" s="47"/>
+      <c r="F55" s="41"/>
       <c r="G55" s="34" t="s">
         <v>117</v>
       </c>
@@ -27850,7 +27850,7 @@
       <c r="L55" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="M55" s="47"/>
+      <c r="M55" s="41"/>
       <c r="N55" s="34" t="s">
         <v>117</v>
       </c>
@@ -27869,7 +27869,7 @@
       <c r="S55" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T55" s="47"/>
+      <c r="T55" s="41"/>
       <c r="U55" s="34" t="s">
         <v>117</v>
       </c>
@@ -27885,17 +27885,17 @@
       <c r="Y55" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z55" s="37"/>
-      <c r="AA55" s="47"/>
-      <c r="AB55" s="37"/>
-      <c r="AC55" s="37"/>
-      <c r="AD55" s="37"/>
-      <c r="AE55" s="37"/>
-      <c r="AF55" s="37"/>
-      <c r="AG55" s="37"/>
-      <c r="AH55" s="47"/>
-      <c r="AI55" s="37"/>
-      <c r="AJ55" s="37"/>
+      <c r="Z55" s="44"/>
+      <c r="AA55" s="41"/>
+      <c r="AB55" s="44"/>
+      <c r="AC55" s="44"/>
+      <c r="AD55" s="44"/>
+      <c r="AE55" s="44"/>
+      <c r="AF55" s="44"/>
+      <c r="AG55" s="44"/>
+      <c r="AH55" s="41"/>
+      <c r="AI55" s="44"/>
+      <c r="AJ55" s="44"/>
       <c r="AK55" s="5">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -27919,7 +27919,7 @@
       <c r="E56" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F56" s="47"/>
+      <c r="F56" s="41"/>
       <c r="G56" s="34" t="s">
         <v>117</v>
       </c>
@@ -27938,7 +27938,7 @@
       <c r="L56" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M56" s="47"/>
+      <c r="M56" s="41"/>
       <c r="N56" s="34" t="s">
         <v>117</v>
       </c>
@@ -27957,7 +27957,7 @@
       <c r="S56" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T56" s="47"/>
+      <c r="T56" s="41"/>
       <c r="U56" s="34" t="s">
         <v>117</v>
       </c>
@@ -27973,17 +27973,17 @@
       <c r="Y56" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z56" s="37"/>
-      <c r="AA56" s="47"/>
-      <c r="AB56" s="37"/>
-      <c r="AC56" s="37"/>
-      <c r="AD56" s="37"/>
-      <c r="AE56" s="37"/>
-      <c r="AF56" s="37"/>
-      <c r="AG56" s="37"/>
-      <c r="AH56" s="47"/>
-      <c r="AI56" s="37"/>
-      <c r="AJ56" s="37"/>
+      <c r="Z56" s="44"/>
+      <c r="AA56" s="41"/>
+      <c r="AB56" s="44"/>
+      <c r="AC56" s="44"/>
+      <c r="AD56" s="44"/>
+      <c r="AE56" s="44"/>
+      <c r="AF56" s="44"/>
+      <c r="AG56" s="44"/>
+      <c r="AH56" s="41"/>
+      <c r="AI56" s="44"/>
+      <c r="AJ56" s="44"/>
       <c r="AK56" s="5">
         <f t="shared" si="3"/>
         <v>13</v>
@@ -28007,7 +28007,7 @@
       <c r="E57" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="47"/>
+      <c r="F57" s="41"/>
       <c r="G57" s="34" t="s">
         <v>117</v>
       </c>
@@ -28026,7 +28026,7 @@
       <c r="L57" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="M57" s="47"/>
+      <c r="M57" s="41"/>
       <c r="N57" s="34" t="s">
         <v>117</v>
       </c>
@@ -28045,7 +28045,7 @@
       <c r="S57" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T57" s="47"/>
+      <c r="T57" s="41"/>
       <c r="U57" s="34" t="s">
         <v>117</v>
       </c>
@@ -28061,17 +28061,17 @@
       <c r="Y57" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Z57" s="37"/>
-      <c r="AA57" s="47"/>
-      <c r="AB57" s="37"/>
-      <c r="AC57" s="37"/>
-      <c r="AD57" s="37"/>
-      <c r="AE57" s="37"/>
-      <c r="AF57" s="37"/>
-      <c r="AG57" s="37"/>
-      <c r="AH57" s="47"/>
-      <c r="AI57" s="37"/>
-      <c r="AJ57" s="37"/>
+      <c r="Z57" s="44"/>
+      <c r="AA57" s="41"/>
+      <c r="AB57" s="44"/>
+      <c r="AC57" s="44"/>
+      <c r="AD57" s="44"/>
+      <c r="AE57" s="44"/>
+      <c r="AF57" s="44"/>
+      <c r="AG57" s="44"/>
+      <c r="AH57" s="41"/>
+      <c r="AI57" s="44"/>
+      <c r="AJ57" s="44"/>
       <c r="AK57" s="5">
         <f t="shared" si="3"/>
         <v>13</v>
@@ -28097,7 +28097,7 @@
       <c r="E58" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F58" s="48"/>
+      <c r="F58" s="42"/>
       <c r="G58" s="34" t="s">
         <v>116</v>
       </c>
@@ -28116,7 +28116,7 @@
       <c r="L58" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="M58" s="48"/>
+      <c r="M58" s="42"/>
       <c r="N58" s="34" t="s">
         <v>117</v>
       </c>
@@ -28135,7 +28135,7 @@
       <c r="S58" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="T58" s="48"/>
+      <c r="T58" s="42"/>
       <c r="U58" s="34" t="s">
         <v>117</v>
       </c>
@@ -28151,17 +28151,17 @@
       <c r="Y58" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Z58" s="38"/>
-      <c r="AA58" s="48"/>
-      <c r="AB58" s="38"/>
-      <c r="AC58" s="38"/>
-      <c r="AD58" s="38"/>
-      <c r="AE58" s="38"/>
-      <c r="AF58" s="38"/>
-      <c r="AG58" s="38"/>
-      <c r="AH58" s="48"/>
-      <c r="AI58" s="38"/>
-      <c r="AJ58" s="38"/>
+      <c r="Z58" s="45"/>
+      <c r="AA58" s="42"/>
+      <c r="AB58" s="45"/>
+      <c r="AC58" s="45"/>
+      <c r="AD58" s="45"/>
+      <c r="AE58" s="45"/>
+      <c r="AF58" s="45"/>
+      <c r="AG58" s="45"/>
+      <c r="AH58" s="42"/>
+      <c r="AI58" s="45"/>
+      <c r="AJ58" s="45"/>
       <c r="AK58" s="5">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -28176,6 +28176,13 @@
     <sortCondition ref="A58"/>
   </sortState>
   <mergeCells count="23">
+    <mergeCell ref="T5:T58"/>
+    <mergeCell ref="AL3:AL4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="A1:AI1"/>
     <mergeCell ref="A2:AI2"/>
     <mergeCell ref="AK3:AK4"/>
@@ -28192,13 +28199,6 @@
     <mergeCell ref="M5:M58"/>
     <mergeCell ref="AA5:AA58"/>
     <mergeCell ref="AH5:AH58"/>
-    <mergeCell ref="T5:T58"/>
-    <mergeCell ref="AL3:AL4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:M5 T5 Z5:AJ5 N5:S58 U5:Y58 G6:L58">
     <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
@@ -28284,88 +28284,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="39"/>
-      <c r="U1" s="39"/>
-      <c r="V1" s="39"/>
-      <c r="W1" s="39"/>
-      <c r="X1" s="39"/>
-      <c r="Y1" s="39"/>
-      <c r="Z1" s="39"/>
-      <c r="AA1" s="39"/>
-      <c r="AB1" s="39"/>
-      <c r="AC1" s="39"/>
-      <c r="AD1" s="39"/>
-      <c r="AE1" s="39"/>
-      <c r="AF1" s="39"/>
-      <c r="AG1" s="39"/>
-      <c r="AH1" s="39"/>
-      <c r="AI1" s="39"/>
-      <c r="AJ1" s="39"/>
-      <c r="AK1" s="39"/>
-      <c r="AL1" s="39"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="47"/>
+      <c r="AA1" s="47"/>
+      <c r="AB1" s="47"/>
+      <c r="AC1" s="47"/>
+      <c r="AD1" s="47"/>
+      <c r="AE1" s="47"/>
+      <c r="AF1" s="47"/>
+      <c r="AG1" s="47"/>
+      <c r="AH1" s="47"/>
+      <c r="AI1" s="47"/>
+      <c r="AJ1" s="47"/>
+      <c r="AK1" s="47"/>
+      <c r="AL1" s="47"/>
     </row>
     <row r="2" spans="1:38" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="48" t="s">
         <v>133</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="40"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="40"/>
-      <c r="U2" s="40"/>
-      <c r="V2" s="40"/>
-      <c r="W2" s="40"/>
-      <c r="X2" s="40"/>
-      <c r="Y2" s="40"/>
-      <c r="Z2" s="40"/>
-      <c r="AA2" s="40"/>
-      <c r="AB2" s="40"/>
-      <c r="AC2" s="40"/>
-      <c r="AD2" s="40"/>
-      <c r="AE2" s="40"/>
-      <c r="AF2" s="40"/>
-      <c r="AG2" s="40"/>
-      <c r="AH2" s="40"/>
-      <c r="AI2" s="40"/>
-      <c r="AJ2" s="40"/>
-      <c r="AK2" s="40"/>
-      <c r="AL2" s="40"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
+      <c r="W2" s="48"/>
+      <c r="X2" s="48"/>
+      <c r="Y2" s="48"/>
+      <c r="Z2" s="48"/>
+      <c r="AA2" s="48"/>
+      <c r="AB2" s="48"/>
+      <c r="AC2" s="48"/>
+      <c r="AD2" s="48"/>
+      <c r="AE2" s="48"/>
+      <c r="AF2" s="48"/>
+      <c r="AG2" s="48"/>
+      <c r="AH2" s="48"/>
+      <c r="AI2" s="48"/>
+      <c r="AJ2" s="48"/>
+      <c r="AK2" s="48"/>
+      <c r="AL2" s="48"/>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" s="50" t="s">
@@ -28507,7 +28507,7 @@
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="AK3" s="35" t="s">
+      <c r="AK3" s="46" t="s">
         <v>5</v>
       </c>
       <c r="AL3" s="53" t="s">
@@ -28613,7 +28613,7 @@
       <c r="AJ4" s="23">
         <v>45688</v>
       </c>
-      <c r="AK4" s="35"/>
+      <c r="AK4" s="46"/>
       <c r="AL4" s="54"/>
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28642,7 +28642,7 @@
       <c r="I5" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="J5" s="46" t="s">
+      <c r="J5" s="40" t="s">
         <v>141</v>
       </c>
       <c r="K5" s="34" t="s">
@@ -28663,7 +28663,7 @@
       <c r="P5" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q5" s="46" t="s">
+      <c r="Q5" s="40" t="s">
         <v>141</v>
       </c>
       <c r="R5" s="34" t="s">
@@ -28678,7 +28678,7 @@
       <c r="U5" s="34"/>
       <c r="V5" s="34"/>
       <c r="W5" s="34"/>
-      <c r="X5" s="46" t="s">
+      <c r="X5" s="40" t="s">
         <v>141</v>
       </c>
       <c r="Y5" s="34"/>
@@ -28687,7 +28687,7 @@
       <c r="AB5" s="34"/>
       <c r="AC5" s="34"/>
       <c r="AD5" s="34"/>
-      <c r="AE5" s="46" t="s">
+      <c r="AE5" s="40" t="s">
         <v>141</v>
       </c>
       <c r="AF5" s="34"/>
@@ -28732,7 +28732,7 @@
       <c r="I6" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="J6" s="47"/>
+      <c r="J6" s="41"/>
       <c r="K6" s="34" t="s">
         <v>117</v>
       </c>
@@ -28751,7 +28751,7 @@
       <c r="P6" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q6" s="47"/>
+      <c r="Q6" s="41"/>
       <c r="R6" s="34" t="s">
         <v>117</v>
       </c>
@@ -28764,14 +28764,14 @@
       <c r="U6" s="34"/>
       <c r="V6" s="34"/>
       <c r="W6" s="34"/>
-      <c r="X6" s="47"/>
+      <c r="X6" s="41"/>
       <c r="Y6" s="34"/>
       <c r="Z6" s="34"/>
       <c r="AA6" s="34"/>
       <c r="AB6" s="34"/>
       <c r="AC6" s="34"/>
       <c r="AD6" s="34"/>
-      <c r="AE6" s="47"/>
+      <c r="AE6" s="41"/>
       <c r="AF6" s="34"/>
       <c r="AG6" s="34"/>
       <c r="AH6" s="34"/>
@@ -28814,7 +28814,7 @@
       <c r="I7" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="J7" s="47"/>
+      <c r="J7" s="41"/>
       <c r="K7" s="34" t="s">
         <v>117</v>
       </c>
@@ -28833,7 +28833,7 @@
       <c r="P7" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q7" s="47"/>
+      <c r="Q7" s="41"/>
       <c r="R7" s="34" t="s">
         <v>116</v>
       </c>
@@ -28846,14 +28846,14 @@
       <c r="U7" s="34"/>
       <c r="V7" s="34"/>
       <c r="W7" s="34"/>
-      <c r="X7" s="47"/>
+      <c r="X7" s="41"/>
       <c r="Y7" s="34"/>
       <c r="Z7" s="34"/>
       <c r="AA7" s="34"/>
       <c r="AB7" s="34"/>
       <c r="AC7" s="34"/>
       <c r="AD7" s="34"/>
-      <c r="AE7" s="47"/>
+      <c r="AE7" s="41"/>
       <c r="AF7" s="34"/>
       <c r="AG7" s="34"/>
       <c r="AH7" s="34"/>
@@ -28894,7 +28894,7 @@
       <c r="I8" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J8" s="47"/>
+      <c r="J8" s="41"/>
       <c r="K8" s="34" t="s">
         <v>117</v>
       </c>
@@ -28913,7 +28913,7 @@
       <c r="P8" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q8" s="47"/>
+      <c r="Q8" s="41"/>
       <c r="R8" s="34" t="s">
         <v>117</v>
       </c>
@@ -28926,14 +28926,14 @@
       <c r="U8" s="34"/>
       <c r="V8" s="34"/>
       <c r="W8" s="34"/>
-      <c r="X8" s="47"/>
+      <c r="X8" s="41"/>
       <c r="Y8" s="34"/>
       <c r="Z8" s="34"/>
       <c r="AA8" s="34"/>
       <c r="AB8" s="34"/>
       <c r="AC8" s="34"/>
       <c r="AD8" s="34"/>
-      <c r="AE8" s="47"/>
+      <c r="AE8" s="41"/>
       <c r="AF8" s="34"/>
       <c r="AG8" s="34"/>
       <c r="AH8" s="34"/>
@@ -28976,7 +28976,7 @@
       <c r="I9" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J9" s="47"/>
+      <c r="J9" s="41"/>
       <c r="K9" s="34" t="s">
         <v>116</v>
       </c>
@@ -28995,7 +28995,7 @@
       <c r="P9" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q9" s="47"/>
+      <c r="Q9" s="41"/>
       <c r="R9" s="34" t="s">
         <v>117</v>
       </c>
@@ -29008,14 +29008,14 @@
       <c r="U9" s="34"/>
       <c r="V9" s="34"/>
       <c r="W9" s="34"/>
-      <c r="X9" s="47"/>
+      <c r="X9" s="41"/>
       <c r="Y9" s="34"/>
       <c r="Z9" s="34"/>
       <c r="AA9" s="34"/>
       <c r="AB9" s="34"/>
       <c r="AC9" s="34"/>
       <c r="AD9" s="34"/>
-      <c r="AE9" s="47"/>
+      <c r="AE9" s="41"/>
       <c r="AF9" s="34"/>
       <c r="AG9" s="34"/>
       <c r="AH9" s="34"/>
@@ -29058,7 +29058,7 @@
       <c r="I10" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="J10" s="47"/>
+      <c r="J10" s="41"/>
       <c r="K10" s="34" t="s">
         <v>117</v>
       </c>
@@ -29077,7 +29077,7 @@
       <c r="P10" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q10" s="47"/>
+      <c r="Q10" s="41"/>
       <c r="R10" s="34" t="s">
         <v>116</v>
       </c>
@@ -29090,14 +29090,14 @@
       <c r="U10" s="34"/>
       <c r="V10" s="34"/>
       <c r="W10" s="34"/>
-      <c r="X10" s="47"/>
+      <c r="X10" s="41"/>
       <c r="Y10" s="34"/>
       <c r="Z10" s="34"/>
       <c r="AA10" s="34"/>
       <c r="AB10" s="34"/>
       <c r="AC10" s="34"/>
       <c r="AD10" s="34"/>
-      <c r="AE10" s="47"/>
+      <c r="AE10" s="41"/>
       <c r="AF10" s="34"/>
       <c r="AG10" s="34"/>
       <c r="AH10" s="34"/>
@@ -29140,7 +29140,7 @@
       <c r="I11" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="J11" s="47"/>
+      <c r="J11" s="41"/>
       <c r="K11" s="34" t="s">
         <v>116</v>
       </c>
@@ -29159,7 +29159,7 @@
       <c r="P11" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Q11" s="47"/>
+      <c r="Q11" s="41"/>
       <c r="R11" s="34" t="s">
         <v>117</v>
       </c>
@@ -29172,14 +29172,14 @@
       <c r="U11" s="34"/>
       <c r="V11" s="34"/>
       <c r="W11" s="34"/>
-      <c r="X11" s="47"/>
+      <c r="X11" s="41"/>
       <c r="Y11" s="34"/>
       <c r="Z11" s="34"/>
       <c r="AA11" s="34"/>
       <c r="AB11" s="34"/>
       <c r="AC11" s="34"/>
       <c r="AD11" s="34"/>
-      <c r="AE11" s="47"/>
+      <c r="AE11" s="41"/>
       <c r="AF11" s="34"/>
       <c r="AG11" s="34"/>
       <c r="AH11" s="34"/>
@@ -29222,7 +29222,7 @@
       <c r="I12" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J12" s="47"/>
+      <c r="J12" s="41"/>
       <c r="K12" s="34" t="s">
         <v>116</v>
       </c>
@@ -29241,7 +29241,7 @@
       <c r="P12" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q12" s="47"/>
+      <c r="Q12" s="41"/>
       <c r="R12" s="34" t="s">
         <v>117</v>
       </c>
@@ -29254,14 +29254,14 @@
       <c r="U12" s="34"/>
       <c r="V12" s="34"/>
       <c r="W12" s="34"/>
-      <c r="X12" s="47"/>
+      <c r="X12" s="41"/>
       <c r="Y12" s="34"/>
       <c r="Z12" s="34"/>
       <c r="AA12" s="34"/>
       <c r="AB12" s="34"/>
       <c r="AC12" s="34"/>
       <c r="AD12" s="34"/>
-      <c r="AE12" s="47"/>
+      <c r="AE12" s="41"/>
       <c r="AF12" s="34"/>
       <c r="AG12" s="34"/>
       <c r="AH12" s="34"/>
@@ -29304,7 +29304,7 @@
       <c r="I13" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="J13" s="47"/>
+      <c r="J13" s="41"/>
       <c r="K13" s="34" t="s">
         <v>117</v>
       </c>
@@ -29323,7 +29323,7 @@
       <c r="P13" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q13" s="47"/>
+      <c r="Q13" s="41"/>
       <c r="R13" s="34" t="s">
         <v>117</v>
       </c>
@@ -29336,14 +29336,14 @@
       <c r="U13" s="34"/>
       <c r="V13" s="34"/>
       <c r="W13" s="34"/>
-      <c r="X13" s="47"/>
+      <c r="X13" s="41"/>
       <c r="Y13" s="34"/>
       <c r="Z13" s="34"/>
       <c r="AA13" s="34"/>
       <c r="AB13" s="34"/>
       <c r="AC13" s="34"/>
       <c r="AD13" s="34"/>
-      <c r="AE13" s="47"/>
+      <c r="AE13" s="41"/>
       <c r="AF13" s="34"/>
       <c r="AG13" s="34"/>
       <c r="AH13" s="34"/>
@@ -29386,7 +29386,7 @@
       <c r="I14" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J14" s="47"/>
+      <c r="J14" s="41"/>
       <c r="K14" s="34" t="s">
         <v>116</v>
       </c>
@@ -29405,7 +29405,7 @@
       <c r="P14" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q14" s="47"/>
+      <c r="Q14" s="41"/>
       <c r="R14" s="34" t="s">
         <v>117</v>
       </c>
@@ -29418,14 +29418,14 @@
       <c r="U14" s="34"/>
       <c r="V14" s="34"/>
       <c r="W14" s="34"/>
-      <c r="X14" s="47"/>
+      <c r="X14" s="41"/>
       <c r="Y14" s="34"/>
       <c r="Z14" s="34"/>
       <c r="AA14" s="34"/>
       <c r="AB14" s="34"/>
       <c r="AC14" s="34"/>
       <c r="AD14" s="34"/>
-      <c r="AE14" s="47"/>
+      <c r="AE14" s="41"/>
       <c r="AF14" s="34"/>
       <c r="AG14" s="34"/>
       <c r="AH14" s="34"/>
@@ -29468,7 +29468,7 @@
       <c r="I15" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="J15" s="47"/>
+      <c r="J15" s="41"/>
       <c r="K15" s="34" t="s">
         <v>117</v>
       </c>
@@ -29487,7 +29487,7 @@
       <c r="P15" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Q15" s="47"/>
+      <c r="Q15" s="41"/>
       <c r="R15" s="34" t="s">
         <v>117</v>
       </c>
@@ -29500,14 +29500,14 @@
       <c r="U15" s="34"/>
       <c r="V15" s="34"/>
       <c r="W15" s="34"/>
-      <c r="X15" s="47"/>
+      <c r="X15" s="41"/>
       <c r="Y15" s="34"/>
       <c r="Z15" s="34"/>
       <c r="AA15" s="34"/>
       <c r="AB15" s="34"/>
       <c r="AC15" s="34"/>
       <c r="AD15" s="34"/>
-      <c r="AE15" s="47"/>
+      <c r="AE15" s="41"/>
       <c r="AF15" s="34"/>
       <c r="AG15" s="34"/>
       <c r="AH15" s="34"/>
@@ -29550,7 +29550,7 @@
       <c r="I16" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J16" s="47"/>
+      <c r="J16" s="41"/>
       <c r="K16" s="34" t="s">
         <v>117</v>
       </c>
@@ -29569,7 +29569,7 @@
       <c r="P16" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Q16" s="47"/>
+      <c r="Q16" s="41"/>
       <c r="R16" s="34" t="s">
         <v>117</v>
       </c>
@@ -29582,14 +29582,14 @@
       <c r="U16" s="34"/>
       <c r="V16" s="34"/>
       <c r="W16" s="34"/>
-      <c r="X16" s="47"/>
+      <c r="X16" s="41"/>
       <c r="Y16" s="34"/>
       <c r="Z16" s="34"/>
       <c r="AA16" s="34"/>
       <c r="AB16" s="34"/>
       <c r="AC16" s="34"/>
       <c r="AD16" s="34"/>
-      <c r="AE16" s="47"/>
+      <c r="AE16" s="41"/>
       <c r="AF16" s="34"/>
       <c r="AG16" s="34"/>
       <c r="AH16" s="34"/>
@@ -29632,7 +29632,7 @@
       <c r="I17" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="J17" s="47"/>
+      <c r="J17" s="41"/>
       <c r="K17" s="34" t="s">
         <v>117</v>
       </c>
@@ -29651,7 +29651,7 @@
       <c r="P17" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q17" s="47"/>
+      <c r="Q17" s="41"/>
       <c r="R17" s="34" t="s">
         <v>117</v>
       </c>
@@ -29664,14 +29664,14 @@
       <c r="U17" s="34"/>
       <c r="V17" s="34"/>
       <c r="W17" s="34"/>
-      <c r="X17" s="47"/>
+      <c r="X17" s="41"/>
       <c r="Y17" s="34"/>
       <c r="Z17" s="34"/>
       <c r="AA17" s="34"/>
       <c r="AB17" s="34"/>
       <c r="AC17" s="34"/>
       <c r="AD17" s="34"/>
-      <c r="AE17" s="47"/>
+      <c r="AE17" s="41"/>
       <c r="AF17" s="34"/>
       <c r="AG17" s="34"/>
       <c r="AH17" s="34"/>
@@ -29714,7 +29714,7 @@
       <c r="I18" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J18" s="47"/>
+      <c r="J18" s="41"/>
       <c r="K18" s="34" t="s">
         <v>116</v>
       </c>
@@ -29733,7 +29733,7 @@
       <c r="P18" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Q18" s="47"/>
+      <c r="Q18" s="41"/>
       <c r="R18" s="34" t="s">
         <v>117</v>
       </c>
@@ -29746,14 +29746,14 @@
       <c r="U18" s="34"/>
       <c r="V18" s="34"/>
       <c r="W18" s="34"/>
-      <c r="X18" s="47"/>
+      <c r="X18" s="41"/>
       <c r="Y18" s="34"/>
       <c r="Z18" s="34"/>
       <c r="AA18" s="34"/>
       <c r="AB18" s="34"/>
       <c r="AC18" s="34"/>
       <c r="AD18" s="34"/>
-      <c r="AE18" s="47"/>
+      <c r="AE18" s="41"/>
       <c r="AF18" s="34"/>
       <c r="AG18" s="34"/>
       <c r="AH18" s="34"/>
@@ -29796,7 +29796,7 @@
       <c r="I19" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J19" s="47"/>
+      <c r="J19" s="41"/>
       <c r="K19" s="34" t="s">
         <v>117</v>
       </c>
@@ -29815,7 +29815,7 @@
       <c r="P19" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q19" s="47"/>
+      <c r="Q19" s="41"/>
       <c r="R19" s="34" t="s">
         <v>120</v>
       </c>
@@ -29828,14 +29828,14 @@
       <c r="U19" s="34"/>
       <c r="V19" s="34"/>
       <c r="W19" s="34"/>
-      <c r="X19" s="47"/>
+      <c r="X19" s="41"/>
       <c r="Y19" s="34"/>
       <c r="Z19" s="34"/>
       <c r="AA19" s="34"/>
       <c r="AB19" s="34"/>
       <c r="AC19" s="34"/>
       <c r="AD19" s="34"/>
-      <c r="AE19" s="47"/>
+      <c r="AE19" s="41"/>
       <c r="AF19" s="34"/>
       <c r="AG19" s="34"/>
       <c r="AH19" s="34"/>
@@ -29878,7 +29878,7 @@
       <c r="I20" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="J20" s="47"/>
+      <c r="J20" s="41"/>
       <c r="K20" s="34" t="s">
         <v>117</v>
       </c>
@@ -29897,7 +29897,7 @@
       <c r="P20" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q20" s="47"/>
+      <c r="Q20" s="41"/>
       <c r="R20" s="34" t="s">
         <v>117</v>
       </c>
@@ -29910,14 +29910,14 @@
       <c r="U20" s="34"/>
       <c r="V20" s="34"/>
       <c r="W20" s="34"/>
-      <c r="X20" s="47"/>
+      <c r="X20" s="41"/>
       <c r="Y20" s="34"/>
       <c r="Z20" s="34"/>
       <c r="AA20" s="34"/>
       <c r="AB20" s="34"/>
       <c r="AC20" s="34"/>
       <c r="AD20" s="34"/>
-      <c r="AE20" s="47"/>
+      <c r="AE20" s="41"/>
       <c r="AF20" s="34"/>
       <c r="AG20" s="34"/>
       <c r="AH20" s="34"/>
@@ -29960,7 +29960,7 @@
       <c r="I21" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J21" s="47"/>
+      <c r="J21" s="41"/>
       <c r="K21" s="34" t="s">
         <v>116</v>
       </c>
@@ -29979,7 +29979,7 @@
       <c r="P21" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q21" s="47"/>
+      <c r="Q21" s="41"/>
       <c r="R21" s="34" t="s">
         <v>117</v>
       </c>
@@ -29992,14 +29992,14 @@
       <c r="U21" s="34"/>
       <c r="V21" s="34"/>
       <c r="W21" s="34"/>
-      <c r="X21" s="47"/>
+      <c r="X21" s="41"/>
       <c r="Y21" s="34"/>
       <c r="Z21" s="34"/>
       <c r="AA21" s="34"/>
       <c r="AB21" s="34"/>
       <c r="AC21" s="34"/>
       <c r="AD21" s="34"/>
-      <c r="AE21" s="47"/>
+      <c r="AE21" s="41"/>
       <c r="AF21" s="34"/>
       <c r="AG21" s="34"/>
       <c r="AH21" s="34"/>
@@ -30042,7 +30042,7 @@
       <c r="I22" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J22" s="47"/>
+      <c r="J22" s="41"/>
       <c r="K22" s="34" t="s">
         <v>117</v>
       </c>
@@ -30061,7 +30061,7 @@
       <c r="P22" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Q22" s="47"/>
+      <c r="Q22" s="41"/>
       <c r="R22" s="34" t="s">
         <v>117</v>
       </c>
@@ -30074,14 +30074,14 @@
       <c r="U22" s="34"/>
       <c r="V22" s="34"/>
       <c r="W22" s="34"/>
-      <c r="X22" s="47"/>
+      <c r="X22" s="41"/>
       <c r="Y22" s="34"/>
       <c r="Z22" s="34"/>
       <c r="AA22" s="34"/>
       <c r="AB22" s="34"/>
       <c r="AC22" s="34"/>
       <c r="AD22" s="34"/>
-      <c r="AE22" s="47"/>
+      <c r="AE22" s="41"/>
       <c r="AF22" s="34"/>
       <c r="AG22" s="34"/>
       <c r="AH22" s="34"/>
@@ -30124,7 +30124,7 @@
       <c r="I23" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J23" s="47"/>
+      <c r="J23" s="41"/>
       <c r="K23" s="34" t="s">
         <v>117</v>
       </c>
@@ -30143,7 +30143,7 @@
       <c r="P23" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q23" s="47"/>
+      <c r="Q23" s="41"/>
       <c r="R23" s="34" t="s">
         <v>116</v>
       </c>
@@ -30156,14 +30156,14 @@
       <c r="U23" s="34"/>
       <c r="V23" s="34"/>
       <c r="W23" s="34"/>
-      <c r="X23" s="47"/>
+      <c r="X23" s="41"/>
       <c r="Y23" s="34"/>
       <c r="Z23" s="34"/>
       <c r="AA23" s="34"/>
       <c r="AB23" s="34"/>
       <c r="AC23" s="34"/>
       <c r="AD23" s="34"/>
-      <c r="AE23" s="47"/>
+      <c r="AE23" s="41"/>
       <c r="AF23" s="34"/>
       <c r="AG23" s="34"/>
       <c r="AH23" s="34"/>
@@ -30204,7 +30204,7 @@
       <c r="I24" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J24" s="47"/>
+      <c r="J24" s="41"/>
       <c r="K24" s="34" t="s">
         <v>117</v>
       </c>
@@ -30223,7 +30223,7 @@
       <c r="P24" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q24" s="47"/>
+      <c r="Q24" s="41"/>
       <c r="R24" s="34" t="s">
         <v>117</v>
       </c>
@@ -30236,14 +30236,14 @@
       <c r="U24" s="34"/>
       <c r="V24" s="34"/>
       <c r="W24" s="34"/>
-      <c r="X24" s="47"/>
+      <c r="X24" s="41"/>
       <c r="Y24" s="34"/>
       <c r="Z24" s="34"/>
       <c r="AA24" s="34"/>
       <c r="AB24" s="34"/>
       <c r="AC24" s="34"/>
       <c r="AD24" s="34"/>
-      <c r="AE24" s="47"/>
+      <c r="AE24" s="41"/>
       <c r="AF24" s="34"/>
       <c r="AG24" s="34"/>
       <c r="AH24" s="34"/>
@@ -30286,7 +30286,7 @@
       <c r="I25" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J25" s="47"/>
+      <c r="J25" s="41"/>
       <c r="K25" s="34" t="s">
         <v>116</v>
       </c>
@@ -30305,7 +30305,7 @@
       <c r="P25" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q25" s="47"/>
+      <c r="Q25" s="41"/>
       <c r="R25" s="34" t="s">
         <v>117</v>
       </c>
@@ -30318,14 +30318,14 @@
       <c r="U25" s="34"/>
       <c r="V25" s="34"/>
       <c r="W25" s="34"/>
-      <c r="X25" s="47"/>
+      <c r="X25" s="41"/>
       <c r="Y25" s="34"/>
       <c r="Z25" s="34"/>
       <c r="AA25" s="34"/>
       <c r="AB25" s="34"/>
       <c r="AC25" s="34"/>
       <c r="AD25" s="34"/>
-      <c r="AE25" s="47"/>
+      <c r="AE25" s="41"/>
       <c r="AF25" s="34"/>
       <c r="AG25" s="34"/>
       <c r="AH25" s="34"/>
@@ -30366,7 +30366,7 @@
       <c r="I26" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="J26" s="47"/>
+      <c r="J26" s="41"/>
       <c r="K26" s="34" t="s">
         <v>116</v>
       </c>
@@ -30385,7 +30385,7 @@
       <c r="P26" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Q26" s="47"/>
+      <c r="Q26" s="41"/>
       <c r="R26" s="34" t="s">
         <v>117</v>
       </c>
@@ -30398,14 +30398,14 @@
       <c r="U26" s="34"/>
       <c r="V26" s="34"/>
       <c r="W26" s="34"/>
-      <c r="X26" s="47"/>
+      <c r="X26" s="41"/>
       <c r="Y26" s="34"/>
       <c r="Z26" s="34"/>
       <c r="AA26" s="34"/>
       <c r="AB26" s="34"/>
       <c r="AC26" s="34"/>
       <c r="AD26" s="34"/>
-      <c r="AE26" s="47"/>
+      <c r="AE26" s="41"/>
       <c r="AF26" s="34"/>
       <c r="AG26" s="34"/>
       <c r="AH26" s="34"/>
@@ -30444,7 +30444,7 @@
       <c r="I27" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J27" s="47"/>
+      <c r="J27" s="41"/>
       <c r="K27" s="34" t="s">
         <v>116</v>
       </c>
@@ -30463,7 +30463,7 @@
       <c r="P27" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Q27" s="47"/>
+      <c r="Q27" s="41"/>
       <c r="R27" s="34" t="s">
         <v>116</v>
       </c>
@@ -30476,14 +30476,14 @@
       <c r="U27" s="34"/>
       <c r="V27" s="34"/>
       <c r="W27" s="34"/>
-      <c r="X27" s="47"/>
+      <c r="X27" s="41"/>
       <c r="Y27" s="34"/>
       <c r="Z27" s="34"/>
       <c r="AA27" s="34"/>
       <c r="AB27" s="34"/>
       <c r="AC27" s="34"/>
       <c r="AD27" s="34"/>
-      <c r="AE27" s="47"/>
+      <c r="AE27" s="41"/>
       <c r="AF27" s="34"/>
       <c r="AG27" s="34"/>
       <c r="AH27" s="34"/>
@@ -30524,7 +30524,7 @@
       <c r="I28" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="J28" s="47"/>
+      <c r="J28" s="41"/>
       <c r="K28" s="34" t="s">
         <v>117</v>
       </c>
@@ -30543,7 +30543,7 @@
       <c r="P28" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q28" s="47"/>
+      <c r="Q28" s="41"/>
       <c r="R28" s="34" t="s">
         <v>117</v>
       </c>
@@ -30556,14 +30556,14 @@
       <c r="U28" s="34"/>
       <c r="V28" s="34"/>
       <c r="W28" s="34"/>
-      <c r="X28" s="47"/>
+      <c r="X28" s="41"/>
       <c r="Y28" s="34"/>
       <c r="Z28" s="34"/>
       <c r="AA28" s="34"/>
       <c r="AB28" s="34"/>
       <c r="AC28" s="34"/>
       <c r="AD28" s="34"/>
-      <c r="AE28" s="47"/>
+      <c r="AE28" s="41"/>
       <c r="AF28" s="34"/>
       <c r="AG28" s="34"/>
       <c r="AH28" s="34"/>
@@ -30602,7 +30602,7 @@
       <c r="I29" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J29" s="47"/>
+      <c r="J29" s="41"/>
       <c r="K29" s="34" t="s">
         <v>116</v>
       </c>
@@ -30621,7 +30621,7 @@
       <c r="P29" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q29" s="47"/>
+      <c r="Q29" s="41"/>
       <c r="R29" s="34" t="s">
         <v>117</v>
       </c>
@@ -30634,14 +30634,14 @@
       <c r="U29" s="34"/>
       <c r="V29" s="34"/>
       <c r="W29" s="34"/>
-      <c r="X29" s="47"/>
+      <c r="X29" s="41"/>
       <c r="Y29" s="34"/>
       <c r="Z29" s="34"/>
       <c r="AA29" s="34"/>
       <c r="AB29" s="34"/>
       <c r="AC29" s="34"/>
       <c r="AD29" s="34"/>
-      <c r="AE29" s="47"/>
+      <c r="AE29" s="41"/>
       <c r="AF29" s="34"/>
       <c r="AG29" s="34"/>
       <c r="AH29" s="34"/>
@@ -30682,7 +30682,7 @@
       <c r="I30" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="J30" s="47"/>
+      <c r="J30" s="41"/>
       <c r="K30" s="34" t="s">
         <v>117</v>
       </c>
@@ -30701,7 +30701,7 @@
       <c r="P30" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q30" s="47"/>
+      <c r="Q30" s="41"/>
       <c r="R30" s="34" t="s">
         <v>117</v>
       </c>
@@ -30714,14 +30714,14 @@
       <c r="U30" s="34"/>
       <c r="V30" s="34"/>
       <c r="W30" s="34"/>
-      <c r="X30" s="47"/>
+      <c r="X30" s="41"/>
       <c r="Y30" s="34"/>
       <c r="Z30" s="34"/>
       <c r="AA30" s="34"/>
       <c r="AB30" s="34"/>
       <c r="AC30" s="34"/>
       <c r="AD30" s="34"/>
-      <c r="AE30" s="47"/>
+      <c r="AE30" s="41"/>
       <c r="AF30" s="34"/>
       <c r="AG30" s="34"/>
       <c r="AH30" s="34"/>
@@ -30762,7 +30762,7 @@
       <c r="I31" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J31" s="47"/>
+      <c r="J31" s="41"/>
       <c r="K31" s="34" t="s">
         <v>117</v>
       </c>
@@ -30781,7 +30781,7 @@
       <c r="P31" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q31" s="47"/>
+      <c r="Q31" s="41"/>
       <c r="R31" s="34" t="s">
         <v>117</v>
       </c>
@@ -30794,14 +30794,14 @@
       <c r="U31" s="34"/>
       <c r="V31" s="34"/>
       <c r="W31" s="34"/>
-      <c r="X31" s="47"/>
+      <c r="X31" s="41"/>
       <c r="Y31" s="34"/>
       <c r="Z31" s="34"/>
       <c r="AA31" s="34"/>
       <c r="AB31" s="34"/>
       <c r="AC31" s="34"/>
       <c r="AD31" s="34"/>
-      <c r="AE31" s="47"/>
+      <c r="AE31" s="41"/>
       <c r="AF31" s="34"/>
       <c r="AG31" s="34"/>
       <c r="AH31" s="34"/>
@@ -30844,7 +30844,7 @@
       <c r="I32" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="J32" s="47"/>
+      <c r="J32" s="41"/>
       <c r="K32" s="34" t="s">
         <v>117</v>
       </c>
@@ -30863,7 +30863,7 @@
       <c r="P32" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q32" s="47"/>
+      <c r="Q32" s="41"/>
       <c r="R32" s="34" t="s">
         <v>117</v>
       </c>
@@ -30876,14 +30876,14 @@
       <c r="U32" s="34"/>
       <c r="V32" s="34"/>
       <c r="W32" s="34"/>
-      <c r="X32" s="47"/>
+      <c r="X32" s="41"/>
       <c r="Y32" s="34"/>
       <c r="Z32" s="34"/>
       <c r="AA32" s="34"/>
       <c r="AB32" s="34"/>
       <c r="AC32" s="34"/>
       <c r="AD32" s="34"/>
-      <c r="AE32" s="47"/>
+      <c r="AE32" s="41"/>
       <c r="AF32" s="34"/>
       <c r="AG32" s="34"/>
       <c r="AH32" s="34"/>
@@ -30926,7 +30926,7 @@
       <c r="I33" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J33" s="47"/>
+      <c r="J33" s="41"/>
       <c r="K33" s="34" t="s">
         <v>117</v>
       </c>
@@ -30945,7 +30945,7 @@
       <c r="P33" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q33" s="47"/>
+      <c r="Q33" s="41"/>
       <c r="R33" s="34" t="s">
         <v>117</v>
       </c>
@@ -30958,14 +30958,14 @@
       <c r="U33" s="34"/>
       <c r="V33" s="34"/>
       <c r="W33" s="34"/>
-      <c r="X33" s="47"/>
+      <c r="X33" s="41"/>
       <c r="Y33" s="34"/>
       <c r="Z33" s="34"/>
       <c r="AA33" s="34"/>
       <c r="AB33" s="34"/>
       <c r="AC33" s="34"/>
       <c r="AD33" s="34"/>
-      <c r="AE33" s="47"/>
+      <c r="AE33" s="41"/>
       <c r="AF33" s="34"/>
       <c r="AG33" s="34"/>
       <c r="AH33" s="34"/>
@@ -31008,7 +31008,7 @@
       <c r="I34" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J34" s="47"/>
+      <c r="J34" s="41"/>
       <c r="K34" s="34" t="s">
         <v>116</v>
       </c>
@@ -31027,7 +31027,7 @@
       <c r="P34" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q34" s="47"/>
+      <c r="Q34" s="41"/>
       <c r="R34" s="34" t="s">
         <v>117</v>
       </c>
@@ -31040,14 +31040,14 @@
       <c r="U34" s="34"/>
       <c r="V34" s="34"/>
       <c r="W34" s="34"/>
-      <c r="X34" s="47"/>
+      <c r="X34" s="41"/>
       <c r="Y34" s="34"/>
       <c r="Z34" s="34"/>
       <c r="AA34" s="34"/>
       <c r="AB34" s="34"/>
       <c r="AC34" s="34"/>
       <c r="AD34" s="34"/>
-      <c r="AE34" s="47"/>
+      <c r="AE34" s="41"/>
       <c r="AF34" s="34"/>
       <c r="AG34" s="34"/>
       <c r="AH34" s="34"/>
@@ -31090,7 +31090,7 @@
       <c r="I35" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="J35" s="47"/>
+      <c r="J35" s="41"/>
       <c r="K35" s="34" t="s">
         <v>117</v>
       </c>
@@ -31109,7 +31109,7 @@
       <c r="P35" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q35" s="47"/>
+      <c r="Q35" s="41"/>
       <c r="R35" s="34" t="s">
         <v>117</v>
       </c>
@@ -31122,14 +31122,14 @@
       <c r="U35" s="34"/>
       <c r="V35" s="34"/>
       <c r="W35" s="34"/>
-      <c r="X35" s="47"/>
+      <c r="X35" s="41"/>
       <c r="Y35" s="34"/>
       <c r="Z35" s="34"/>
       <c r="AA35" s="34"/>
       <c r="AB35" s="34"/>
       <c r="AC35" s="34"/>
       <c r="AD35" s="34"/>
-      <c r="AE35" s="47"/>
+      <c r="AE35" s="41"/>
       <c r="AF35" s="34"/>
       <c r="AG35" s="34"/>
       <c r="AH35" s="34"/>
@@ -31172,7 +31172,7 @@
       <c r="I36" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J36" s="47"/>
+      <c r="J36" s="41"/>
       <c r="K36" s="34" t="s">
         <v>116</v>
       </c>
@@ -31191,7 +31191,7 @@
       <c r="P36" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q36" s="47"/>
+      <c r="Q36" s="41"/>
       <c r="R36" s="34" t="s">
         <v>117</v>
       </c>
@@ -31204,14 +31204,14 @@
       <c r="U36" s="34"/>
       <c r="V36" s="34"/>
       <c r="W36" s="34"/>
-      <c r="X36" s="47"/>
+      <c r="X36" s="41"/>
       <c r="Y36" s="34"/>
       <c r="Z36" s="34"/>
       <c r="AA36" s="34"/>
       <c r="AB36" s="34"/>
       <c r="AC36" s="34"/>
       <c r="AD36" s="34"/>
-      <c r="AE36" s="47"/>
+      <c r="AE36" s="41"/>
       <c r="AF36" s="34"/>
       <c r="AG36" s="34"/>
       <c r="AH36" s="34"/>
@@ -31254,7 +31254,7 @@
       <c r="I37" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J37" s="47"/>
+      <c r="J37" s="41"/>
       <c r="K37" s="34" t="s">
         <v>117</v>
       </c>
@@ -31273,7 +31273,7 @@
       <c r="P37" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q37" s="47"/>
+      <c r="Q37" s="41"/>
       <c r="R37" s="34" t="s">
         <v>117</v>
       </c>
@@ -31286,14 +31286,14 @@
       <c r="U37" s="34"/>
       <c r="V37" s="34"/>
       <c r="W37" s="34"/>
-      <c r="X37" s="47"/>
+      <c r="X37" s="41"/>
       <c r="Y37" s="34"/>
       <c r="Z37" s="34"/>
       <c r="AA37" s="34"/>
       <c r="AB37" s="34"/>
       <c r="AC37" s="34"/>
       <c r="AD37" s="34"/>
-      <c r="AE37" s="47"/>
+      <c r="AE37" s="41"/>
       <c r="AF37" s="34"/>
       <c r="AG37" s="34"/>
       <c r="AH37" s="34"/>
@@ -31336,7 +31336,7 @@
       <c r="I38" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J38" s="47"/>
+      <c r="J38" s="41"/>
       <c r="K38" s="34" t="s">
         <v>116</v>
       </c>
@@ -31355,7 +31355,7 @@
       <c r="P38" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Q38" s="47"/>
+      <c r="Q38" s="41"/>
       <c r="R38" s="34" t="s">
         <v>116</v>
       </c>
@@ -31368,14 +31368,14 @@
       <c r="U38" s="34"/>
       <c r="V38" s="34"/>
       <c r="W38" s="34"/>
-      <c r="X38" s="47"/>
+      <c r="X38" s="41"/>
       <c r="Y38" s="34"/>
       <c r="Z38" s="34"/>
       <c r="AA38" s="34"/>
       <c r="AB38" s="34"/>
       <c r="AC38" s="34"/>
       <c r="AD38" s="34"/>
-      <c r="AE38" s="47"/>
+      <c r="AE38" s="41"/>
       <c r="AF38" s="34"/>
       <c r="AG38" s="34"/>
       <c r="AH38" s="34"/>
@@ -31418,7 +31418,7 @@
       <c r="I39" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J39" s="47"/>
+      <c r="J39" s="41"/>
       <c r="K39" s="34" t="s">
         <v>116</v>
       </c>
@@ -31437,7 +31437,7 @@
       <c r="P39" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q39" s="47"/>
+      <c r="Q39" s="41"/>
       <c r="R39" s="34" t="s">
         <v>117</v>
       </c>
@@ -31450,14 +31450,14 @@
       <c r="U39" s="34"/>
       <c r="V39" s="34"/>
       <c r="W39" s="34"/>
-      <c r="X39" s="47"/>
+      <c r="X39" s="41"/>
       <c r="Y39" s="34"/>
       <c r="Z39" s="34"/>
       <c r="AA39" s="34"/>
       <c r="AB39" s="34"/>
       <c r="AC39" s="34"/>
       <c r="AD39" s="34"/>
-      <c r="AE39" s="47"/>
+      <c r="AE39" s="41"/>
       <c r="AF39" s="34"/>
       <c r="AG39" s="34"/>
       <c r="AH39" s="34"/>
@@ -31500,7 +31500,7 @@
       <c r="I40" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="J40" s="47"/>
+      <c r="J40" s="41"/>
       <c r="K40" s="34" t="s">
         <v>117</v>
       </c>
@@ -31519,7 +31519,7 @@
       <c r="P40" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q40" s="47"/>
+      <c r="Q40" s="41"/>
       <c r="R40" s="34" t="s">
         <v>117</v>
       </c>
@@ -31532,14 +31532,14 @@
       <c r="U40" s="34"/>
       <c r="V40" s="34"/>
       <c r="W40" s="34"/>
-      <c r="X40" s="47"/>
+      <c r="X40" s="41"/>
       <c r="Y40" s="34"/>
       <c r="Z40" s="34"/>
       <c r="AA40" s="34"/>
       <c r="AB40" s="34"/>
       <c r="AC40" s="34"/>
       <c r="AD40" s="34"/>
-      <c r="AE40" s="47"/>
+      <c r="AE40" s="41"/>
       <c r="AF40" s="34"/>
       <c r="AG40" s="34"/>
       <c r="AH40" s="34"/>
@@ -31582,7 +31582,7 @@
       <c r="I41" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="J41" s="47"/>
+      <c r="J41" s="41"/>
       <c r="K41" s="34" t="s">
         <v>117</v>
       </c>
@@ -31601,7 +31601,7 @@
       <c r="P41" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q41" s="47"/>
+      <c r="Q41" s="41"/>
       <c r="R41" s="34" t="s">
         <v>117</v>
       </c>
@@ -31614,14 +31614,14 @@
       <c r="U41" s="34"/>
       <c r="V41" s="34"/>
       <c r="W41" s="34"/>
-      <c r="X41" s="47"/>
+      <c r="X41" s="41"/>
       <c r="Y41" s="34"/>
       <c r="Z41" s="34"/>
       <c r="AA41" s="34"/>
       <c r="AB41" s="34"/>
       <c r="AC41" s="34"/>
       <c r="AD41" s="34"/>
-      <c r="AE41" s="47"/>
+      <c r="AE41" s="41"/>
       <c r="AF41" s="34"/>
       <c r="AG41" s="34"/>
       <c r="AH41" s="34"/>
@@ -31664,7 +31664,7 @@
       <c r="I42" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J42" s="47"/>
+      <c r="J42" s="41"/>
       <c r="K42" s="34" t="s">
         <v>116</v>
       </c>
@@ -31683,7 +31683,7 @@
       <c r="P42" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q42" s="47"/>
+      <c r="Q42" s="41"/>
       <c r="R42" s="34" t="s">
         <v>117</v>
       </c>
@@ -31696,14 +31696,14 @@
       <c r="U42" s="34"/>
       <c r="V42" s="34"/>
       <c r="W42" s="34"/>
-      <c r="X42" s="47"/>
+      <c r="X42" s="41"/>
       <c r="Y42" s="34"/>
       <c r="Z42" s="34"/>
       <c r="AA42" s="34"/>
       <c r="AB42" s="34"/>
       <c r="AC42" s="34"/>
       <c r="AD42" s="34"/>
-      <c r="AE42" s="47"/>
+      <c r="AE42" s="41"/>
       <c r="AF42" s="34"/>
       <c r="AG42" s="34"/>
       <c r="AH42" s="34"/>
@@ -31746,7 +31746,7 @@
       <c r="I43" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J43" s="47"/>
+      <c r="J43" s="41"/>
       <c r="K43" s="34" t="s">
         <v>117</v>
       </c>
@@ -31765,7 +31765,7 @@
       <c r="P43" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Q43" s="47"/>
+      <c r="Q43" s="41"/>
       <c r="R43" s="34" t="s">
         <v>117</v>
       </c>
@@ -31778,14 +31778,14 @@
       <c r="U43" s="34"/>
       <c r="V43" s="34"/>
       <c r="W43" s="34"/>
-      <c r="X43" s="47"/>
+      <c r="X43" s="41"/>
       <c r="Y43" s="34"/>
       <c r="Z43" s="34"/>
       <c r="AA43" s="34"/>
       <c r="AB43" s="34"/>
       <c r="AC43" s="34"/>
       <c r="AD43" s="34"/>
-      <c r="AE43" s="47"/>
+      <c r="AE43" s="41"/>
       <c r="AF43" s="34"/>
       <c r="AG43" s="34"/>
       <c r="AH43" s="34"/>
@@ -31828,7 +31828,7 @@
       <c r="I44" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J44" s="47"/>
+      <c r="J44" s="41"/>
       <c r="K44" s="34" t="s">
         <v>116</v>
       </c>
@@ -31847,7 +31847,7 @@
       <c r="P44" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q44" s="47"/>
+      <c r="Q44" s="41"/>
       <c r="R44" s="34" t="s">
         <v>116</v>
       </c>
@@ -31860,14 +31860,14 @@
       <c r="U44" s="34"/>
       <c r="V44" s="34"/>
       <c r="W44" s="34"/>
-      <c r="X44" s="47"/>
+      <c r="X44" s="41"/>
       <c r="Y44" s="34"/>
       <c r="Z44" s="34"/>
       <c r="AA44" s="34"/>
       <c r="AB44" s="34"/>
       <c r="AC44" s="34"/>
       <c r="AD44" s="34"/>
-      <c r="AE44" s="47"/>
+      <c r="AE44" s="41"/>
       <c r="AF44" s="34"/>
       <c r="AG44" s="34"/>
       <c r="AH44" s="34"/>
@@ -31910,7 +31910,7 @@
       <c r="I45" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J45" s="47"/>
+      <c r="J45" s="41"/>
       <c r="K45" s="34" t="s">
         <v>116</v>
       </c>
@@ -31929,7 +31929,7 @@
       <c r="P45" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Q45" s="47"/>
+      <c r="Q45" s="41"/>
       <c r="R45" s="34" t="s">
         <v>117</v>
       </c>
@@ -31942,14 +31942,14 @@
       <c r="U45" s="34"/>
       <c r="V45" s="34"/>
       <c r="W45" s="34"/>
-      <c r="X45" s="47"/>
+      <c r="X45" s="41"/>
       <c r="Y45" s="34"/>
       <c r="Z45" s="34"/>
       <c r="AA45" s="34"/>
       <c r="AB45" s="34"/>
       <c r="AC45" s="34"/>
       <c r="AD45" s="34"/>
-      <c r="AE45" s="47"/>
+      <c r="AE45" s="41"/>
       <c r="AF45" s="34"/>
       <c r="AG45" s="34"/>
       <c r="AH45" s="34"/>
@@ -31992,7 +31992,7 @@
       <c r="I46" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="J46" s="47"/>
+      <c r="J46" s="41"/>
       <c r="K46" s="34" t="s">
         <v>117</v>
       </c>
@@ -32011,7 +32011,7 @@
       <c r="P46" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q46" s="47"/>
+      <c r="Q46" s="41"/>
       <c r="R46" s="34" t="s">
         <v>117</v>
       </c>
@@ -32024,14 +32024,14 @@
       <c r="U46" s="34"/>
       <c r="V46" s="34"/>
       <c r="W46" s="34"/>
-      <c r="X46" s="47"/>
+      <c r="X46" s="41"/>
       <c r="Y46" s="34"/>
       <c r="Z46" s="34"/>
       <c r="AA46" s="34"/>
       <c r="AB46" s="34"/>
       <c r="AC46" s="34"/>
       <c r="AD46" s="34"/>
-      <c r="AE46" s="47"/>
+      <c r="AE46" s="41"/>
       <c r="AF46" s="34"/>
       <c r="AG46" s="34"/>
       <c r="AH46" s="34"/>
@@ -32074,7 +32074,7 @@
       <c r="I47" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J47" s="47"/>
+      <c r="J47" s="41"/>
       <c r="K47" s="34" t="s">
         <v>116</v>
       </c>
@@ -32093,7 +32093,7 @@
       <c r="P47" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q47" s="47"/>
+      <c r="Q47" s="41"/>
       <c r="R47" s="34" t="s">
         <v>117</v>
       </c>
@@ -32106,14 +32106,14 @@
       <c r="U47" s="34"/>
       <c r="V47" s="34"/>
       <c r="W47" s="34"/>
-      <c r="X47" s="47"/>
+      <c r="X47" s="41"/>
       <c r="Y47" s="34"/>
       <c r="Z47" s="34"/>
       <c r="AA47" s="34"/>
       <c r="AB47" s="34"/>
       <c r="AC47" s="34"/>
       <c r="AD47" s="34"/>
-      <c r="AE47" s="47"/>
+      <c r="AE47" s="41"/>
       <c r="AF47" s="34"/>
       <c r="AG47" s="34"/>
       <c r="AH47" s="34"/>
@@ -32154,7 +32154,7 @@
       <c r="I48" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J48" s="47"/>
+      <c r="J48" s="41"/>
       <c r="K48" s="34" t="s">
         <v>116</v>
       </c>
@@ -32173,7 +32173,7 @@
       <c r="P48" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q48" s="47"/>
+      <c r="Q48" s="41"/>
       <c r="R48" s="34" t="s">
         <v>117</v>
       </c>
@@ -32186,14 +32186,14 @@
       <c r="U48" s="34"/>
       <c r="V48" s="34"/>
       <c r="W48" s="34"/>
-      <c r="X48" s="47"/>
+      <c r="X48" s="41"/>
       <c r="Y48" s="34"/>
       <c r="Z48" s="34"/>
       <c r="AA48" s="34"/>
       <c r="AB48" s="34"/>
       <c r="AC48" s="34"/>
       <c r="AD48" s="34"/>
-      <c r="AE48" s="47"/>
+      <c r="AE48" s="41"/>
       <c r="AF48" s="34"/>
       <c r="AG48" s="34"/>
       <c r="AH48" s="34"/>
@@ -32236,7 +32236,7 @@
       <c r="I49" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J49" s="47"/>
+      <c r="J49" s="41"/>
       <c r="K49" s="34" t="s">
         <v>117</v>
       </c>
@@ -32255,7 +32255,7 @@
       <c r="P49" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q49" s="47"/>
+      <c r="Q49" s="41"/>
       <c r="R49" s="34" t="s">
         <v>116</v>
       </c>
@@ -32268,14 +32268,14 @@
       <c r="U49" s="34"/>
       <c r="V49" s="34"/>
       <c r="W49" s="34"/>
-      <c r="X49" s="47"/>
+      <c r="X49" s="41"/>
       <c r="Y49" s="34"/>
       <c r="Z49" s="34"/>
       <c r="AA49" s="34"/>
       <c r="AB49" s="34"/>
       <c r="AC49" s="34"/>
       <c r="AD49" s="34"/>
-      <c r="AE49" s="47"/>
+      <c r="AE49" s="41"/>
       <c r="AF49" s="34"/>
       <c r="AG49" s="34"/>
       <c r="AH49" s="34"/>
@@ -32318,7 +32318,7 @@
       <c r="I50" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="J50" s="47"/>
+      <c r="J50" s="41"/>
       <c r="K50" s="34" t="s">
         <v>117</v>
       </c>
@@ -32337,7 +32337,7 @@
       <c r="P50" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q50" s="47"/>
+      <c r="Q50" s="41"/>
       <c r="R50" s="34" t="s">
         <v>117</v>
       </c>
@@ -32350,14 +32350,14 @@
       <c r="U50" s="34"/>
       <c r="V50" s="34"/>
       <c r="W50" s="34"/>
-      <c r="X50" s="47"/>
+      <c r="X50" s="41"/>
       <c r="Y50" s="34"/>
       <c r="Z50" s="34"/>
       <c r="AA50" s="34"/>
       <c r="AB50" s="34"/>
       <c r="AC50" s="34"/>
       <c r="AD50" s="34"/>
-      <c r="AE50" s="47"/>
+      <c r="AE50" s="41"/>
       <c r="AF50" s="34"/>
       <c r="AG50" s="34"/>
       <c r="AH50" s="34"/>
@@ -32400,7 +32400,7 @@
       <c r="I51" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J51" s="47"/>
+      <c r="J51" s="41"/>
       <c r="K51" s="34" t="s">
         <v>116</v>
       </c>
@@ -32419,7 +32419,7 @@
       <c r="P51" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q51" s="47"/>
+      <c r="Q51" s="41"/>
       <c r="R51" s="34" t="s">
         <v>117</v>
       </c>
@@ -32430,14 +32430,14 @@
       <c r="U51" s="34"/>
       <c r="V51" s="34"/>
       <c r="W51" s="34"/>
-      <c r="X51" s="47"/>
+      <c r="X51" s="41"/>
       <c r="Y51" s="34"/>
       <c r="Z51" s="34"/>
       <c r="AA51" s="34"/>
       <c r="AB51" s="34"/>
       <c r="AC51" s="34"/>
       <c r="AD51" s="34"/>
-      <c r="AE51" s="47"/>
+      <c r="AE51" s="41"/>
       <c r="AF51" s="34"/>
       <c r="AG51" s="34"/>
       <c r="AH51" s="34"/>
@@ -32478,7 +32478,7 @@
       <c r="I52" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="J52" s="47"/>
+      <c r="J52" s="41"/>
       <c r="K52" s="34" t="s">
         <v>117</v>
       </c>
@@ -32497,7 +32497,7 @@
       <c r="P52" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Q52" s="47"/>
+      <c r="Q52" s="41"/>
       <c r="R52" s="34" t="s">
         <v>116</v>
       </c>
@@ -32510,14 +32510,14 @@
       <c r="U52" s="34"/>
       <c r="V52" s="34"/>
       <c r="W52" s="34"/>
-      <c r="X52" s="47"/>
+      <c r="X52" s="41"/>
       <c r="Y52" s="34"/>
       <c r="Z52" s="34"/>
       <c r="AA52" s="34"/>
       <c r="AB52" s="34"/>
       <c r="AC52" s="34"/>
       <c r="AD52" s="34"/>
-      <c r="AE52" s="47"/>
+      <c r="AE52" s="41"/>
       <c r="AF52" s="34"/>
       <c r="AG52" s="34"/>
       <c r="AH52" s="34"/>
@@ -32558,7 +32558,7 @@
       <c r="I53" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J53" s="47"/>
+      <c r="J53" s="41"/>
       <c r="K53" s="34" t="s">
         <v>116</v>
       </c>
@@ -32577,7 +32577,7 @@
       <c r="P53" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q53" s="47"/>
+      <c r="Q53" s="41"/>
       <c r="R53" s="34" t="s">
         <v>117</v>
       </c>
@@ -32590,14 +32590,14 @@
       <c r="U53" s="34"/>
       <c r="V53" s="34"/>
       <c r="W53" s="34"/>
-      <c r="X53" s="47"/>
+      <c r="X53" s="41"/>
       <c r="Y53" s="34"/>
       <c r="Z53" s="34"/>
       <c r="AA53" s="34"/>
       <c r="AB53" s="34"/>
       <c r="AC53" s="34"/>
       <c r="AD53" s="34"/>
-      <c r="AE53" s="47"/>
+      <c r="AE53" s="41"/>
       <c r="AF53" s="34"/>
       <c r="AG53" s="34"/>
       <c r="AH53" s="34"/>
@@ -32638,7 +32638,7 @@
       <c r="I54" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J54" s="47"/>
+      <c r="J54" s="41"/>
       <c r="K54" s="34" t="s">
         <v>117</v>
       </c>
@@ -32657,7 +32657,7 @@
       <c r="P54" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q54" s="47"/>
+      <c r="Q54" s="41"/>
       <c r="R54" s="34" t="s">
         <v>117</v>
       </c>
@@ -32670,14 +32670,14 @@
       <c r="U54" s="34"/>
       <c r="V54" s="34"/>
       <c r="W54" s="34"/>
-      <c r="X54" s="47"/>
+      <c r="X54" s="41"/>
       <c r="Y54" s="34"/>
       <c r="Z54" s="34"/>
       <c r="AA54" s="34"/>
       <c r="AB54" s="34"/>
       <c r="AC54" s="34"/>
       <c r="AD54" s="34"/>
-      <c r="AE54" s="47"/>
+      <c r="AE54" s="41"/>
       <c r="AF54" s="34"/>
       <c r="AG54" s="34"/>
       <c r="AH54" s="34"/>
@@ -32718,7 +32718,7 @@
       <c r="I55" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J55" s="47"/>
+      <c r="J55" s="41"/>
       <c r="K55" s="34" t="s">
         <v>116</v>
       </c>
@@ -32737,7 +32737,7 @@
       <c r="P55" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q55" s="47"/>
+      <c r="Q55" s="41"/>
       <c r="R55" s="34" t="s">
         <v>117</v>
       </c>
@@ -32750,14 +32750,14 @@
       <c r="U55" s="34"/>
       <c r="V55" s="34"/>
       <c r="W55" s="34"/>
-      <c r="X55" s="47"/>
+      <c r="X55" s="41"/>
       <c r="Y55" s="34"/>
       <c r="Z55" s="34"/>
       <c r="AA55" s="34"/>
       <c r="AB55" s="34"/>
       <c r="AC55" s="34"/>
       <c r="AD55" s="34"/>
-      <c r="AE55" s="47"/>
+      <c r="AE55" s="41"/>
       <c r="AF55" s="34"/>
       <c r="AG55" s="34"/>
       <c r="AH55" s="34"/>
@@ -32798,7 +32798,7 @@
       <c r="I56" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="J56" s="47"/>
+      <c r="J56" s="41"/>
       <c r="K56" s="34" t="s">
         <v>116</v>
       </c>
@@ -32817,7 +32817,7 @@
       <c r="P56" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q56" s="47"/>
+      <c r="Q56" s="41"/>
       <c r="R56" s="34" t="s">
         <v>117</v>
       </c>
@@ -32830,14 +32830,14 @@
       <c r="U56" s="34"/>
       <c r="V56" s="34"/>
       <c r="W56" s="34"/>
-      <c r="X56" s="47"/>
+      <c r="X56" s="41"/>
       <c r="Y56" s="34"/>
       <c r="Z56" s="34"/>
       <c r="AA56" s="34"/>
       <c r="AB56" s="34"/>
       <c r="AC56" s="34"/>
       <c r="AD56" s="34"/>
-      <c r="AE56" s="47"/>
+      <c r="AE56" s="41"/>
       <c r="AF56" s="34"/>
       <c r="AG56" s="34"/>
       <c r="AH56" s="34"/>
@@ -32878,7 +32878,7 @@
       <c r="I57" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="J57" s="47"/>
+      <c r="J57" s="41"/>
       <c r="K57" s="34" t="s">
         <v>117</v>
       </c>
@@ -32897,7 +32897,7 @@
       <c r="P57" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q57" s="47"/>
+      <c r="Q57" s="41"/>
       <c r="R57" s="34" t="s">
         <v>117</v>
       </c>
@@ -32910,14 +32910,14 @@
       <c r="U57" s="34"/>
       <c r="V57" s="34"/>
       <c r="W57" s="34"/>
-      <c r="X57" s="47"/>
+      <c r="X57" s="41"/>
       <c r="Y57" s="34"/>
       <c r="Z57" s="34"/>
       <c r="AA57" s="34"/>
       <c r="AB57" s="34"/>
       <c r="AC57" s="34"/>
       <c r="AD57" s="34"/>
-      <c r="AE57" s="47"/>
+      <c r="AE57" s="41"/>
       <c r="AF57" s="34"/>
       <c r="AG57" s="34"/>
       <c r="AH57" s="34"/>
@@ -32960,7 +32960,7 @@
       <c r="I58" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J58" s="48"/>
+      <c r="J58" s="42"/>
       <c r="K58" s="34" t="s">
         <v>116</v>
       </c>
@@ -32979,7 +32979,7 @@
       <c r="P58" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q58" s="48"/>
+      <c r="Q58" s="42"/>
       <c r="R58" s="34" t="s">
         <v>117</v>
       </c>
@@ -32992,14 +32992,14 @@
       <c r="U58" s="34"/>
       <c r="V58" s="34"/>
       <c r="W58" s="34"/>
-      <c r="X58" s="48"/>
+      <c r="X58" s="42"/>
       <c r="Y58" s="34"/>
       <c r="Z58" s="34"/>
       <c r="AA58" s="34"/>
       <c r="AB58" s="34"/>
       <c r="AC58" s="34"/>
       <c r="AD58" s="34"/>
-      <c r="AE58" s="48"/>
+      <c r="AE58" s="42"/>
       <c r="AF58" s="34"/>
       <c r="AG58" s="34"/>
       <c r="AH58" s="34"/>
